--- a/gstdatabase/GSTR-1-2019-2020.xlsx
+++ b/gstdatabase/GSTR-1-2019-2020.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Feb-26\GST Statistics Downloads 28th Feb 26\Downloads\GSTR 1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\May-26\GST Statistics Downloads 31st May 26\Downloads\GSTR 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62F9C0CB-E0F0-46A4-ACE9-C31CF49FD465}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8763A217-B6B4-4FF8-9138-2DC3F70EEE84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -185,10 +185,10 @@
     <t>Andaman and Nicobar Islands</t>
   </si>
   <si>
-    <t>Data Considered upto 28th Feb 2026</t>
+    <t>Data Considered upto 31st May 2026</t>
   </si>
   <si>
-    <t>Filing %age as on 28th Feb 2026</t>
+    <t>Filing %age as on 31st May 2026</t>
   </si>
 </sst>
 </file>
@@ -1387,14 +1387,14 @@
       </c>
       <c r="AI10" s="6">
         <f t="shared" ref="AI10:AI46" si="12">AJ10-AH10</f>
-        <v>12034</v>
+        <v>12035</v>
       </c>
       <c r="AJ10" s="14">
-        <v>18764</v>
+        <v>18765</v>
       </c>
       <c r="AK10" s="7">
         <f t="shared" ref="AK10:AK46" si="13">AJ10/AG10</f>
-        <v>0.63639138545022889</v>
+        <v>0.63642530100050876</v>
       </c>
       <c r="AL10" s="13">
         <v>28002</v>
@@ -1438,14 +1438,14 @@
       </c>
       <c r="AX10" s="6">
         <f t="shared" ref="AX10:AX46" si="18">AY10-AW10</f>
-        <v>8724</v>
+        <v>8726</v>
       </c>
       <c r="AY10" s="14">
-        <v>19075</v>
+        <v>19077</v>
       </c>
       <c r="AZ10" s="7">
         <f t="shared" ref="AZ10:AZ46" si="19">AY10/AV10</f>
-        <v>0.78646821142904266</v>
+        <v>0.78655067205409412</v>
       </c>
       <c r="BA10" s="13">
         <v>23136</v>
@@ -1455,14 +1455,14 @@
       </c>
       <c r="BC10" s="6">
         <f t="shared" ref="BC10:BC46" si="20">BD10-BB10</f>
-        <v>4134</v>
+        <v>4135</v>
       </c>
       <c r="BD10" s="14">
-        <v>18992</v>
+        <v>18993</v>
       </c>
       <c r="BE10" s="7">
         <f t="shared" ref="BE10:BE46" si="21">BD10/BA10</f>
-        <v>0.82088520055325032</v>
+        <v>0.82092842323651449</v>
       </c>
       <c r="BF10" s="13">
         <v>86286</v>
@@ -1497,14 +1497,14 @@
       </c>
       <c r="E11" s="6">
         <f t="shared" si="0"/>
-        <v>33672</v>
+        <v>33674</v>
       </c>
       <c r="F11" s="14">
-        <v>80282</v>
+        <v>80284</v>
       </c>
       <c r="G11" s="7">
         <f t="shared" si="1"/>
-        <v>0.65025675916476322</v>
+        <v>0.65027295848115207</v>
       </c>
       <c r="H11" s="13">
         <v>119967</v>
@@ -1514,14 +1514,14 @@
       </c>
       <c r="J11" s="6">
         <f t="shared" si="2"/>
-        <v>32235</v>
+        <v>32237</v>
       </c>
       <c r="K11" s="14">
-        <v>80360</v>
+        <v>80362</v>
       </c>
       <c r="L11" s="7">
         <f t="shared" si="3"/>
-        <v>0.66985087565747248</v>
+        <v>0.66986754690873318</v>
       </c>
       <c r="M11" s="13">
         <v>308875</v>
@@ -1548,14 +1548,14 @@
       </c>
       <c r="T11" s="6">
         <f t="shared" si="6"/>
-        <v>37776</v>
+        <v>37777</v>
       </c>
       <c r="U11" s="14">
-        <v>80673</v>
+        <v>80674</v>
       </c>
       <c r="V11" s="7">
         <f t="shared" si="7"/>
-        <v>0.73532950505879136</v>
+        <v>0.73533861999817696</v>
       </c>
       <c r="W11" s="13">
         <v>106470</v>
@@ -1565,14 +1565,14 @@
       </c>
       <c r="Y11" s="6">
         <f t="shared" si="8"/>
-        <v>35323</v>
+        <v>35325</v>
       </c>
       <c r="Z11" s="14">
-        <v>80882</v>
+        <v>80884</v>
       </c>
       <c r="AA11" s="7">
         <f t="shared" si="9"/>
-        <v>0.75966939043862125</v>
+        <v>0.75968817507279041</v>
       </c>
       <c r="AB11" s="13">
         <v>311089</v>
@@ -1599,14 +1599,14 @@
       </c>
       <c r="AI11" s="6">
         <f t="shared" si="12"/>
-        <v>41899</v>
+        <v>41901</v>
       </c>
       <c r="AJ11" s="14">
-        <v>81282</v>
+        <v>81284</v>
       </c>
       <c r="AK11" s="7">
         <f t="shared" si="13"/>
-        <v>0.80077632408575028</v>
+        <v>0.80079602774274905</v>
       </c>
       <c r="AL11" s="13">
         <v>97659</v>
@@ -1616,14 +1616,14 @@
       </c>
       <c r="AN11" s="6">
         <f t="shared" si="14"/>
-        <v>35080</v>
+        <v>35082</v>
       </c>
       <c r="AO11" s="14">
-        <v>81621</v>
+        <v>81623</v>
       </c>
       <c r="AP11" s="7">
         <f t="shared" si="15"/>
-        <v>0.8357755045617915</v>
+        <v>0.83579598398509103</v>
       </c>
       <c r="AQ11" s="13">
         <v>308579</v>
@@ -1633,14 +1633,14 @@
       </c>
       <c r="AS11" s="6">
         <f t="shared" si="16"/>
-        <v>60441</v>
+        <v>60442</v>
       </c>
       <c r="AT11" s="15">
-        <v>286177</v>
+        <v>286178</v>
       </c>
       <c r="AU11" s="7">
         <f t="shared" si="17"/>
-        <v>0.92740270724838691</v>
+        <v>0.92740594790961151</v>
       </c>
       <c r="AV11" s="13">
         <v>95635</v>
@@ -1650,14 +1650,14 @@
       </c>
       <c r="AX11" s="6">
         <f t="shared" si="18"/>
-        <v>22639</v>
+        <v>22641</v>
       </c>
       <c r="AY11" s="14">
-        <v>81845</v>
+        <v>81847</v>
       </c>
       <c r="AZ11" s="7">
         <f t="shared" si="19"/>
-        <v>0.85580592879176032</v>
+        <v>0.8558268416374758</v>
       </c>
       <c r="BA11" s="13">
         <v>94540</v>
@@ -1667,14 +1667,14 @@
       </c>
       <c r="BC11" s="6">
         <f t="shared" si="20"/>
-        <v>10545</v>
+        <v>10547</v>
       </c>
       <c r="BD11" s="14">
-        <v>81916</v>
+        <v>81918</v>
       </c>
       <c r="BE11" s="7">
         <f t="shared" si="21"/>
-        <v>0.866469219378041</v>
+        <v>0.86649037444467947</v>
       </c>
       <c r="BF11" s="13">
         <v>312194</v>
@@ -1684,14 +1684,14 @@
       </c>
       <c r="BH11" s="6">
         <f t="shared" si="22"/>
-        <v>52703</v>
+        <v>52704</v>
       </c>
       <c r="BI11" s="15">
-        <v>286766</v>
+        <v>286767</v>
       </c>
       <c r="BJ11" s="7">
         <f t="shared" si="23"/>
-        <v>0.91855064479137971</v>
+        <v>0.91855384792789097</v>
       </c>
     </row>
     <row r="12" spans="1:62" x14ac:dyDescent="0.3">
@@ -1921,14 +1921,14 @@
       </c>
       <c r="E13" s="6">
         <f t="shared" si="0"/>
-        <v>21647</v>
+        <v>21649</v>
       </c>
       <c r="F13" s="14">
-        <v>30723</v>
+        <v>30725</v>
       </c>
       <c r="G13" s="7">
         <f t="shared" si="1"/>
-        <v>0.4809034843314654</v>
+        <v>0.48093479009485646</v>
       </c>
       <c r="H13" s="13">
         <v>59731</v>
@@ -1938,14 +1938,14 @@
       </c>
       <c r="J13" s="6">
         <f t="shared" si="2"/>
-        <v>21938</v>
+        <v>21940</v>
       </c>
       <c r="K13" s="14">
-        <v>30921</v>
+        <v>30923</v>
       </c>
       <c r="L13" s="7">
         <f t="shared" si="3"/>
-        <v>0.51767089116204312</v>
+        <v>0.51770437461284757</v>
       </c>
       <c r="M13" s="13">
         <v>129422</v>
@@ -1955,14 +1955,14 @@
       </c>
       <c r="O13" s="6">
         <f t="shared" si="4"/>
-        <v>68067</v>
+        <v>68074</v>
       </c>
       <c r="P13" s="15">
-        <v>110015</v>
+        <v>110022</v>
       </c>
       <c r="Q13" s="7">
         <f t="shared" si="5"/>
-        <v>0.85004867796819705</v>
+        <v>0.85010276459952716</v>
       </c>
       <c r="R13" s="13">
         <v>54062</v>
@@ -1972,14 +1972,14 @@
       </c>
       <c r="T13" s="6">
         <f t="shared" si="6"/>
-        <v>22607</v>
+        <v>22610</v>
       </c>
       <c r="U13" s="14">
-        <v>31329</v>
+        <v>31332</v>
       </c>
       <c r="V13" s="7">
         <f t="shared" si="7"/>
-        <v>0.57950131330694388</v>
+        <v>0.57955680514964303</v>
       </c>
       <c r="W13" s="13">
         <v>51426</v>
@@ -1989,14 +1989,14 @@
       </c>
       <c r="Y13" s="6">
         <f t="shared" si="8"/>
-        <v>22434</v>
+        <v>22436</v>
       </c>
       <c r="Z13" s="14">
-        <v>31583</v>
+        <v>31585</v>
       </c>
       <c r="AA13" s="7">
         <f t="shared" si="9"/>
-        <v>0.61414459611869487</v>
+        <v>0.61418348695212543</v>
       </c>
       <c r="AB13" s="13">
         <v>131532</v>
@@ -2006,14 +2006,14 @@
       </c>
       <c r="AD13" s="6">
         <f t="shared" si="10"/>
-        <v>76391</v>
+        <v>76398</v>
       </c>
       <c r="AE13" s="15">
-        <v>113197</v>
+        <v>113204</v>
       </c>
       <c r="AF13" s="7">
         <f t="shared" si="11"/>
-        <v>0.86060426360125297</v>
+        <v>0.86065748258978803</v>
       </c>
       <c r="AG13" s="13">
         <v>48183</v>
@@ -2023,14 +2023,14 @@
       </c>
       <c r="AI13" s="6">
         <f t="shared" si="12"/>
-        <v>23602</v>
+        <v>23605</v>
       </c>
       <c r="AJ13" s="14">
-        <v>32138</v>
+        <v>32141</v>
       </c>
       <c r="AK13" s="7">
         <f t="shared" si="13"/>
-        <v>0.66699873399331711</v>
+        <v>0.66706099661706408</v>
       </c>
       <c r="AL13" s="13">
         <v>44607</v>
@@ -2040,14 +2040,14 @@
       </c>
       <c r="AN13" s="6">
         <f t="shared" si="14"/>
-        <v>21900</v>
+        <v>21902</v>
       </c>
       <c r="AO13" s="14">
-        <v>32579</v>
+        <v>32581</v>
       </c>
       <c r="AP13" s="7">
         <f t="shared" si="15"/>
-        <v>0.73035622211760487</v>
+        <v>0.73040105812988998</v>
       </c>
       <c r="AQ13" s="13">
         <v>128458</v>
@@ -2057,14 +2057,14 @@
       </c>
       <c r="AS13" s="6">
         <f t="shared" si="16"/>
-        <v>42764</v>
+        <v>42773</v>
       </c>
       <c r="AT13" s="15">
-        <v>115591</v>
+        <v>115600</v>
       </c>
       <c r="AU13" s="7">
         <f t="shared" si="17"/>
-        <v>0.8998349655140202</v>
+        <v>0.89990502732410593</v>
       </c>
       <c r="AV13" s="13">
         <v>43497</v>
@@ -2074,14 +2074,14 @@
       </c>
       <c r="AX13" s="6">
         <f t="shared" si="18"/>
-        <v>16344</v>
+        <v>16346</v>
       </c>
       <c r="AY13" s="14">
-        <v>32536</v>
+        <v>32538</v>
       </c>
       <c r="AZ13" s="7">
         <f t="shared" si="19"/>
-        <v>0.74800560958227003</v>
+        <v>0.74805158976481134</v>
       </c>
       <c r="BA13" s="13">
         <v>42767</v>
@@ -2091,14 +2091,14 @@
       </c>
       <c r="BC13" s="6">
         <f t="shared" si="20"/>
-        <v>8686</v>
+        <v>8689</v>
       </c>
       <c r="BD13" s="14">
-        <v>32553</v>
+        <v>32556</v>
       </c>
       <c r="BE13" s="7">
         <f t="shared" si="21"/>
-        <v>0.76117099632894525</v>
+        <v>0.7612411438726121</v>
       </c>
       <c r="BF13" s="13">
         <v>131773</v>
@@ -2108,14 +2108,14 @@
       </c>
       <c r="BH13" s="6">
         <f t="shared" si="22"/>
-        <v>38715</v>
+        <v>38731</v>
       </c>
       <c r="BI13" s="15">
-        <v>114868</v>
+        <v>114884</v>
       </c>
       <c r="BJ13" s="7">
         <f t="shared" si="23"/>
-        <v>0.87171120032176541</v>
+        <v>0.87183262125018024</v>
       </c>
     </row>
     <row r="14" spans="1:62" x14ac:dyDescent="0.3">
@@ -2269,14 +2269,14 @@
       </c>
       <c r="AS14" s="6">
         <f t="shared" si="16"/>
-        <v>103992</v>
+        <v>103993</v>
       </c>
       <c r="AT14" s="15">
-        <v>383963</v>
+        <v>383964</v>
       </c>
       <c r="AU14" s="7">
         <f t="shared" si="17"/>
-        <v>0.90462794768673294</v>
+        <v>0.90463030371569331</v>
       </c>
       <c r="AV14" s="13">
         <v>153606</v>
@@ -2320,14 +2320,14 @@
       </c>
       <c r="BH14" s="6">
         <f t="shared" si="22"/>
-        <v>88260</v>
+        <v>88262</v>
       </c>
       <c r="BI14" s="15">
-        <v>383339</v>
+        <v>383341</v>
       </c>
       <c r="BJ14" s="7">
         <f t="shared" si="23"/>
-        <v>0.90548740879317635</v>
+        <v>0.90549213300547304</v>
       </c>
     </row>
     <row r="15" spans="1:62" x14ac:dyDescent="0.3">
@@ -2345,14 +2345,14 @@
       </c>
       <c r="E15" s="6">
         <f t="shared" si="0"/>
-        <v>98666</v>
+        <v>98667</v>
       </c>
       <c r="F15" s="14">
-        <v>169653</v>
+        <v>169654</v>
       </c>
       <c r="G15" s="7">
         <f t="shared" si="1"/>
-        <v>0.46546331506082606</v>
+        <v>0.46546605868053842</v>
       </c>
       <c r="H15" s="13">
         <v>355644</v>
@@ -2430,14 +2430,14 @@
       </c>
       <c r="AD15" s="6">
         <f t="shared" si="10"/>
-        <v>363278</v>
+        <v>363279</v>
       </c>
       <c r="AE15" s="15">
-        <v>629776</v>
+        <v>629777</v>
       </c>
       <c r="AF15" s="7">
         <f t="shared" si="11"/>
-        <v>0.82186467817773468</v>
+        <v>0.82186598318884685</v>
       </c>
       <c r="AG15" s="13">
         <v>285320</v>
@@ -2532,14 +2532,14 @@
       </c>
       <c r="BH15" s="6">
         <f t="shared" si="22"/>
-        <v>177747</v>
+        <v>177750</v>
       </c>
       <c r="BI15" s="15">
-        <v>634472</v>
+        <v>634475</v>
       </c>
       <c r="BJ15" s="7">
         <f t="shared" si="23"/>
-        <v>0.8435893685764051</v>
+        <v>0.84359335735464225</v>
       </c>
     </row>
     <row r="16" spans="1:62" x14ac:dyDescent="0.3">
@@ -2557,14 +2557,14 @@
       </c>
       <c r="E16" s="6">
         <f t="shared" si="0"/>
-        <v>70968</v>
+        <v>70972</v>
       </c>
       <c r="F16" s="14">
-        <v>122146</v>
+        <v>122150</v>
       </c>
       <c r="G16" s="7">
         <f t="shared" si="1"/>
-        <v>0.49552531866384314</v>
+        <v>0.49554154597603228</v>
       </c>
       <c r="H16" s="13">
         <v>236220</v>
@@ -2574,14 +2574,14 @@
       </c>
       <c r="J16" s="6">
         <f t="shared" si="2"/>
-        <v>67805</v>
+        <v>67808</v>
       </c>
       <c r="K16" s="14">
-        <v>122232</v>
+        <v>122235</v>
       </c>
       <c r="L16" s="7">
         <f t="shared" si="3"/>
-        <v>0.51744983489966978</v>
+        <v>0.51746253492506988</v>
       </c>
       <c r="M16" s="13">
         <v>560439</v>
@@ -2591,14 +2591,14 @@
       </c>
       <c r="O16" s="6">
         <f t="shared" si="4"/>
-        <v>226141</v>
+        <v>226145</v>
       </c>
       <c r="P16" s="15">
-        <v>489302</v>
+        <v>489306</v>
       </c>
       <c r="Q16" s="7">
         <f t="shared" si="5"/>
-        <v>0.87306914757895149</v>
+        <v>0.87307628484099076</v>
       </c>
       <c r="R16" s="13">
         <v>205814</v>
@@ -2608,14 +2608,14 @@
       </c>
       <c r="T16" s="6">
         <f t="shared" si="6"/>
-        <v>72871</v>
+        <v>72872</v>
       </c>
       <c r="U16" s="14">
-        <v>123836</v>
+        <v>123837</v>
       </c>
       <c r="V16" s="7">
         <f t="shared" si="7"/>
-        <v>0.6016889035731291</v>
+        <v>0.60169376232909322</v>
       </c>
       <c r="W16" s="13">
         <v>193923</v>
@@ -2625,14 +2625,14 @@
       </c>
       <c r="Y16" s="6">
         <f t="shared" si="8"/>
-        <v>69744</v>
+        <v>69745</v>
       </c>
       <c r="Z16" s="14">
-        <v>123964</v>
+        <v>123965</v>
       </c>
       <c r="AA16" s="7">
         <f t="shared" si="9"/>
-        <v>0.63924341104458982</v>
+        <v>0.63924856773049099</v>
       </c>
       <c r="AB16" s="13">
         <v>559918</v>
@@ -2642,14 +2642,14 @@
       </c>
       <c r="AD16" s="6">
         <f t="shared" si="10"/>
-        <v>300028</v>
+        <v>300033</v>
       </c>
       <c r="AE16" s="15">
-        <v>499291</v>
+        <v>499296</v>
       </c>
       <c r="AF16" s="7">
         <f t="shared" si="11"/>
-        <v>0.89172164495515416</v>
+        <v>0.89173057483417217</v>
       </c>
       <c r="AG16" s="13">
         <v>184413</v>
@@ -2659,14 +2659,14 @@
       </c>
       <c r="AI16" s="6">
         <f t="shared" si="12"/>
-        <v>81873</v>
+        <v>81875</v>
       </c>
       <c r="AJ16" s="14">
-        <v>125167</v>
+        <v>125169</v>
       </c>
       <c r="AK16" s="7">
         <f t="shared" si="13"/>
-        <v>0.67873197659601003</v>
+        <v>0.6787428218184185</v>
       </c>
       <c r="AL16" s="13">
         <v>173833</v>
@@ -2676,14 +2676,14 @@
       </c>
       <c r="AN16" s="6">
         <f t="shared" si="14"/>
-        <v>72241</v>
+        <v>72245</v>
       </c>
       <c r="AO16" s="14">
-        <v>127952</v>
+        <v>127956</v>
       </c>
       <c r="AP16" s="7">
         <f t="shared" si="15"/>
-        <v>0.73606277289122324</v>
+        <v>0.7360857834818475</v>
       </c>
       <c r="AQ16" s="13">
         <v>541872</v>
@@ -2693,14 +2693,14 @@
       </c>
       <c r="AS16" s="6">
         <f t="shared" si="16"/>
-        <v>139187</v>
+        <v>139194</v>
       </c>
       <c r="AT16" s="15">
-        <v>507930</v>
+        <v>507937</v>
       </c>
       <c r="AU16" s="7">
         <f t="shared" si="17"/>
-        <v>0.93736159092922311</v>
+        <v>0.93737450910916231</v>
       </c>
       <c r="AV16" s="13">
         <v>152784</v>
@@ -2710,14 +2710,14 @@
       </c>
       <c r="AX16" s="6">
         <f t="shared" si="18"/>
-        <v>47561</v>
+        <v>47564</v>
       </c>
       <c r="AY16" s="14">
-        <v>126480</v>
+        <v>126483</v>
       </c>
       <c r="AZ16" s="7">
         <f t="shared" si="19"/>
-        <v>0.82783537543198238</v>
+        <v>0.82785501099591585</v>
       </c>
       <c r="BA16" s="13">
         <v>150750</v>
@@ -2727,14 +2727,14 @@
       </c>
       <c r="BC16" s="6">
         <f t="shared" si="20"/>
-        <v>24123</v>
+        <v>24125</v>
       </c>
       <c r="BD16" s="14">
-        <v>126191</v>
+        <v>126193</v>
       </c>
       <c r="BE16" s="7">
         <f t="shared" si="21"/>
-        <v>0.83708789386401328</v>
+        <v>0.83710116086235486</v>
       </c>
       <c r="BF16" s="13">
         <v>552190</v>
@@ -2744,14 +2744,14 @@
       </c>
       <c r="BH16" s="6">
         <f t="shared" si="22"/>
-        <v>134265</v>
+        <v>134280</v>
       </c>
       <c r="BI16" s="15">
-        <v>511720</v>
+        <v>511735</v>
       </c>
       <c r="BJ16" s="7">
         <f t="shared" si="23"/>
-        <v>0.92671000923595137</v>
+        <v>0.92673717379887355</v>
       </c>
     </row>
     <row r="17" spans="1:62" x14ac:dyDescent="0.3">
@@ -2769,14 +2769,14 @@
       </c>
       <c r="E17" s="6">
         <f t="shared" si="0"/>
-        <v>210826</v>
+        <v>210829</v>
       </c>
       <c r="F17" s="14">
-        <v>290684</v>
+        <v>290687</v>
       </c>
       <c r="G17" s="7">
         <f t="shared" si="1"/>
-        <v>0.55425812651585638</v>
+        <v>0.55426384672880091</v>
       </c>
       <c r="H17" s="13">
         <v>496559</v>
@@ -2786,14 +2786,14 @@
       </c>
       <c r="J17" s="6">
         <f t="shared" si="2"/>
-        <v>213167</v>
+        <v>213169</v>
       </c>
       <c r="K17" s="14">
-        <v>291883</v>
+        <v>291885</v>
       </c>
       <c r="L17" s="7">
         <f t="shared" si="3"/>
-        <v>0.58781131748694515</v>
+        <v>0.58781534520570566</v>
       </c>
       <c r="M17" s="13">
         <v>1118687</v>
@@ -2803,14 +2803,14 @@
       </c>
       <c r="O17" s="6">
         <f t="shared" si="4"/>
-        <v>588928</v>
+        <v>588933</v>
       </c>
       <c r="P17" s="15">
-        <v>956746</v>
+        <v>956751</v>
       </c>
       <c r="Q17" s="7">
         <f t="shared" si="5"/>
-        <v>0.85524011631492991</v>
+        <v>0.85524458584036467</v>
       </c>
       <c r="R17" s="13">
         <v>453407</v>
@@ -2820,14 +2820,14 @@
       </c>
       <c r="T17" s="6">
         <f t="shared" si="6"/>
-        <v>222423</v>
+        <v>222425</v>
       </c>
       <c r="U17" s="14">
-        <v>295661</v>
+        <v>295663</v>
       </c>
       <c r="V17" s="7">
         <f t="shared" si="7"/>
-        <v>0.65208741814749216</v>
+        <v>0.65209182919540276</v>
       </c>
       <c r="W17" s="13">
         <v>432883</v>
@@ -2837,14 +2837,14 @@
       </c>
       <c r="Y17" s="6">
         <f t="shared" si="8"/>
-        <v>221220</v>
+        <v>221222</v>
       </c>
       <c r="Z17" s="14">
-        <v>298023</v>
+        <v>298025</v>
       </c>
       <c r="AA17" s="7">
         <f t="shared" si="9"/>
-        <v>0.68846085431860338</v>
+        <v>0.68846547450465834</v>
       </c>
       <c r="AB17" s="13">
         <v>1126122</v>
@@ -2854,14 +2854,14 @@
       </c>
       <c r="AD17" s="6">
         <f t="shared" si="10"/>
-        <v>697972</v>
+        <v>697979</v>
       </c>
       <c r="AE17" s="15">
-        <v>983306</v>
+        <v>983313</v>
       </c>
       <c r="AF17" s="7">
         <f t="shared" si="11"/>
-        <v>0.87317892732758973</v>
+        <v>0.87318514335036523</v>
       </c>
       <c r="AG17" s="13">
         <v>411675</v>
@@ -2871,14 +2871,14 @@
       </c>
       <c r="AI17" s="6">
         <f t="shared" si="12"/>
-        <v>236495</v>
+        <v>236497</v>
       </c>
       <c r="AJ17" s="14">
-        <v>303063</v>
+        <v>303065</v>
       </c>
       <c r="AK17" s="7">
         <f t="shared" si="13"/>
-        <v>0.7361705228639096</v>
+        <v>0.73617538106516067</v>
       </c>
       <c r="AL17" s="13">
         <v>391787</v>
@@ -2888,14 +2888,14 @@
       </c>
       <c r="AN17" s="6">
         <f t="shared" si="14"/>
-        <v>224650</v>
+        <v>224656</v>
       </c>
       <c r="AO17" s="14">
-        <v>307337</v>
+        <v>307343</v>
       </c>
       <c r="AP17" s="7">
         <f t="shared" si="15"/>
-        <v>0.78444920326606038</v>
+        <v>0.78446451770987802</v>
       </c>
       <c r="AQ17" s="13">
         <v>1127354</v>
@@ -2905,14 +2905,14 @@
       </c>
       <c r="AS17" s="6">
         <f t="shared" si="16"/>
-        <v>381260</v>
+        <v>381270</v>
       </c>
       <c r="AT17" s="15">
-        <v>1005683</v>
+        <v>1005693</v>
       </c>
       <c r="AU17" s="7">
         <f t="shared" si="17"/>
-        <v>0.8920738295158398</v>
+        <v>0.89208269984405963</v>
       </c>
       <c r="AV17" s="13">
         <v>386848</v>
@@ -2922,14 +2922,14 @@
       </c>
       <c r="AX17" s="6">
         <f t="shared" si="18"/>
-        <v>170735</v>
+        <v>170741</v>
       </c>
       <c r="AY17" s="14">
-        <v>308725</v>
+        <v>308731</v>
       </c>
       <c r="AZ17" s="7">
         <f t="shared" si="19"/>
-        <v>0.79805246505087268</v>
+        <v>0.79806797501861193</v>
       </c>
       <c r="BA17" s="13">
         <v>379844</v>
@@ -2939,14 +2939,14 @@
       </c>
       <c r="BC17" s="6">
         <f t="shared" si="20"/>
-        <v>93333</v>
+        <v>93339</v>
       </c>
       <c r="BD17" s="14">
-        <v>308639</v>
+        <v>308645</v>
       </c>
       <c r="BE17" s="7">
         <f t="shared" si="21"/>
-        <v>0.81254146439064456</v>
+        <v>0.81255726034898534</v>
       </c>
       <c r="BF17" s="13">
         <v>1155076</v>
@@ -2956,14 +2956,14 @@
       </c>
       <c r="BH17" s="6">
         <f t="shared" si="22"/>
-        <v>370522</v>
+        <v>370536</v>
       </c>
       <c r="BI17" s="15">
-        <v>1003155</v>
+        <v>1003169</v>
       </c>
       <c r="BJ17" s="7">
         <f t="shared" si="23"/>
-        <v>0.86847532110441217</v>
+        <v>0.86848744151899959</v>
       </c>
     </row>
     <row r="18" spans="1:62" x14ac:dyDescent="0.3">
@@ -2981,14 +2981,14 @@
       </c>
       <c r="E18" s="6">
         <f t="shared" si="0"/>
-        <v>67980</v>
+        <v>67981</v>
       </c>
       <c r="F18" s="14">
-        <v>79213</v>
+        <v>79214</v>
       </c>
       <c r="G18" s="7">
         <f t="shared" si="1"/>
-        <v>0.46235517291697065</v>
+        <v>0.46236100977674011</v>
       </c>
       <c r="H18" s="13">
         <v>162671</v>
@@ -3015,14 +3015,14 @@
       </c>
       <c r="O18" s="6">
         <f t="shared" si="4"/>
-        <v>182282</v>
+        <v>182284</v>
       </c>
       <c r="P18" s="15">
-        <v>250836</v>
+        <v>250838</v>
       </c>
       <c r="Q18" s="7">
         <f t="shared" si="5"/>
-        <v>0.80023990990617355</v>
+        <v>0.80024629048878448</v>
       </c>
       <c r="R18" s="13">
         <v>151876</v>
@@ -3066,14 +3066,14 @@
       </c>
       <c r="AD18" s="6">
         <f t="shared" si="10"/>
-        <v>208683</v>
+        <v>208685</v>
       </c>
       <c r="AE18" s="15">
-        <v>261861</v>
+        <v>261863</v>
       </c>
       <c r="AF18" s="7">
         <f t="shared" si="11"/>
-        <v>0.80430068555421774</v>
+        <v>0.80430682851315827</v>
       </c>
       <c r="AG18" s="13">
         <v>146984</v>
@@ -3100,14 +3100,14 @@
       </c>
       <c r="AN18" s="6">
         <f t="shared" si="14"/>
-        <v>72162</v>
+        <v>72163</v>
       </c>
       <c r="AO18" s="14">
-        <v>85366</v>
+        <v>85367</v>
       </c>
       <c r="AP18" s="7">
         <f t="shared" si="15"/>
-        <v>0.59336748524679039</v>
+        <v>0.59337443611113039</v>
       </c>
       <c r="AQ18" s="13">
         <v>332886</v>
@@ -3117,14 +3117,14 @@
       </c>
       <c r="AS18" s="6">
         <f t="shared" si="16"/>
-        <v>124397</v>
+        <v>124400</v>
       </c>
       <c r="AT18" s="15">
-        <v>271042</v>
+        <v>271045</v>
       </c>
       <c r="AU18" s="7">
         <f t="shared" si="17"/>
-        <v>0.81421868147053345</v>
+        <v>0.81422769356476388</v>
       </c>
       <c r="AV18" s="13">
         <v>133090</v>
@@ -3134,14 +3134,14 @@
       </c>
       <c r="AX18" s="6">
         <f t="shared" si="18"/>
-        <v>60378</v>
+        <v>60380</v>
       </c>
       <c r="AY18" s="14">
-        <v>88557</v>
+        <v>88559</v>
       </c>
       <c r="AZ18" s="7">
         <f t="shared" si="19"/>
-        <v>0.66539184010819741</v>
+        <v>0.66540686753324818</v>
       </c>
       <c r="BA18" s="13">
         <v>108549</v>
@@ -3151,14 +3151,14 @@
       </c>
       <c r="BC18" s="6">
         <f t="shared" si="20"/>
-        <v>35929</v>
+        <v>35930</v>
       </c>
       <c r="BD18" s="14">
-        <v>86216</v>
+        <v>86217</v>
       </c>
       <c r="BE18" s="7">
         <f t="shared" si="21"/>
-        <v>0.79425881399183784</v>
+        <v>0.7942680264212475</v>
       </c>
       <c r="BF18" s="13">
         <v>320339</v>
@@ -3168,14 +3168,14 @@
       </c>
       <c r="BH18" s="6">
         <f t="shared" si="22"/>
-        <v>125691</v>
+        <v>125697</v>
       </c>
       <c r="BI18" s="15">
-        <v>270243</v>
+        <v>270249</v>
       </c>
       <c r="BJ18" s="7">
         <f t="shared" si="23"/>
-        <v>0.84361566964996459</v>
+        <v>0.84363439980770372</v>
       </c>
     </row>
     <row r="19" spans="1:62" x14ac:dyDescent="0.3">
@@ -3439,14 +3439,14 @@
       </c>
       <c r="O20" s="6">
         <f t="shared" si="4"/>
-        <v>6284</v>
+        <v>6285</v>
       </c>
       <c r="P20" s="15">
-        <v>7674</v>
+        <v>7675</v>
       </c>
       <c r="Q20" s="7">
         <f t="shared" si="5"/>
-        <v>0.68868347841694333</v>
+        <v>0.6887732208561429</v>
       </c>
       <c r="R20" s="13">
         <v>7639</v>
@@ -3490,14 +3490,14 @@
       </c>
       <c r="AD20" s="6">
         <f t="shared" si="10"/>
-        <v>6802</v>
+        <v>6803</v>
       </c>
       <c r="AE20" s="15">
-        <v>8151</v>
+        <v>8152</v>
       </c>
       <c r="AF20" s="7">
         <f t="shared" si="11"/>
-        <v>0.68152173913043479</v>
+        <v>0.68160535117056853</v>
       </c>
       <c r="AG20" s="13">
         <v>7480</v>
@@ -3541,14 +3541,14 @@
       </c>
       <c r="AS20" s="6">
         <f t="shared" si="16"/>
-        <v>5064</v>
+        <v>5065</v>
       </c>
       <c r="AT20" s="15">
-        <v>8491</v>
+        <v>8492</v>
       </c>
       <c r="AU20" s="7">
         <f t="shared" si="17"/>
-        <v>0.67846584099081098</v>
+        <v>0.67854574510587295</v>
       </c>
       <c r="AV20" s="13">
         <v>7275</v>
@@ -3592,14 +3592,14 @@
       </c>
       <c r="BH20" s="6">
         <f t="shared" si="22"/>
-        <v>4690</v>
+        <v>4691</v>
       </c>
       <c r="BI20" s="15">
-        <v>8671</v>
+        <v>8672</v>
       </c>
       <c r="BJ20" s="7">
         <f t="shared" si="23"/>
-        <v>0.69157760408358593</v>
+        <v>0.69165736162067315</v>
       </c>
     </row>
     <row r="21" spans="1:62" x14ac:dyDescent="0.3">
@@ -3634,14 +3634,14 @@
       </c>
       <c r="J21" s="6">
         <f t="shared" si="2"/>
-        <v>2621</v>
+        <v>2622</v>
       </c>
       <c r="K21" s="14">
-        <v>3212</v>
+        <v>3213</v>
       </c>
       <c r="L21" s="7">
         <f t="shared" si="3"/>
-        <v>0.60330578512396693</v>
+        <v>0.60349361382419231</v>
       </c>
       <c r="M21" s="13">
         <v>6463</v>
@@ -3651,14 +3651,14 @@
       </c>
       <c r="O21" s="6">
         <f t="shared" si="4"/>
-        <v>3784</v>
+        <v>3785</v>
       </c>
       <c r="P21" s="15">
-        <v>4870</v>
+        <v>4871</v>
       </c>
       <c r="Q21" s="7">
         <f t="shared" si="5"/>
-        <v>0.7535200371344577</v>
+        <v>0.75367476404146683</v>
       </c>
       <c r="R21" s="13">
         <v>5094</v>
@@ -3668,14 +3668,14 @@
       </c>
       <c r="T21" s="6">
         <f t="shared" si="6"/>
-        <v>2796</v>
+        <v>2797</v>
       </c>
       <c r="U21" s="14">
-        <v>3317</v>
+        <v>3318</v>
       </c>
       <c r="V21" s="7">
         <f t="shared" si="7"/>
-        <v>0.65115822536317236</v>
+        <v>0.65135453474676086</v>
       </c>
       <c r="W21" s="13">
         <v>5116</v>
@@ -3685,14 +3685,14 @@
       </c>
       <c r="Y21" s="6">
         <f t="shared" si="8"/>
-        <v>2753</v>
+        <v>2754</v>
       </c>
       <c r="Z21" s="14">
-        <v>3374</v>
+        <v>3375</v>
       </c>
       <c r="AA21" s="7">
         <f t="shared" si="9"/>
-        <v>0.6594996090695856</v>
+        <v>0.65969507427677876</v>
       </c>
       <c r="AB21" s="13">
         <v>6718</v>
@@ -3702,14 +3702,14 @@
       </c>
       <c r="AD21" s="6">
         <f t="shared" si="10"/>
-        <v>4093</v>
+        <v>4095</v>
       </c>
       <c r="AE21" s="15">
-        <v>5091</v>
+        <v>5093</v>
       </c>
       <c r="AF21" s="7">
         <f t="shared" si="11"/>
-        <v>0.75781482584102411</v>
+        <v>0.75811253349211072</v>
       </c>
       <c r="AG21" s="13">
         <v>5117</v>
@@ -3719,14 +3719,14 @@
       </c>
       <c r="AI21" s="6">
         <f t="shared" si="12"/>
-        <v>2865</v>
+        <v>2866</v>
       </c>
       <c r="AJ21" s="14">
-        <v>3472</v>
+        <v>3473</v>
       </c>
       <c r="AK21" s="7">
         <f t="shared" si="13"/>
-        <v>0.67852257181942544</v>
+        <v>0.678717998827438</v>
       </c>
       <c r="AL21" s="13">
         <v>5024</v>
@@ -3736,14 +3736,14 @@
       </c>
       <c r="AN21" s="6">
         <f t="shared" si="14"/>
-        <v>2789</v>
+        <v>2790</v>
       </c>
       <c r="AO21" s="14">
-        <v>3497</v>
+        <v>3498</v>
       </c>
       <c r="AP21" s="7">
         <f t="shared" si="15"/>
-        <v>0.69605891719745228</v>
+        <v>0.69625796178343946</v>
       </c>
       <c r="AQ21" s="13">
         <v>6694</v>
@@ -3753,14 +3753,14 @@
       </c>
       <c r="AS21" s="6">
         <f t="shared" si="16"/>
-        <v>3500</v>
+        <v>3502</v>
       </c>
       <c r="AT21" s="15">
-        <v>5200</v>
+        <v>5202</v>
       </c>
       <c r="AU21" s="7">
         <f t="shared" si="17"/>
-        <v>0.7768150582611294</v>
+        <v>0.77711383328353745</v>
       </c>
       <c r="AV21" s="13">
         <v>4925</v>
@@ -3770,14 +3770,14 @@
       </c>
       <c r="AX21" s="6">
         <f t="shared" si="18"/>
-        <v>2547</v>
+        <v>2548</v>
       </c>
       <c r="AY21" s="14">
-        <v>3545</v>
+        <v>3546</v>
       </c>
       <c r="AZ21" s="7">
         <f t="shared" si="19"/>
-        <v>0.71979695431472079</v>
+        <v>0.72</v>
       </c>
       <c r="BA21" s="13">
         <v>4794</v>
@@ -3787,14 +3787,14 @@
       </c>
       <c r="BC21" s="6">
         <f t="shared" si="20"/>
-        <v>1538</v>
+        <v>1540</v>
       </c>
       <c r="BD21" s="14">
-        <v>3561</v>
+        <v>3563</v>
       </c>
       <c r="BE21" s="7">
         <f t="shared" si="21"/>
-        <v>0.7428035043804756</v>
+        <v>0.74322069253233203</v>
       </c>
       <c r="BF21" s="13">
         <v>6784</v>
@@ -3804,14 +3804,14 @@
       </c>
       <c r="BH21" s="6">
         <f t="shared" si="22"/>
-        <v>2185</v>
+        <v>2188</v>
       </c>
       <c r="BI21" s="15">
-        <v>5236</v>
+        <v>5239</v>
       </c>
       <c r="BJ21" s="7">
         <f t="shared" si="23"/>
-        <v>0.77181603773584906</v>
+        <v>0.77225825471698117</v>
       </c>
     </row>
     <row r="22" spans="1:62" x14ac:dyDescent="0.3">
@@ -3863,14 +3863,14 @@
       </c>
       <c r="O22" s="6">
         <f t="shared" si="4"/>
-        <v>5555</v>
+        <v>5556</v>
       </c>
       <c r="P22" s="15">
-        <v>6790</v>
+        <v>6791</v>
       </c>
       <c r="Q22" s="7">
         <f t="shared" si="5"/>
-        <v>0.62060140754958415</v>
+        <v>0.62069280687322914</v>
       </c>
       <c r="R22" s="13">
         <v>8347</v>
@@ -4270,14 +4270,14 @@
       </c>
       <c r="J24" s="6">
         <f t="shared" si="2"/>
-        <v>5271</v>
+        <v>5272</v>
       </c>
       <c r="K24" s="14">
-        <v>6842</v>
+        <v>6843</v>
       </c>
       <c r="L24" s="7">
         <f t="shared" si="3"/>
-        <v>0.52622673434856171</v>
+        <v>0.5263036455929857</v>
       </c>
       <c r="M24" s="13">
         <v>24026</v>
@@ -4465,14 +4465,14 @@
       </c>
       <c r="E25" s="6">
         <f t="shared" si="0"/>
-        <v>6505</v>
+        <v>6507</v>
       </c>
       <c r="F25" s="14">
-        <v>7896</v>
+        <v>7898</v>
       </c>
       <c r="G25" s="7">
         <f t="shared" si="1"/>
-        <v>0.47871953437613679</v>
+        <v>0.47884079059051776</v>
       </c>
       <c r="H25" s="13">
         <v>16584</v>
@@ -4482,14 +4482,14 @@
       </c>
       <c r="J25" s="6">
         <f t="shared" si="2"/>
-        <v>6404</v>
+        <v>6406</v>
       </c>
       <c r="K25" s="14">
-        <v>7999</v>
+        <v>8001</v>
       </c>
       <c r="L25" s="7">
         <f t="shared" si="3"/>
-        <v>0.48233236854799805</v>
+        <v>0.48245296671490595</v>
       </c>
       <c r="M25" s="13">
         <v>24878</v>
@@ -4499,14 +4499,14 @@
       </c>
       <c r="O25" s="6">
         <f t="shared" si="4"/>
-        <v>11570</v>
+        <v>11574</v>
       </c>
       <c r="P25" s="15">
-        <v>17309</v>
+        <v>17313</v>
       </c>
       <c r="Q25" s="7">
         <f t="shared" si="5"/>
-        <v>0.69575528579467805</v>
+        <v>0.69591607042366754</v>
       </c>
       <c r="R25" s="13">
         <v>16556</v>
@@ -4516,14 +4516,14 @@
       </c>
       <c r="T25" s="6">
         <f t="shared" si="6"/>
-        <v>6768</v>
+        <v>6771</v>
       </c>
       <c r="U25" s="14">
-        <v>8313</v>
+        <v>8316</v>
       </c>
       <c r="V25" s="7">
         <f t="shared" si="7"/>
-        <v>0.50211403720705483</v>
+        <v>0.50229524039623097</v>
       </c>
       <c r="W25" s="13">
         <v>16201</v>
@@ -4533,14 +4533,14 @@
       </c>
       <c r="Y25" s="6">
         <f t="shared" si="8"/>
-        <v>6523</v>
+        <v>6526</v>
       </c>
       <c r="Z25" s="14">
-        <v>8352</v>
+        <v>8355</v>
       </c>
       <c r="AA25" s="7">
         <f t="shared" si="9"/>
-        <v>0.5155237331028949</v>
+        <v>0.5157089068576014</v>
       </c>
       <c r="AB25" s="13">
         <v>26140</v>
@@ -4550,14 +4550,14 @@
       </c>
       <c r="AD25" s="6">
         <f t="shared" si="10"/>
-        <v>12081</v>
+        <v>12086</v>
       </c>
       <c r="AE25" s="15">
-        <v>18074</v>
+        <v>18079</v>
       </c>
       <c r="AF25" s="7">
         <f t="shared" si="11"/>
-        <v>0.69143075745983162</v>
+        <v>0.69162203519510324</v>
       </c>
       <c r="AG25" s="13">
         <v>16090</v>
@@ -4567,14 +4567,14 @@
       </c>
       <c r="AI25" s="6">
         <f t="shared" si="12"/>
-        <v>6880</v>
+        <v>6883</v>
       </c>
       <c r="AJ25" s="14">
-        <v>8404</v>
+        <v>8407</v>
       </c>
       <c r="AK25" s="7">
         <f t="shared" si="13"/>
-        <v>0.52231199502796766</v>
+        <v>0.5224984462399006</v>
       </c>
       <c r="AL25" s="13">
         <v>15981</v>
@@ -4584,14 +4584,14 @@
       </c>
       <c r="AN25" s="6">
         <f t="shared" si="14"/>
-        <v>6623</v>
+        <v>6626</v>
       </c>
       <c r="AO25" s="14">
-        <v>8370</v>
+        <v>8373</v>
       </c>
       <c r="AP25" s="7">
         <f t="shared" si="15"/>
-        <v>0.52374694950253431</v>
+        <v>0.52393467242350289</v>
       </c>
       <c r="AQ25" s="13">
         <v>26428</v>
@@ -4601,14 +4601,14 @@
       </c>
       <c r="AS25" s="6">
         <f t="shared" si="16"/>
-        <v>10622</v>
+        <v>10628</v>
       </c>
       <c r="AT25" s="15">
-        <v>17978</v>
+        <v>17984</v>
       </c>
       <c r="AU25" s="7">
         <f t="shared" si="17"/>
-        <v>0.68026335704555774</v>
+        <v>0.68049038898138337</v>
       </c>
       <c r="AV25" s="13">
         <v>15911</v>
@@ -4618,14 +4618,14 @@
       </c>
       <c r="AX25" s="6">
         <f t="shared" si="18"/>
-        <v>6032</v>
+        <v>6035</v>
       </c>
       <c r="AY25" s="14">
-        <v>8509</v>
+        <v>8512</v>
       </c>
       <c r="AZ25" s="7">
         <f t="shared" si="19"/>
-        <v>0.53478725410093642</v>
+        <v>0.53497580290365154</v>
       </c>
       <c r="BA25" s="13">
         <v>15896</v>
@@ -4635,14 +4635,14 @@
       </c>
       <c r="BC25" s="6">
         <f t="shared" si="20"/>
-        <v>3836</v>
+        <v>3839</v>
       </c>
       <c r="BD25" s="14">
-        <v>8383</v>
+        <v>8386</v>
       </c>
       <c r="BE25" s="7">
         <f t="shared" si="21"/>
-        <v>0.52736537493709112</v>
+        <v>0.52755410166079519</v>
       </c>
       <c r="BF25" s="13">
         <v>26706</v>
@@ -4652,14 +4652,14 @@
       </c>
       <c r="BH25" s="6">
         <f t="shared" si="22"/>
-        <v>7376</v>
+        <v>7381</v>
       </c>
       <c r="BI25" s="15">
-        <v>17603</v>
+        <v>17608</v>
       </c>
       <c r="BJ25" s="7">
         <f t="shared" si="23"/>
-        <v>0.65914026810454585</v>
+        <v>0.65932749194937468</v>
       </c>
     </row>
     <row r="26" spans="1:62" x14ac:dyDescent="0.3">
@@ -4677,14 +4677,14 @@
       </c>
       <c r="E26" s="6">
         <f t="shared" si="0"/>
-        <v>40078</v>
+        <v>40079</v>
       </c>
       <c r="F26" s="14">
-        <v>48339</v>
+        <v>48340</v>
       </c>
       <c r="G26" s="7">
         <f t="shared" si="1"/>
-        <v>0.43152886143298397</v>
+        <v>0.43153778856969416</v>
       </c>
       <c r="H26" s="13">
         <v>109409</v>
@@ -4694,14 +4694,14 @@
       </c>
       <c r="J26" s="6">
         <f t="shared" si="2"/>
-        <v>39828</v>
+        <v>39829</v>
       </c>
       <c r="K26" s="14">
-        <v>48657</v>
+        <v>48658</v>
       </c>
       <c r="L26" s="7">
         <f t="shared" si="3"/>
-        <v>0.44472575382281165</v>
+        <v>0.44473489383871528</v>
       </c>
       <c r="M26" s="13">
         <v>161175</v>
@@ -4711,14 +4711,14 @@
       </c>
       <c r="O26" s="6">
         <f t="shared" si="4"/>
-        <v>84814</v>
+        <v>84818</v>
       </c>
       <c r="P26" s="15">
-        <v>115382</v>
+        <v>115386</v>
       </c>
       <c r="Q26" s="7">
         <f t="shared" si="5"/>
-        <v>0.71588025438188307</v>
+        <v>0.71590507212657051</v>
       </c>
       <c r="R26" s="13">
         <v>103195</v>
@@ -4728,14 +4728,14 @@
       </c>
       <c r="T26" s="6">
         <f t="shared" si="6"/>
-        <v>40748</v>
+        <v>40749</v>
       </c>
       <c r="U26" s="14">
-        <v>49533</v>
+        <v>49534</v>
       </c>
       <c r="V26" s="7">
         <f t="shared" si="7"/>
-        <v>0.47999418576481417</v>
+        <v>0.48000387615679052</v>
       </c>
       <c r="W26" s="13">
         <v>101010</v>
@@ -4745,14 +4745,14 @@
       </c>
       <c r="Y26" s="6">
         <f t="shared" si="8"/>
-        <v>40868</v>
+        <v>40869</v>
       </c>
       <c r="Z26" s="14">
-        <v>49980</v>
+        <v>49981</v>
       </c>
       <c r="AA26" s="7">
         <f t="shared" si="9"/>
-        <v>0.49480249480249483</v>
+        <v>0.49481239481239481</v>
       </c>
       <c r="AB26" s="13">
         <v>167059</v>
@@ -4762,14 +4762,14 @@
       </c>
       <c r="AD26" s="6">
         <f t="shared" si="10"/>
-        <v>96132</v>
+        <v>96136</v>
       </c>
       <c r="AE26" s="15">
-        <v>119658</v>
+        <v>119662</v>
       </c>
       <c r="AF26" s="7">
         <f t="shared" si="11"/>
-        <v>0.71626191944163442</v>
+        <v>0.71628586307831366</v>
       </c>
       <c r="AG26" s="13">
         <v>98900</v>
@@ -4779,14 +4779,14 @@
       </c>
       <c r="AI26" s="6">
         <f t="shared" si="12"/>
-        <v>42352</v>
+        <v>42354</v>
       </c>
       <c r="AJ26" s="14">
-        <v>50960</v>
+        <v>50962</v>
       </c>
       <c r="AK26" s="7">
         <f t="shared" si="13"/>
-        <v>0.51526794742163806</v>
+        <v>0.51528816986855408</v>
       </c>
       <c r="AL26" s="13">
         <v>94250</v>
@@ -4796,14 +4796,14 @@
       </c>
       <c r="AN26" s="6">
         <f t="shared" si="14"/>
-        <v>43784</v>
+        <v>43786</v>
       </c>
       <c r="AO26" s="14">
-        <v>53049</v>
+        <v>53051</v>
       </c>
       <c r="AP26" s="7">
         <f t="shared" si="15"/>
-        <v>0.56285411140583552</v>
+        <v>0.5628753315649867</v>
       </c>
       <c r="AQ26" s="13">
         <v>146205</v>
@@ -4813,14 +4813,14 @@
       </c>
       <c r="AS26" s="6">
         <f t="shared" si="16"/>
-        <v>62915</v>
+        <v>62920</v>
       </c>
       <c r="AT26" s="15">
-        <v>120753</v>
+        <v>120758</v>
       </c>
       <c r="AU26" s="7">
         <f t="shared" si="17"/>
-        <v>0.8259156663588797</v>
+        <v>0.82594986491570055</v>
       </c>
       <c r="AV26" s="13">
         <v>71728</v>
@@ -4830,14 +4830,14 @@
       </c>
       <c r="AX26" s="6">
         <f t="shared" si="18"/>
-        <v>33620</v>
+        <v>33622</v>
       </c>
       <c r="AY26" s="14">
-        <v>51513</v>
+        <v>51515</v>
       </c>
       <c r="AZ26" s="7">
         <f t="shared" si="19"/>
-        <v>0.71817142538478695</v>
+        <v>0.71819930849877311</v>
       </c>
       <c r="BA26" s="13">
         <v>70808</v>
@@ -4847,14 +4847,14 @@
       </c>
       <c r="BC26" s="6">
         <f t="shared" si="20"/>
-        <v>21393</v>
+        <v>21396</v>
       </c>
       <c r="BD26" s="14">
-        <v>51517</v>
+        <v>51520</v>
       </c>
       <c r="BE26" s="7">
         <f t="shared" si="21"/>
-        <v>0.7275590328776409</v>
+        <v>0.72760140097164161</v>
       </c>
       <c r="BF26" s="13">
         <v>145908</v>
@@ -4864,14 +4864,14 @@
       </c>
       <c r="BH26" s="6">
         <f t="shared" si="22"/>
-        <v>57940</v>
+        <v>57950</v>
       </c>
       <c r="BI26" s="15">
-        <v>119795</v>
+        <v>119805</v>
       </c>
       <c r="BJ26" s="7">
         <f t="shared" si="23"/>
-        <v>0.8210310606683664</v>
+        <v>0.82109959700633273</v>
       </c>
     </row>
     <row r="27" spans="1:62" x14ac:dyDescent="0.3">
@@ -4889,14 +4889,14 @@
       </c>
       <c r="E27" s="6">
         <f t="shared" si="0"/>
-        <v>125129</v>
+        <v>125131</v>
       </c>
       <c r="F27" s="14">
-        <v>173520</v>
+        <v>173522</v>
       </c>
       <c r="G27" s="7">
         <f t="shared" si="1"/>
-        <v>0.5684185699123393</v>
+        <v>0.56842512153255498</v>
       </c>
       <c r="H27" s="13">
         <v>294634</v>
@@ -4923,14 +4923,14 @@
       </c>
       <c r="O27" s="6">
         <f t="shared" si="4"/>
-        <v>303565</v>
+        <v>303566</v>
       </c>
       <c r="P27" s="15">
-        <v>504382</v>
+        <v>504383</v>
       </c>
       <c r="Q27" s="7">
         <f t="shared" si="5"/>
-        <v>0.84995214214457115</v>
+        <v>0.84995382728032576</v>
       </c>
       <c r="R27" s="13">
         <v>274036</v>
@@ -4974,14 +4974,14 @@
       </c>
       <c r="AD27" s="6">
         <f t="shared" si="10"/>
-        <v>355302</v>
+        <v>355304</v>
       </c>
       <c r="AE27" s="15">
-        <v>515676</v>
+        <v>515678</v>
       </c>
       <c r="AF27" s="7">
         <f t="shared" si="11"/>
-        <v>0.84868174187814749</v>
+        <v>0.84868503340903856</v>
       </c>
       <c r="AG27" s="13">
         <v>264148</v>
@@ -4991,14 +4991,14 @@
       </c>
       <c r="AI27" s="6">
         <f t="shared" si="12"/>
-        <v>131915</v>
+        <v>131916</v>
       </c>
       <c r="AJ27" s="14">
-        <v>178850</v>
+        <v>178851</v>
       </c>
       <c r="AK27" s="7">
         <f t="shared" si="13"/>
-        <v>0.67708254463406881</v>
+        <v>0.67708633039053867</v>
       </c>
       <c r="AL27" s="13">
         <v>259704</v>
@@ -5025,14 +5025,14 @@
       </c>
       <c r="AS27" s="6">
         <f t="shared" si="16"/>
-        <v>208694</v>
+        <v>208699</v>
       </c>
       <c r="AT27" s="15">
-        <v>521676</v>
+        <v>521681</v>
       </c>
       <c r="AU27" s="7">
         <f t="shared" si="17"/>
-        <v>0.85332923306430775</v>
+        <v>0.85333741179241729</v>
       </c>
       <c r="AV27" s="13">
         <v>246718</v>
@@ -5042,14 +5042,14 @@
       </c>
       <c r="AX27" s="6">
         <f t="shared" si="18"/>
-        <v>93712</v>
+        <v>93713</v>
       </c>
       <c r="AY27" s="14">
-        <v>181459</v>
+        <v>181460</v>
       </c>
       <c r="AZ27" s="7">
         <f t="shared" si="19"/>
-        <v>0.73549153284316504</v>
+        <v>0.73549558605371312</v>
       </c>
       <c r="BA27" s="13">
         <v>240337</v>
@@ -5076,14 +5076,14 @@
       </c>
       <c r="BH27" s="6">
         <f t="shared" si="22"/>
-        <v>179893</v>
+        <v>179899</v>
       </c>
       <c r="BI27" s="15">
-        <v>515492</v>
+        <v>515498</v>
       </c>
       <c r="BJ27" s="7">
         <f t="shared" si="23"/>
-        <v>0.84282362558757407</v>
+        <v>0.84283343552013079</v>
       </c>
     </row>
     <row r="28" spans="1:62" x14ac:dyDescent="0.3">
@@ -5288,14 +5288,14 @@
       </c>
       <c r="BH28" s="6">
         <f t="shared" si="22"/>
-        <v>48851</v>
+        <v>48852</v>
       </c>
       <c r="BI28" s="15">
-        <v>128167</v>
+        <v>128168</v>
       </c>
       <c r="BJ28" s="7">
         <f t="shared" si="23"/>
-        <v>0.89277032063025474</v>
+        <v>0.89277728631034892</v>
       </c>
     </row>
     <row r="29" spans="1:62" x14ac:dyDescent="0.3">
@@ -5313,14 +5313,14 @@
       </c>
       <c r="E29" s="6">
         <f t="shared" si="0"/>
-        <v>57268</v>
+        <v>57272</v>
       </c>
       <c r="F29" s="14">
-        <v>66581</v>
+        <v>66585</v>
       </c>
       <c r="G29" s="7">
         <f t="shared" si="1"/>
-        <v>0.41047186910471867</v>
+        <v>0.41049652910496531</v>
       </c>
       <c r="H29" s="13">
         <v>149172</v>
@@ -5330,14 +5330,14 @@
       </c>
       <c r="J29" s="6">
         <f t="shared" si="2"/>
-        <v>53949</v>
+        <v>53953</v>
       </c>
       <c r="K29" s="14">
-        <v>66890</v>
+        <v>66894</v>
       </c>
       <c r="L29" s="7">
         <f t="shared" si="3"/>
-        <v>0.44840854852117018</v>
+        <v>0.44843536320489102</v>
       </c>
       <c r="M29" s="13">
         <v>219769</v>
@@ -5347,14 +5347,14 @@
       </c>
       <c r="O29" s="6">
         <f t="shared" si="4"/>
-        <v>127835</v>
+        <v>127844</v>
       </c>
       <c r="P29" s="15">
-        <v>184051</v>
+        <v>184060</v>
       </c>
       <c r="Q29" s="7">
         <f t="shared" si="5"/>
-        <v>0.83747480308869771</v>
+        <v>0.83751575517930188</v>
       </c>
       <c r="R29" s="13">
         <v>104974</v>
@@ -5364,14 +5364,14 @@
       </c>
       <c r="T29" s="6">
         <f t="shared" si="6"/>
-        <v>54560</v>
+        <v>54563</v>
       </c>
       <c r="U29" s="14">
-        <v>68044</v>
+        <v>68047</v>
       </c>
       <c r="V29" s="7">
         <f t="shared" si="7"/>
-        <v>0.64819860155848119</v>
+        <v>0.64822718006363478</v>
       </c>
       <c r="W29" s="13">
         <v>99843</v>
@@ -5381,14 +5381,14 @@
       </c>
       <c r="Y29" s="6">
         <f t="shared" si="8"/>
-        <v>55011</v>
+        <v>55014</v>
       </c>
       <c r="Z29" s="14">
-        <v>68622</v>
+        <v>68625</v>
       </c>
       <c r="AA29" s="7">
         <f t="shared" si="9"/>
-        <v>0.68729905952345183</v>
+        <v>0.68732910669751512</v>
       </c>
       <c r="AB29" s="13">
         <v>220841</v>
@@ -5398,14 +5398,14 @@
       </c>
       <c r="AD29" s="6">
         <f t="shared" si="10"/>
-        <v>139528</v>
+        <v>139535</v>
       </c>
       <c r="AE29" s="15">
-        <v>190124</v>
+        <v>190131</v>
       </c>
       <c r="AF29" s="7">
         <f t="shared" si="11"/>
-        <v>0.86090897976372138</v>
+        <v>0.86094067677650432</v>
       </c>
       <c r="AG29" s="13">
         <v>96497</v>
@@ -5415,14 +5415,14 @@
       </c>
       <c r="AI29" s="6">
         <f t="shared" si="12"/>
-        <v>56617</v>
+        <v>56623</v>
       </c>
       <c r="AJ29" s="14">
-        <v>70150</v>
+        <v>70156</v>
       </c>
       <c r="AK29" s="7">
         <f t="shared" si="13"/>
-        <v>0.72696560514834663</v>
+        <v>0.72702778324714756</v>
       </c>
       <c r="AL29" s="13">
         <v>92661</v>
@@ -5432,14 +5432,14 @@
       </c>
       <c r="AN29" s="6">
         <f t="shared" si="14"/>
-        <v>55021</v>
+        <v>55024</v>
       </c>
       <c r="AO29" s="14">
-        <v>71189</v>
+        <v>71192</v>
       </c>
       <c r="AP29" s="7">
         <f t="shared" si="15"/>
-        <v>0.76827359946471552</v>
+        <v>0.76830597554526714</v>
       </c>
       <c r="AQ29" s="13">
         <v>222288</v>
@@ -5449,14 +5449,14 @@
       </c>
       <c r="AS29" s="6">
         <f t="shared" si="16"/>
-        <v>93472</v>
+        <v>93480</v>
       </c>
       <c r="AT29" s="15">
-        <v>195622</v>
+        <v>195630</v>
       </c>
       <c r="AU29" s="7">
         <f t="shared" si="17"/>
-        <v>0.88003850860145394</v>
+        <v>0.88007449794860726</v>
       </c>
       <c r="AV29" s="13">
         <v>91315</v>
@@ -5466,14 +5466,14 @@
       </c>
       <c r="AX29" s="6">
         <f t="shared" si="18"/>
-        <v>46321</v>
+        <v>46324</v>
       </c>
       <c r="AY29" s="14">
-        <v>71958</v>
+        <v>71961</v>
       </c>
       <c r="AZ29" s="7">
         <f t="shared" si="19"/>
-        <v>0.78801949296391616</v>
+        <v>0.78805234627388709</v>
       </c>
       <c r="BA29" s="13">
         <v>88358</v>
@@ -5483,14 +5483,14 @@
       </c>
       <c r="BC29" s="6">
         <f t="shared" si="20"/>
-        <v>26364</v>
+        <v>26367</v>
       </c>
       <c r="BD29" s="14">
-        <v>72195</v>
+        <v>72198</v>
       </c>
       <c r="BE29" s="7">
         <f t="shared" si="21"/>
-        <v>0.81707372280947965</v>
+        <v>0.8171076755924761</v>
       </c>
       <c r="BF29" s="13">
         <v>223069</v>
@@ -5500,14 +5500,14 @@
       </c>
       <c r="BH29" s="6">
         <f t="shared" si="22"/>
-        <v>74073</v>
+        <v>74085</v>
       </c>
       <c r="BI29" s="15">
-        <v>193563</v>
+        <v>193575</v>
       </c>
       <c r="BJ29" s="7">
         <f t="shared" si="23"/>
-        <v>0.86772702616679143</v>
+        <v>0.86778082118089017</v>
       </c>
     </row>
     <row r="30" spans="1:62" x14ac:dyDescent="0.3">
@@ -5525,14 +5525,14 @@
       </c>
       <c r="E30" s="6">
         <f t="shared" si="0"/>
-        <v>29499</v>
+        <v>29502</v>
       </c>
       <c r="F30" s="14">
-        <v>37486</v>
+        <v>37489</v>
       </c>
       <c r="G30" s="7">
         <f t="shared" si="1"/>
-        <v>0.59078659122787658</v>
+        <v>0.59083387180659086</v>
       </c>
       <c r="H30" s="13">
         <v>60187</v>
@@ -5542,14 +5542,14 @@
       </c>
       <c r="J30" s="6">
         <f t="shared" si="2"/>
-        <v>29149</v>
+        <v>29153</v>
       </c>
       <c r="K30" s="14">
-        <v>37674</v>
+        <v>37678</v>
       </c>
       <c r="L30" s="7">
         <f t="shared" si="3"/>
-        <v>0.6259491252263778</v>
+        <v>0.62601558476082875</v>
       </c>
       <c r="M30" s="13">
         <v>104773</v>
@@ -5559,14 +5559,14 @@
       </c>
       <c r="O30" s="6">
         <f t="shared" si="4"/>
-        <v>65834</v>
+        <v>65841</v>
       </c>
       <c r="P30" s="15">
-        <v>93516</v>
+        <v>93523</v>
       </c>
       <c r="Q30" s="7">
         <f t="shared" si="5"/>
-        <v>0.89255819724547358</v>
+        <v>0.89262500835138825</v>
       </c>
       <c r="R30" s="13">
         <v>53849</v>
@@ -5576,14 +5576,14 @@
       </c>
       <c r="T30" s="6">
         <f t="shared" si="6"/>
-        <v>30046</v>
+        <v>30050</v>
       </c>
       <c r="U30" s="14">
-        <v>38127</v>
+        <v>38131</v>
       </c>
       <c r="V30" s="7">
         <f t="shared" si="7"/>
-        <v>0.70803543241285816</v>
+        <v>0.70810971420082081</v>
       </c>
       <c r="W30" s="13">
         <v>52544</v>
@@ -5593,14 +5593,14 @@
       </c>
       <c r="Y30" s="6">
         <f t="shared" si="8"/>
-        <v>29901</v>
+        <v>29905</v>
       </c>
       <c r="Z30" s="14">
-        <v>38350</v>
+        <v>38354</v>
       </c>
       <c r="AA30" s="7">
         <f t="shared" si="9"/>
-        <v>0.72986449451887947</v>
+        <v>0.72994062119366621</v>
       </c>
       <c r="AB30" s="13">
         <v>107458</v>
@@ -5610,14 +5610,14 @@
       </c>
       <c r="AD30" s="6">
         <f t="shared" si="10"/>
-        <v>74164</v>
+        <v>74170</v>
       </c>
       <c r="AE30" s="15">
-        <v>95860</v>
+        <v>95866</v>
       </c>
       <c r="AF30" s="7">
         <f t="shared" si="11"/>
-        <v>0.89206945969588114</v>
+        <v>0.89212529546427444</v>
       </c>
       <c r="AG30" s="13">
         <v>51279</v>
@@ -5627,14 +5627,14 @@
       </c>
       <c r="AI30" s="6">
         <f t="shared" si="12"/>
-        <v>31062</v>
+        <v>31066</v>
       </c>
       <c r="AJ30" s="14">
-        <v>38898</v>
+        <v>38902</v>
       </c>
       <c r="AK30" s="7">
         <f t="shared" si="13"/>
-        <v>0.75855613408997835</v>
+        <v>0.75863413873125451</v>
       </c>
       <c r="AL30" s="13">
         <v>48984</v>
@@ -5644,14 +5644,14 @@
       </c>
       <c r="AN30" s="6">
         <f t="shared" si="14"/>
-        <v>28865</v>
+        <v>28869</v>
       </c>
       <c r="AO30" s="14">
-        <v>39184</v>
+        <v>39188</v>
       </c>
       <c r="AP30" s="7">
         <f t="shared" si="15"/>
-        <v>0.79993467254613748</v>
+        <v>0.80001633186346566</v>
       </c>
       <c r="AQ30" s="13">
         <v>105112</v>
@@ -5661,14 +5661,14 @@
       </c>
       <c r="AS30" s="6">
         <f t="shared" si="16"/>
-        <v>41211</v>
+        <v>41215</v>
       </c>
       <c r="AT30" s="15">
-        <v>97355</v>
+        <v>97359</v>
       </c>
       <c r="AU30" s="7">
         <f t="shared" si="17"/>
-        <v>0.92620252682852577</v>
+        <v>0.9262405814749981</v>
       </c>
       <c r="AV30" s="13">
         <v>46049</v>
@@ -5678,14 +5678,14 @@
       </c>
       <c r="AX30" s="6">
         <f t="shared" si="18"/>
-        <v>21818</v>
+        <v>21822</v>
       </c>
       <c r="AY30" s="14">
-        <v>39044</v>
+        <v>39048</v>
       </c>
       <c r="AZ30" s="7">
         <f t="shared" si="19"/>
-        <v>0.84787943277812761</v>
+        <v>0.84796629677083102</v>
       </c>
       <c r="BA30" s="13">
         <v>45889</v>
@@ -5695,14 +5695,14 @@
       </c>
       <c r="BC30" s="6">
         <f t="shared" si="20"/>
-        <v>13561</v>
+        <v>13564</v>
       </c>
       <c r="BD30" s="14">
-        <v>38968</v>
+        <v>38971</v>
       </c>
       <c r="BE30" s="7">
         <f t="shared" si="21"/>
-        <v>0.84917954193815515</v>
+        <v>0.84924491708252525</v>
       </c>
       <c r="BF30" s="13">
         <v>107069</v>
@@ -5712,14 +5712,14 @@
       </c>
       <c r="BH30" s="6">
         <f t="shared" si="22"/>
-        <v>37214</v>
+        <v>37221</v>
       </c>
       <c r="BI30" s="15">
-        <v>96257</v>
+        <v>96264</v>
       </c>
       <c r="BJ30" s="7">
         <f t="shared" si="23"/>
-        <v>0.89901839001018036</v>
+        <v>0.89908376841102466</v>
       </c>
     </row>
     <row r="31" spans="1:62" x14ac:dyDescent="0.3">
@@ -5737,14 +5737,14 @@
       </c>
       <c r="E31" s="6">
         <f t="shared" si="0"/>
-        <v>77510</v>
+        <v>77511</v>
       </c>
       <c r="F31" s="14">
-        <v>102640</v>
+        <v>102641</v>
       </c>
       <c r="G31" s="7">
         <f t="shared" si="1"/>
-        <v>0.57882419286620612</v>
+        <v>0.57882983222895812</v>
       </c>
       <c r="H31" s="13">
         <v>166338</v>
@@ -5754,14 +5754,14 @@
       </c>
       <c r="J31" s="6">
         <f t="shared" si="2"/>
-        <v>76089</v>
+        <v>76090</v>
       </c>
       <c r="K31" s="14">
-        <v>102642</v>
+        <v>102643</v>
       </c>
       <c r="L31" s="7">
         <f t="shared" si="3"/>
-        <v>0.61706885979150883</v>
+        <v>0.61707487164688768</v>
       </c>
       <c r="M31" s="13">
         <v>353290</v>
@@ -5771,14 +5771,14 @@
       </c>
       <c r="O31" s="6">
         <f t="shared" si="4"/>
-        <v>205767</v>
+        <v>205768</v>
       </c>
       <c r="P31" s="15">
-        <v>318008</v>
+        <v>318009</v>
       </c>
       <c r="Q31" s="7">
         <f t="shared" si="5"/>
-        <v>0.90013303518356025</v>
+        <v>0.90013586571938065</v>
       </c>
       <c r="R31" s="13">
         <v>149791</v>
@@ -5788,14 +5788,14 @@
       </c>
       <c r="T31" s="6">
         <f t="shared" si="6"/>
-        <v>78519</v>
+        <v>78520</v>
       </c>
       <c r="U31" s="14">
-        <v>103537</v>
+        <v>103538</v>
       </c>
       <c r="V31" s="7">
         <f t="shared" si="7"/>
-        <v>0.69120975225480841</v>
+        <v>0.69121642822332452</v>
       </c>
       <c r="W31" s="13">
         <v>145173</v>
@@ -5805,14 +5805,14 @@
       </c>
       <c r="Y31" s="6">
         <f t="shared" si="8"/>
-        <v>77966</v>
+        <v>77968</v>
       </c>
       <c r="Z31" s="14">
-        <v>103932</v>
+        <v>103934</v>
       </c>
       <c r="AA31" s="7">
         <f t="shared" si="9"/>
-        <v>0.71591824926122627</v>
+        <v>0.71593202592768623</v>
       </c>
       <c r="AB31" s="13">
         <v>359995</v>
@@ -5822,14 +5822,14 @@
       </c>
       <c r="AD31" s="6">
         <f t="shared" si="10"/>
-        <v>244292</v>
+        <v>244295</v>
       </c>
       <c r="AE31" s="15">
-        <v>324777</v>
+        <v>324780</v>
       </c>
       <c r="AF31" s="7">
         <f t="shared" si="11"/>
-        <v>0.90217086348421505</v>
+        <v>0.90217919693329074</v>
       </c>
       <c r="AG31" s="13">
         <v>142536</v>
@@ -5839,14 +5839,14 @@
       </c>
       <c r="AI31" s="6">
         <f t="shared" si="12"/>
-        <v>83174</v>
+        <v>83177</v>
       </c>
       <c r="AJ31" s="14">
-        <v>105191</v>
+        <v>105194</v>
       </c>
       <c r="AK31" s="7">
         <f t="shared" si="13"/>
-        <v>0.737996015041814</v>
+        <v>0.7380170623561767</v>
       </c>
       <c r="AL31" s="13">
         <v>138001</v>
@@ -5856,14 +5856,14 @@
       </c>
       <c r="AN31" s="6">
         <f t="shared" si="14"/>
-        <v>78241</v>
+        <v>78244</v>
       </c>
       <c r="AO31" s="14">
-        <v>106871</v>
+        <v>106874</v>
       </c>
       <c r="AP31" s="7">
         <f t="shared" si="15"/>
-        <v>0.77442192447880809</v>
+        <v>0.77444366345171411</v>
       </c>
       <c r="AQ31" s="13">
         <v>354752</v>
@@ -5873,14 +5873,14 @@
       </c>
       <c r="AS31" s="6">
         <f t="shared" si="16"/>
-        <v>115100</v>
+        <v>115103</v>
       </c>
       <c r="AT31" s="15">
-        <v>329431</v>
+        <v>329434</v>
       </c>
       <c r="AU31" s="7">
         <f t="shared" si="17"/>
-        <v>0.92862337633050696</v>
+        <v>0.92863183294244989</v>
       </c>
       <c r="AV31" s="13">
         <v>121996</v>
@@ -5890,14 +5890,14 @@
       </c>
       <c r="AX31" s="6">
         <f t="shared" si="18"/>
-        <v>53860</v>
+        <v>53862</v>
       </c>
       <c r="AY31" s="14">
-        <v>106630</v>
+        <v>106632</v>
       </c>
       <c r="AZ31" s="7">
         <f t="shared" si="19"/>
-        <v>0.87404505065739857</v>
+        <v>0.87406144463752911</v>
       </c>
       <c r="BA31" s="13">
         <v>118866</v>
@@ -5907,14 +5907,14 @@
       </c>
       <c r="BC31" s="6">
         <f t="shared" si="20"/>
-        <v>27956</v>
+        <v>27959</v>
       </c>
       <c r="BD31" s="14">
-        <v>105924</v>
+        <v>105927</v>
       </c>
       <c r="BE31" s="7">
         <f t="shared" si="21"/>
-        <v>0.89112109434152742</v>
+        <v>0.89114633284538891</v>
       </c>
       <c r="BF31" s="13">
         <v>351474</v>
@@ -5924,14 +5924,14 @@
       </c>
       <c r="BH31" s="6">
         <f t="shared" si="22"/>
-        <v>114604</v>
+        <v>114613</v>
       </c>
       <c r="BI31" s="15">
-        <v>325332</v>
+        <v>325341</v>
       </c>
       <c r="BJ31" s="7">
         <f t="shared" si="23"/>
-        <v>0.92562180986360298</v>
+        <v>0.92564741630959901</v>
       </c>
     </row>
     <row r="32" spans="1:62" x14ac:dyDescent="0.3">
@@ -5949,14 +5949,14 @@
       </c>
       <c r="E32" s="6">
         <f t="shared" si="0"/>
-        <v>139152</v>
+        <v>139154</v>
       </c>
       <c r="F32" s="14">
-        <v>250990</v>
+        <v>250992</v>
       </c>
       <c r="G32" s="7">
         <f t="shared" si="1"/>
-        <v>0.62872616506848633</v>
+        <v>0.62873117503832632</v>
       </c>
       <c r="H32" s="13">
         <v>382894</v>
@@ -5966,14 +5966,14 @@
       </c>
       <c r="J32" s="6">
         <f t="shared" si="2"/>
-        <v>135152</v>
+        <v>135156</v>
       </c>
       <c r="K32" s="14">
-        <v>251281</v>
+        <v>251285</v>
       </c>
       <c r="L32" s="7">
         <f t="shared" si="3"/>
-        <v>0.65626779213045905</v>
+        <v>0.65627823888595804</v>
       </c>
       <c r="M32" s="13">
         <v>877062</v>
@@ -5983,14 +5983,14 @@
       </c>
       <c r="O32" s="6">
         <f t="shared" si="4"/>
-        <v>334423</v>
+        <v>334431</v>
       </c>
       <c r="P32" s="15">
-        <v>803152</v>
+        <v>803160</v>
       </c>
       <c r="Q32" s="7">
         <f t="shared" si="5"/>
-        <v>0.91573001680610944</v>
+        <v>0.91573913816811126</v>
       </c>
       <c r="R32" s="13">
         <v>340947</v>
@@ -6000,14 +6000,14 @@
       </c>
       <c r="T32" s="6">
         <f t="shared" si="6"/>
-        <v>151419</v>
+        <v>151423</v>
       </c>
       <c r="U32" s="14">
-        <v>253228</v>
+        <v>253232</v>
       </c>
       <c r="V32" s="7">
         <f t="shared" si="7"/>
-        <v>0.74271954292016062</v>
+        <v>0.74273127494889235</v>
       </c>
       <c r="W32" s="13">
         <v>329795</v>
@@ -6017,14 +6017,14 @@
       </c>
       <c r="Y32" s="6">
         <f t="shared" si="8"/>
-        <v>140549</v>
+        <v>140554</v>
       </c>
       <c r="Z32" s="14">
-        <v>253982</v>
+        <v>253987</v>
       </c>
       <c r="AA32" s="7">
         <f t="shared" si="9"/>
-        <v>0.77012083263845721</v>
+        <v>0.77013599357176432</v>
       </c>
       <c r="AB32" s="13">
         <v>884817</v>
@@ -6034,14 +6034,14 @@
       </c>
       <c r="AD32" s="6">
         <f t="shared" si="10"/>
-        <v>442907</v>
+        <v>442917</v>
       </c>
       <c r="AE32" s="15">
-        <v>818548</v>
+        <v>818558</v>
       </c>
       <c r="AF32" s="7">
         <f t="shared" si="11"/>
-        <v>0.92510428710117454</v>
+        <v>0.92511558887317946</v>
       </c>
       <c r="AG32" s="13">
         <v>320380</v>
@@ -6051,14 +6051,14 @@
       </c>
       <c r="AI32" s="6">
         <f t="shared" si="12"/>
-        <v>164314</v>
+        <v>164317</v>
       </c>
       <c r="AJ32" s="14">
-        <v>256039</v>
+        <v>256042</v>
       </c>
       <c r="AK32" s="7">
         <f t="shared" si="13"/>
-        <v>0.7991728572320369</v>
+        <v>0.79918222111242898</v>
       </c>
       <c r="AL32" s="13">
         <v>311565</v>
@@ -6068,14 +6068,14 @@
       </c>
       <c r="AN32" s="6">
         <f t="shared" si="14"/>
-        <v>130380</v>
+        <v>130385</v>
       </c>
       <c r="AO32" s="14">
-        <v>258439</v>
+        <v>258444</v>
       </c>
       <c r="AP32" s="7">
         <f t="shared" si="15"/>
-        <v>0.82948662397894501</v>
+        <v>0.82950267199460792</v>
       </c>
       <c r="AQ32" s="13">
         <v>877839</v>
@@ -6085,14 +6085,14 @@
       </c>
       <c r="AS32" s="6">
         <f t="shared" si="16"/>
-        <v>171124</v>
+        <v>171133</v>
       </c>
       <c r="AT32" s="15">
-        <v>832996</v>
+        <v>833005</v>
       </c>
       <c r="AU32" s="7">
         <f t="shared" si="17"/>
-        <v>0.94891660088011587</v>
+        <v>0.94892685332959692</v>
       </c>
       <c r="AV32" s="13">
         <v>297941</v>
@@ -6102,14 +6102,14 @@
       </c>
       <c r="AX32" s="6">
         <f t="shared" si="18"/>
-        <v>79196</v>
+        <v>79199</v>
       </c>
       <c r="AY32" s="14">
-        <v>259930</v>
+        <v>259933</v>
       </c>
       <c r="AZ32" s="7">
         <f t="shared" si="19"/>
-        <v>0.87242104980516277</v>
+        <v>0.87243111891280489</v>
       </c>
       <c r="BA32" s="13">
         <v>294413</v>
@@ -6119,14 +6119,14 @@
       </c>
       <c r="BC32" s="6">
         <f t="shared" si="20"/>
-        <v>35886</v>
+        <v>35889</v>
       </c>
       <c r="BD32" s="14">
-        <v>260525</v>
+        <v>260528</v>
       </c>
       <c r="BE32" s="7">
         <f t="shared" si="21"/>
-        <v>0.88489638704812623</v>
+        <v>0.88490657681556184</v>
       </c>
       <c r="BF32" s="13">
         <v>893063</v>
@@ -6136,14 +6136,14 @@
       </c>
       <c r="BH32" s="6">
         <f t="shared" si="22"/>
-        <v>159632</v>
+        <v>159648</v>
       </c>
       <c r="BI32" s="15">
-        <v>839685</v>
+        <v>839701</v>
       </c>
       <c r="BJ32" s="7">
         <f t="shared" si="23"/>
-        <v>0.94023042047425542</v>
+        <v>0.94024833634357263</v>
       </c>
     </row>
     <row r="33" spans="1:62" x14ac:dyDescent="0.3">
@@ -6373,14 +6373,14 @@
       </c>
       <c r="E34" s="6">
         <f t="shared" si="0"/>
-        <v>1651</v>
+        <v>1652</v>
       </c>
       <c r="F34" s="14">
-        <v>3409</v>
+        <v>3410</v>
       </c>
       <c r="G34" s="7">
         <f t="shared" si="1"/>
-        <v>0.65519892369786659</v>
+        <v>0.65539112050739956</v>
       </c>
       <c r="H34" s="13">
         <v>5064</v>
@@ -6390,14 +6390,14 @@
       </c>
       <c r="J34" s="6">
         <f t="shared" si="2"/>
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="K34" s="14">
-        <v>3419</v>
+        <v>3420</v>
       </c>
       <c r="L34" s="7">
         <f t="shared" si="3"/>
-        <v>0.67515797788309639</v>
+        <v>0.67535545023696686</v>
       </c>
       <c r="M34" s="13">
         <v>8364</v>
@@ -6407,14 +6407,14 @@
       </c>
       <c r="O34" s="6">
         <f t="shared" si="4"/>
-        <v>3506</v>
+        <v>3507</v>
       </c>
       <c r="P34" s="15">
-        <v>7426</v>
+        <v>7427</v>
       </c>
       <c r="Q34" s="7">
         <f t="shared" si="5"/>
-        <v>0.8878527020564323</v>
+        <v>0.8879722620755619</v>
       </c>
       <c r="R34" s="13">
         <v>4659</v>
@@ -6424,14 +6424,14 @@
       </c>
       <c r="T34" s="6">
         <f t="shared" si="6"/>
-        <v>1731</v>
+        <v>1732</v>
       </c>
       <c r="U34" s="14">
-        <v>3446</v>
+        <v>3447</v>
       </c>
       <c r="V34" s="7">
         <f t="shared" si="7"/>
-        <v>0.73964370036488514</v>
+        <v>0.73985833869929174</v>
       </c>
       <c r="W34" s="13">
         <v>4528</v>
@@ -6441,14 +6441,14 @@
       </c>
       <c r="Y34" s="6">
         <f t="shared" si="8"/>
-        <v>1691</v>
+        <v>1692</v>
       </c>
       <c r="Z34" s="14">
-        <v>3457</v>
+        <v>3458</v>
       </c>
       <c r="AA34" s="7">
         <f t="shared" si="9"/>
-        <v>0.76347173144876324</v>
+        <v>0.76369257950530034</v>
       </c>
       <c r="AB34" s="13">
         <v>8395</v>
@@ -6458,14 +6458,14 @@
       </c>
       <c r="AD34" s="6">
         <f t="shared" si="10"/>
-        <v>4193</v>
+        <v>4194</v>
       </c>
       <c r="AE34" s="15">
-        <v>7562</v>
+        <v>7563</v>
       </c>
       <c r="AF34" s="7">
         <f t="shared" si="11"/>
-        <v>0.90077427039904701</v>
+        <v>0.90089338892197734</v>
       </c>
       <c r="AG34" s="13">
         <v>4227</v>
@@ -6475,14 +6475,14 @@
       </c>
       <c r="AI34" s="6">
         <f t="shared" si="12"/>
-        <v>1790</v>
+        <v>1791</v>
       </c>
       <c r="AJ34" s="14">
-        <v>3517</v>
+        <v>3518</v>
       </c>
       <c r="AK34" s="7">
         <f t="shared" si="13"/>
-        <v>0.8320321741187604</v>
+        <v>0.83226874852140997</v>
       </c>
       <c r="AL34" s="13">
         <v>3917</v>
@@ -6492,14 +6492,14 @@
       </c>
       <c r="AN34" s="6">
         <f t="shared" si="14"/>
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="AO34" s="14">
-        <v>3527</v>
+        <v>3528</v>
       </c>
       <c r="AP34" s="7">
         <f t="shared" si="15"/>
-        <v>0.9004340056165433</v>
+        <v>0.90068930303803929</v>
       </c>
       <c r="AQ34" s="13">
         <v>7976</v>
@@ -6585,14 +6585,14 @@
       </c>
       <c r="E35" s="6">
         <f t="shared" si="0"/>
-        <v>222269</v>
+        <v>222274</v>
       </c>
       <c r="F35" s="14">
-        <v>358683</v>
+        <v>358688</v>
       </c>
       <c r="G35" s="7">
         <f t="shared" si="1"/>
-        <v>0.50862087302026215</v>
+        <v>0.50862796313706471</v>
       </c>
       <c r="H35" s="13">
         <v>678572</v>
@@ -6602,14 +6602,14 @@
       </c>
       <c r="J35" s="6">
         <f t="shared" si="2"/>
-        <v>218735</v>
+        <v>218740</v>
       </c>
       <c r="K35" s="14">
-        <v>358785</v>
+        <v>358790</v>
       </c>
       <c r="L35" s="7">
         <f t="shared" si="3"/>
-        <v>0.52873534422286805</v>
+        <v>0.52874271263771566</v>
       </c>
       <c r="M35" s="13">
         <v>1405014</v>
@@ -6619,14 +6619,14 @@
       </c>
       <c r="O35" s="6">
         <f t="shared" si="4"/>
-        <v>635979</v>
+        <v>635991</v>
       </c>
       <c r="P35" s="15">
-        <v>1205946</v>
+        <v>1205958</v>
       </c>
       <c r="Q35" s="7">
         <f t="shared" si="5"/>
-        <v>0.85831600254517038</v>
+        <v>0.85832454338533282</v>
       </c>
       <c r="R35" s="13">
         <v>600814</v>
@@ -6636,14 +6636,14 @@
       </c>
       <c r="T35" s="6">
         <f t="shared" si="6"/>
-        <v>231465</v>
+        <v>231472</v>
       </c>
       <c r="U35" s="14">
-        <v>362727</v>
+        <v>362734</v>
       </c>
       <c r="V35" s="7">
         <f t="shared" si="7"/>
-        <v>0.60372594513443434</v>
+        <v>0.60373759599476706</v>
       </c>
       <c r="W35" s="13">
         <v>577797</v>
@@ -6653,14 +6653,14 @@
       </c>
       <c r="Y35" s="6">
         <f t="shared" si="8"/>
-        <v>225100</v>
+        <v>225106</v>
       </c>
       <c r="Z35" s="14">
-        <v>364103</v>
+        <v>364109</v>
       </c>
       <c r="AA35" s="7">
         <f t="shared" si="9"/>
-        <v>0.6301573043819888</v>
+        <v>0.63016768865189676</v>
       </c>
       <c r="AB35" s="13">
         <v>1416919</v>
@@ -6670,14 +6670,14 @@
       </c>
       <c r="AD35" s="6">
         <f t="shared" si="10"/>
-        <v>775490</v>
+        <v>775503</v>
       </c>
       <c r="AE35" s="15">
-        <v>1227781</v>
+        <v>1227794</v>
       </c>
       <c r="AF35" s="7">
         <f t="shared" si="11"/>
-        <v>0.86651459963484156</v>
+        <v>0.86652377447122952</v>
       </c>
       <c r="AG35" s="13">
         <v>553324</v>
@@ -6687,14 +6687,14 @@
       </c>
       <c r="AI35" s="6">
         <f t="shared" si="12"/>
-        <v>245047</v>
+        <v>245052</v>
       </c>
       <c r="AJ35" s="14">
-        <v>367712</v>
+        <v>367717</v>
       </c>
       <c r="AK35" s="7">
         <f t="shared" si="13"/>
-        <v>0.66455096832958627</v>
+        <v>0.66456000462658404</v>
       </c>
       <c r="AL35" s="13">
         <v>528988</v>
@@ -6704,14 +6704,14 @@
       </c>
       <c r="AN35" s="6">
         <f t="shared" si="14"/>
-        <v>217289</v>
+        <v>217296</v>
       </c>
       <c r="AO35" s="14">
-        <v>372193</v>
+        <v>372200</v>
       </c>
       <c r="AP35" s="7">
         <f t="shared" si="15"/>
-        <v>0.70359441045921645</v>
+        <v>0.70360764327357139</v>
       </c>
       <c r="AQ35" s="13">
         <v>1379433</v>
@@ -6721,14 +6721,14 @@
       </c>
       <c r="AS35" s="6">
         <f t="shared" si="16"/>
-        <v>367216</v>
+        <v>367234</v>
       </c>
       <c r="AT35" s="15">
-        <v>1242112</v>
+        <v>1242130</v>
       </c>
       <c r="AU35" s="7">
         <f t="shared" si="17"/>
-        <v>0.90045112738349742</v>
+        <v>0.90046417622312935</v>
       </c>
       <c r="AV35" s="13">
         <v>465114</v>
@@ -6738,14 +6738,14 @@
       </c>
       <c r="AX35" s="6">
         <f t="shared" si="18"/>
-        <v>150892</v>
+        <v>150899</v>
       </c>
       <c r="AY35" s="14">
-        <v>372265</v>
+        <v>372272</v>
       </c>
       <c r="AZ35" s="7">
         <f t="shared" si="19"/>
-        <v>0.80037367183099195</v>
+        <v>0.80038872190473731</v>
       </c>
       <c r="BA35" s="13">
         <v>457177</v>
@@ -6755,14 +6755,14 @@
       </c>
       <c r="BC35" s="6">
         <f t="shared" si="20"/>
-        <v>87732</v>
+        <v>87742</v>
       </c>
       <c r="BD35" s="14">
-        <v>371915</v>
+        <v>371925</v>
       </c>
       <c r="BE35" s="7">
         <f t="shared" si="21"/>
-        <v>0.81350330397198456</v>
+        <v>0.81352517733831753</v>
       </c>
       <c r="BF35" s="13">
         <v>1380633</v>
@@ -6772,14 +6772,14 @@
       </c>
       <c r="BH35" s="6">
         <f t="shared" si="22"/>
-        <v>474374</v>
+        <v>474405</v>
       </c>
       <c r="BI35" s="15">
-        <v>1225936</v>
+        <v>1225967</v>
       </c>
       <c r="BJ35" s="7">
         <f t="shared" si="23"/>
-        <v>0.88795212051283723</v>
+        <v>0.8879745739816447</v>
       </c>
     </row>
     <row r="36" spans="1:62" x14ac:dyDescent="0.3">
@@ -6797,14 +6797,14 @@
       </c>
       <c r="E36" s="6">
         <f t="shared" si="0"/>
-        <v>256593</v>
+        <v>256600</v>
       </c>
       <c r="F36" s="14">
-        <v>364964</v>
+        <v>364971</v>
       </c>
       <c r="G36" s="7">
         <f t="shared" si="1"/>
-        <v>0.73407257375140045</v>
+        <v>0.73408665324421685</v>
       </c>
       <c r="H36" s="13">
         <v>485610</v>
@@ -6814,14 +6814,14 @@
       </c>
       <c r="J36" s="6">
         <f t="shared" si="2"/>
-        <v>259083</v>
+        <v>259090</v>
       </c>
       <c r="K36" s="14">
-        <v>366697</v>
+        <v>366704</v>
       </c>
       <c r="L36" s="7">
         <f t="shared" si="3"/>
-        <v>0.75512654187516737</v>
+        <v>0.75514095673482839</v>
       </c>
       <c r="M36" s="13">
         <v>710827</v>
@@ -6831,14 +6831,14 @@
       </c>
       <c r="O36" s="6">
         <f t="shared" si="4"/>
-        <v>373990</v>
+        <v>374004</v>
       </c>
       <c r="P36" s="15">
-        <v>612172</v>
+        <v>612186</v>
       </c>
       <c r="Q36" s="7">
         <f t="shared" si="5"/>
-        <v>0.86121095568964035</v>
+        <v>0.86123065105855579</v>
       </c>
       <c r="R36" s="13">
         <v>464623</v>
@@ -6848,14 +6848,14 @@
       </c>
       <c r="T36" s="6">
         <f t="shared" si="6"/>
-        <v>276266</v>
+        <v>276273</v>
       </c>
       <c r="U36" s="14">
-        <v>372852</v>
+        <v>372859</v>
       </c>
       <c r="V36" s="7">
         <f t="shared" si="7"/>
-        <v>0.80248287321118417</v>
+        <v>0.80249793918940737</v>
       </c>
       <c r="W36" s="13">
         <v>451202</v>
@@ -6865,14 +6865,14 @@
       </c>
       <c r="Y36" s="6">
         <f t="shared" si="8"/>
-        <v>271106</v>
+        <v>271111</v>
       </c>
       <c r="Z36" s="14">
-        <v>375729</v>
+        <v>375734</v>
       </c>
       <c r="AA36" s="7">
         <f t="shared" si="9"/>
-        <v>0.83272902159121631</v>
+        <v>0.83274010310237989</v>
       </c>
       <c r="AB36" s="13">
         <v>709880</v>
@@ -6882,14 +6882,14 @@
       </c>
       <c r="AD36" s="6">
         <f t="shared" si="10"/>
-        <v>427601</v>
+        <v>427609</v>
       </c>
       <c r="AE36" s="15">
-        <v>628831</v>
+        <v>628839</v>
       </c>
       <c r="AF36" s="7">
         <f t="shared" si="11"/>
-        <v>0.88582718205893951</v>
+        <v>0.88583845156927932</v>
       </c>
       <c r="AG36" s="13">
         <v>448411</v>
@@ -6899,14 +6899,14 @@
       </c>
       <c r="AI36" s="6">
         <f t="shared" si="12"/>
-        <v>282645</v>
+        <v>282650</v>
       </c>
       <c r="AJ36" s="14">
-        <v>381893</v>
+        <v>381898</v>
       </c>
       <c r="AK36" s="7">
         <f t="shared" si="13"/>
-        <v>0.85165841159115185</v>
+        <v>0.85166956207586342</v>
       </c>
       <c r="AL36" s="13">
         <v>443261</v>
@@ -6916,14 +6916,14 @@
       </c>
       <c r="AN36" s="6">
         <f t="shared" si="14"/>
-        <v>260449</v>
+        <v>260456</v>
       </c>
       <c r="AO36" s="14">
-        <v>386312</v>
+        <v>386319</v>
       </c>
       <c r="AP36" s="7">
         <f t="shared" si="15"/>
-        <v>0.87152264692810777</v>
+        <v>0.87153843897838967</v>
       </c>
       <c r="AQ36" s="13">
         <v>723207</v>
@@ -6933,14 +6933,14 @@
       </c>
       <c r="AS36" s="6">
         <f t="shared" si="16"/>
-        <v>261050</v>
+        <v>261060</v>
       </c>
       <c r="AT36" s="15">
-        <v>644754</v>
+        <v>644764</v>
       </c>
       <c r="AU36" s="7">
         <f t="shared" si="17"/>
-        <v>0.8915206849491224</v>
+        <v>0.89153451224891356</v>
       </c>
       <c r="AV36" s="13">
         <v>443230</v>
@@ -6950,14 +6950,14 @@
       </c>
       <c r="AX36" s="6">
         <f t="shared" si="18"/>
-        <v>196211</v>
+        <v>196219</v>
       </c>
       <c r="AY36" s="14">
-        <v>390281</v>
+        <v>390289</v>
       </c>
       <c r="AZ36" s="7">
         <f t="shared" si="19"/>
-        <v>0.88053832096202878</v>
+        <v>0.88055637028179501</v>
       </c>
       <c r="BA36" s="13">
         <v>443322</v>
@@ -6967,14 +6967,14 @@
       </c>
       <c r="BC36" s="6">
         <f t="shared" si="20"/>
-        <v>88449</v>
+        <v>88456</v>
       </c>
       <c r="BD36" s="14">
-        <v>389667</v>
+        <v>389674</v>
       </c>
       <c r="BE36" s="7">
         <f t="shared" si="21"/>
-        <v>0.87897059022561475</v>
+        <v>0.87898638010295005</v>
       </c>
       <c r="BF36" s="13">
         <v>734800</v>
@@ -6984,14 +6984,14 @@
       </c>
       <c r="BH36" s="6">
         <f t="shared" si="22"/>
-        <v>185079</v>
+        <v>185095</v>
       </c>
       <c r="BI36" s="15">
-        <v>637954</v>
+        <v>637970</v>
       </c>
       <c r="BJ36" s="7">
         <f t="shared" si="23"/>
-        <v>0.86820087098530208</v>
+        <v>0.86822264561785523</v>
       </c>
     </row>
     <row r="37" spans="1:62" x14ac:dyDescent="0.3">
@@ -7009,14 +7009,14 @@
       </c>
       <c r="E37" s="6">
         <f t="shared" si="0"/>
-        <v>7226</v>
+        <v>7227</v>
       </c>
       <c r="F37" s="14">
-        <v>11816</v>
+        <v>11817</v>
       </c>
       <c r="G37" s="7">
         <f t="shared" si="1"/>
-        <v>0.55450748510019243</v>
+        <v>0.55455441362804447</v>
       </c>
       <c r="H37" s="13">
         <v>20779</v>
@@ -7026,14 +7026,14 @@
       </c>
       <c r="J37" s="6">
         <f t="shared" si="2"/>
-        <v>7245</v>
+        <v>7246</v>
       </c>
       <c r="K37" s="14">
-        <v>11845</v>
+        <v>11846</v>
       </c>
       <c r="L37" s="7">
         <f t="shared" si="3"/>
-        <v>0.5700466817459936</v>
+        <v>0.57009480725732709</v>
       </c>
       <c r="M37" s="13">
         <v>33757</v>
@@ -7043,14 +7043,14 @@
       </c>
       <c r="O37" s="6">
         <f t="shared" si="4"/>
-        <v>15105</v>
+        <v>15106</v>
       </c>
       <c r="P37" s="15">
-        <v>28365</v>
+        <v>28366</v>
       </c>
       <c r="Q37" s="7">
         <f t="shared" si="5"/>
-        <v>0.84027016618775363</v>
+        <v>0.84029978967325292</v>
       </c>
       <c r="R37" s="13">
         <v>19308</v>
@@ -7060,14 +7060,14 @@
       </c>
       <c r="T37" s="6">
         <f t="shared" si="6"/>
-        <v>7594</v>
+        <v>7595</v>
       </c>
       <c r="U37" s="14">
-        <v>11977</v>
+        <v>11978</v>
       </c>
       <c r="V37" s="7">
         <f t="shared" si="7"/>
-        <v>0.62031282370002072</v>
+        <v>0.62036461570333545</v>
       </c>
       <c r="W37" s="13">
         <v>18815</v>
@@ -7077,14 +7077,14 @@
       </c>
       <c r="Y37" s="6">
         <f t="shared" si="8"/>
-        <v>7582</v>
+        <v>7583</v>
       </c>
       <c r="Z37" s="14">
-        <v>12035</v>
+        <v>12036</v>
       </c>
       <c r="AA37" s="7">
         <f t="shared" si="9"/>
-        <v>0.6396492160510231</v>
+        <v>0.63970236513420142</v>
       </c>
       <c r="AB37" s="13">
         <v>34397</v>
@@ -7094,14 +7094,14 @@
       </c>
       <c r="AD37" s="6">
         <f t="shared" si="10"/>
-        <v>16588</v>
+        <v>16591</v>
       </c>
       <c r="AE37" s="15">
-        <v>28816</v>
+        <v>28819</v>
       </c>
       <c r="AF37" s="7">
         <f t="shared" si="11"/>
-        <v>0.83774747797773064</v>
+        <v>0.8378346948861819</v>
       </c>
       <c r="AG37" s="13">
         <v>18492</v>
@@ -7111,14 +7111,14 @@
       </c>
       <c r="AI37" s="6">
         <f t="shared" si="12"/>
-        <v>7691</v>
+        <v>7693</v>
       </c>
       <c r="AJ37" s="14">
-        <v>12190</v>
+        <v>12192</v>
       </c>
       <c r="AK37" s="7">
         <f t="shared" si="13"/>
-        <v>0.65920398009950254</v>
+        <v>0.65931213497728747</v>
       </c>
       <c r="AL37" s="13">
         <v>18104</v>
@@ -7128,14 +7128,14 @@
       </c>
       <c r="AN37" s="6">
         <f t="shared" si="14"/>
-        <v>7094</v>
+        <v>7095</v>
       </c>
       <c r="AO37" s="14">
-        <v>12268</v>
+        <v>12269</v>
       </c>
       <c r="AP37" s="7">
         <f t="shared" si="15"/>
-        <v>0.67764030048608037</v>
+        <v>0.67769553689792306</v>
       </c>
       <c r="AQ37" s="13">
         <v>35044</v>
@@ -7145,14 +7145,14 @@
       </c>
       <c r="AS37" s="6">
         <f t="shared" si="16"/>
-        <v>11902</v>
+        <v>11905</v>
       </c>
       <c r="AT37" s="15">
-        <v>29385</v>
+        <v>29388</v>
       </c>
       <c r="AU37" s="7">
         <f t="shared" si="17"/>
-        <v>0.83851729254651297</v>
+        <v>0.83860289921241871</v>
       </c>
       <c r="AV37" s="13">
         <v>17705</v>
@@ -7162,14 +7162,14 @@
       </c>
       <c r="AX37" s="6">
         <f t="shared" si="18"/>
-        <v>5986</v>
+        <v>5987</v>
       </c>
       <c r="AY37" s="14">
-        <v>12400</v>
+        <v>12401</v>
       </c>
       <c r="AZ37" s="7">
         <f t="shared" si="19"/>
-        <v>0.70036712792996325</v>
+        <v>0.7004236091499576</v>
       </c>
       <c r="BA37" s="13">
         <v>17648</v>
@@ -7179,14 +7179,14 @@
       </c>
       <c r="BC37" s="6">
         <f t="shared" si="20"/>
-        <v>3378</v>
+        <v>3379</v>
       </c>
       <c r="BD37" s="14">
-        <v>12413</v>
+        <v>12414</v>
       </c>
       <c r="BE37" s="7">
         <f t="shared" si="21"/>
-        <v>0.70336582048957386</v>
+        <v>0.70342248413417952</v>
       </c>
       <c r="BF37" s="13">
         <v>36052</v>
@@ -7196,14 +7196,14 @@
       </c>
       <c r="BH37" s="6">
         <f t="shared" si="22"/>
-        <v>9365</v>
+        <v>9366</v>
       </c>
       <c r="BI37" s="15">
-        <v>29561</v>
+        <v>29562</v>
       </c>
       <c r="BJ37" s="7">
         <f t="shared" si="23"/>
-        <v>0.81995451015200271</v>
+        <v>0.81998224786419616</v>
       </c>
     </row>
     <row r="38" spans="1:62" x14ac:dyDescent="0.3">
@@ -7433,14 +7433,14 @@
       </c>
       <c r="E39" s="6">
         <f t="shared" si="0"/>
-        <v>107047</v>
+        <v>107053</v>
       </c>
       <c r="F39" s="14">
-        <v>146406</v>
+        <v>146412</v>
       </c>
       <c r="G39" s="7">
         <f t="shared" si="1"/>
-        <v>0.72364297788629783</v>
+        <v>0.72367263416997007</v>
       </c>
       <c r="H39" s="13">
         <v>195184</v>
@@ -7450,14 +7450,14 @@
       </c>
       <c r="J39" s="6">
         <f t="shared" si="2"/>
-        <v>109483</v>
+        <v>109488</v>
       </c>
       <c r="K39" s="14">
-        <v>147121</v>
+        <v>147126</v>
       </c>
       <c r="L39" s="7">
         <f t="shared" si="3"/>
-        <v>0.75375543077301421</v>
+        <v>0.75378104762685461</v>
       </c>
       <c r="M39" s="13">
         <v>295913</v>
@@ -7467,14 +7467,14 @@
       </c>
       <c r="O39" s="6">
         <f t="shared" si="4"/>
-        <v>164039</v>
+        <v>164047</v>
       </c>
       <c r="P39" s="15">
-        <v>262812</v>
+        <v>262820</v>
       </c>
       <c r="Q39" s="7">
         <f t="shared" si="5"/>
-        <v>0.88813941935636487</v>
+        <v>0.88816645432948194</v>
       </c>
       <c r="R39" s="13">
         <v>189177</v>
@@ -7484,14 +7484,14 @@
       </c>
       <c r="T39" s="6">
         <f t="shared" si="6"/>
-        <v>118715</v>
+        <v>118720</v>
       </c>
       <c r="U39" s="14">
-        <v>149146</v>
+        <v>149151</v>
       </c>
       <c r="V39" s="7">
         <f t="shared" si="7"/>
-        <v>0.78839393795228807</v>
+        <v>0.78842036822658146</v>
       </c>
       <c r="W39" s="13">
         <v>187045</v>
@@ -7501,14 +7501,14 @@
       </c>
       <c r="Y39" s="6">
         <f t="shared" si="8"/>
-        <v>120604</v>
+        <v>120608</v>
       </c>
       <c r="Z39" s="14">
-        <v>150223</v>
+        <v>150227</v>
       </c>
       <c r="AA39" s="7">
         <f t="shared" si="9"/>
-        <v>0.80313828223154859</v>
+        <v>0.80315966745970224</v>
       </c>
       <c r="AB39" s="13">
         <v>301836</v>
@@ -7518,14 +7518,14 @@
       </c>
       <c r="AD39" s="6">
         <f t="shared" si="10"/>
-        <v>185918</v>
+        <v>185924</v>
       </c>
       <c r="AE39" s="15">
-        <v>268517</v>
+        <v>268523</v>
       </c>
       <c r="AF39" s="7">
         <f t="shared" si="11"/>
-        <v>0.88961223975933956</v>
+        <v>0.88963211810387099</v>
       </c>
       <c r="AG39" s="13">
         <v>184754</v>
@@ -7535,14 +7535,14 @@
       </c>
       <c r="AI39" s="6">
         <f t="shared" si="12"/>
-        <v>115702</v>
+        <v>115707</v>
       </c>
       <c r="AJ39" s="14">
-        <v>152272</v>
+        <v>152277</v>
       </c>
       <c r="AK39" s="7">
         <f t="shared" si="13"/>
-        <v>0.8241878389642443</v>
+        <v>0.82421490197776504</v>
       </c>
       <c r="AL39" s="13">
         <v>180486</v>
@@ -7552,14 +7552,14 @@
       </c>
       <c r="AN39" s="6">
         <f t="shared" si="14"/>
-        <v>98537</v>
+        <v>98542</v>
       </c>
       <c r="AO39" s="14">
-        <v>153963</v>
+        <v>153968</v>
       </c>
       <c r="AP39" s="7">
         <f t="shared" si="15"/>
-        <v>0.85304677371098037</v>
+        <v>0.8530744766907129</v>
       </c>
       <c r="AQ39" s="13">
         <v>302709</v>
@@ -7569,14 +7569,14 @@
       </c>
       <c r="AS39" s="6">
         <f t="shared" si="16"/>
-        <v>112530</v>
+        <v>112536</v>
       </c>
       <c r="AT39" s="15">
-        <v>273380</v>
+        <v>273386</v>
       </c>
       <c r="AU39" s="7">
         <f t="shared" si="17"/>
-        <v>0.90311156919681934</v>
+        <v>0.90313139021304289</v>
       </c>
       <c r="AV39" s="13">
         <v>175450</v>
@@ -7586,14 +7586,14 @@
       </c>
       <c r="AX39" s="6">
         <f t="shared" si="18"/>
-        <v>78375</v>
+        <v>78380</v>
       </c>
       <c r="AY39" s="14">
-        <v>155010</v>
+        <v>155015</v>
       </c>
       <c r="AZ39" s="7">
         <f t="shared" si="19"/>
-        <v>0.88349957252778566</v>
+        <v>0.88352807067540606</v>
       </c>
       <c r="BA39" s="13">
         <v>174499</v>
@@ -7603,14 +7603,14 @@
       </c>
       <c r="BC39" s="6">
         <f t="shared" si="20"/>
-        <v>36463</v>
+        <v>36470</v>
       </c>
       <c r="BD39" s="14">
-        <v>155243</v>
+        <v>155250</v>
       </c>
       <c r="BE39" s="7">
         <f t="shared" si="21"/>
-        <v>0.88964979742004258</v>
+        <v>0.88968991226310756</v>
       </c>
       <c r="BF39" s="13">
         <v>304085</v>
@@ -7620,14 +7620,14 @@
       </c>
       <c r="BH39" s="6">
         <f t="shared" si="22"/>
-        <v>83579</v>
+        <v>83593</v>
       </c>
       <c r="BI39" s="15">
-        <v>273265</v>
+        <v>273279</v>
       </c>
       <c r="BJ39" s="7">
         <f t="shared" si="23"/>
-        <v>0.89864675995198706</v>
+        <v>0.89869279971060723</v>
       </c>
     </row>
     <row r="40" spans="1:62" x14ac:dyDescent="0.3">
@@ -7645,14 +7645,14 @@
       </c>
       <c r="E40" s="6">
         <f t="shared" si="0"/>
-        <v>374801</v>
+        <v>374865</v>
       </c>
       <c r="F40" s="14">
-        <v>520678</v>
+        <v>520742</v>
       </c>
       <c r="G40" s="7">
         <f t="shared" si="1"/>
-        <v>0.764194780301229</v>
+        <v>0.76428871257019237</v>
       </c>
       <c r="H40" s="13">
         <v>679109</v>
@@ -7662,14 +7662,14 @@
       </c>
       <c r="J40" s="6">
         <f t="shared" si="2"/>
-        <v>379352</v>
+        <v>379415</v>
       </c>
       <c r="K40" s="14">
-        <v>523646</v>
+        <v>523709</v>
       </c>
       <c r="L40" s="7">
         <f t="shared" si="3"/>
-        <v>0.77107798600813715</v>
+        <v>0.77117075462112861</v>
       </c>
       <c r="M40" s="13">
         <v>894344</v>
@@ -7679,14 +7679,14 @@
       </c>
       <c r="O40" s="6">
         <f t="shared" si="4"/>
-        <v>479323</v>
+        <v>479407</v>
       </c>
       <c r="P40" s="15">
-        <v>752419</v>
+        <v>752503</v>
       </c>
       <c r="Q40" s="7">
         <f t="shared" si="5"/>
-        <v>0.84130826617051158</v>
+        <v>0.84140218976143411</v>
       </c>
       <c r="R40" s="13">
         <v>670695</v>
@@ -7696,14 +7696,14 @@
       </c>
       <c r="T40" s="6">
         <f t="shared" si="6"/>
-        <v>398422</v>
+        <v>398490</v>
       </c>
       <c r="U40" s="14">
-        <v>530899</v>
+        <v>530967</v>
       </c>
       <c r="V40" s="7">
         <f t="shared" si="7"/>
-        <v>0.79156546567366681</v>
+        <v>0.79166685304050277</v>
       </c>
       <c r="W40" s="13">
         <v>664170</v>
@@ -7713,14 +7713,14 @@
       </c>
       <c r="Y40" s="6">
         <f t="shared" si="8"/>
-        <v>396911</v>
+        <v>396971</v>
       </c>
       <c r="Z40" s="14">
-        <v>534848</v>
+        <v>534908</v>
       </c>
       <c r="AA40" s="7">
         <f t="shared" si="9"/>
-        <v>0.80528780282156676</v>
+        <v>0.80537814113856387</v>
       </c>
       <c r="AB40" s="13">
         <v>900385</v>
@@ -7730,14 +7730,14 @@
       </c>
       <c r="AD40" s="6">
         <f t="shared" si="10"/>
-        <v>541761</v>
+        <v>541852</v>
       </c>
       <c r="AE40" s="15">
-        <v>769237</v>
+        <v>769328</v>
       </c>
       <c r="AF40" s="7">
         <f t="shared" si="11"/>
-        <v>0.85434230912331943</v>
+        <v>0.85444337699983897</v>
       </c>
       <c r="AG40" s="13">
         <v>654051</v>
@@ -7747,14 +7747,14 @@
       </c>
       <c r="AI40" s="6">
         <f t="shared" si="12"/>
-        <v>407200</v>
+        <v>407259</v>
       </c>
       <c r="AJ40" s="14">
-        <v>542033</v>
+        <v>542092</v>
       </c>
       <c r="AK40" s="7">
         <f t="shared" si="13"/>
-        <v>0.8287320101949236</v>
+        <v>0.82882221722770855</v>
       </c>
       <c r="AL40" s="13">
         <v>640748</v>
@@ -7764,14 +7764,14 @@
       </c>
       <c r="AN40" s="6">
         <f t="shared" si="14"/>
-        <v>372321</v>
+        <v>372381</v>
       </c>
       <c r="AO40" s="14">
-        <v>547265</v>
+        <v>547325</v>
       </c>
       <c r="AP40" s="7">
         <f t="shared" si="15"/>
-        <v>0.85410332923395782</v>
+        <v>0.85419696979155613</v>
       </c>
       <c r="AQ40" s="13">
         <v>877850</v>
@@ -7781,14 +7781,14 @@
       </c>
       <c r="AS40" s="6">
         <f t="shared" si="16"/>
-        <v>283930</v>
+        <v>284003</v>
       </c>
       <c r="AT40" s="15">
-        <v>786446</v>
+        <v>786519</v>
       </c>
       <c r="AU40" s="7">
         <f t="shared" si="17"/>
-        <v>0.89587742780657287</v>
+        <v>0.89596058552144442</v>
       </c>
       <c r="AV40" s="13">
         <v>620078</v>
@@ -7798,14 +7798,14 @@
       </c>
       <c r="AX40" s="6">
         <f t="shared" si="18"/>
-        <v>256970</v>
+        <v>257012</v>
       </c>
       <c r="AY40" s="14">
-        <v>553816</v>
+        <v>553858</v>
       </c>
       <c r="AZ40" s="7">
         <f t="shared" si="19"/>
-        <v>0.89313925022335905</v>
+        <v>0.89320698363754236</v>
       </c>
       <c r="BA40" s="13">
         <v>613352</v>
@@ -7815,14 +7815,14 @@
       </c>
       <c r="BC40" s="6">
         <f t="shared" si="20"/>
-        <v>101312</v>
+        <v>101357</v>
       </c>
       <c r="BD40" s="14">
-        <v>555546</v>
+        <v>555591</v>
       </c>
       <c r="BE40" s="7">
         <f t="shared" si="21"/>
-        <v>0.9057539553144035</v>
+        <v>0.90582732264670207</v>
       </c>
       <c r="BF40" s="13">
         <v>876639</v>
@@ -7832,14 +7832,14 @@
       </c>
       <c r="BH40" s="6">
         <f t="shared" si="22"/>
-        <v>217516</v>
+        <v>217596</v>
       </c>
       <c r="BI40" s="15">
-        <v>785547</v>
+        <v>785627</v>
       </c>
       <c r="BJ40" s="7">
         <f t="shared" si="23"/>
-        <v>0.89608949636053148</v>
+        <v>0.89618075399337693</v>
       </c>
     </row>
     <row r="41" spans="1:62" x14ac:dyDescent="0.3">
@@ -7942,14 +7942,14 @@
       </c>
       <c r="AD41" s="6">
         <f t="shared" si="10"/>
-        <v>11892</v>
+        <v>11894</v>
       </c>
       <c r="AE41" s="15">
-        <v>17189</v>
+        <v>17191</v>
       </c>
       <c r="AF41" s="7">
         <f t="shared" si="11"/>
-        <v>0.81755053507728892</v>
+        <v>0.81764565992865634</v>
       </c>
       <c r="AG41" s="13">
         <v>15000</v>
@@ -7959,14 +7959,14 @@
       </c>
       <c r="AI41" s="6">
         <f t="shared" si="12"/>
-        <v>8523</v>
+        <v>8525</v>
       </c>
       <c r="AJ41" s="14">
-        <v>11949</v>
+        <v>11951</v>
       </c>
       <c r="AK41" s="7">
         <f t="shared" si="13"/>
-        <v>0.79659999999999997</v>
+        <v>0.79673333333333329</v>
       </c>
       <c r="AL41" s="13">
         <v>14741</v>
@@ -7976,14 +7976,14 @@
       </c>
       <c r="AN41" s="6">
         <f t="shared" si="14"/>
-        <v>7789</v>
+        <v>7790</v>
       </c>
       <c r="AO41" s="14">
-        <v>11998</v>
+        <v>11999</v>
       </c>
       <c r="AP41" s="7">
         <f t="shared" si="15"/>
-        <v>0.81392035818465502</v>
+        <v>0.81398819618750429</v>
       </c>
       <c r="AQ41" s="13">
         <v>20391</v>
@@ -7993,14 +7993,14 @@
       </c>
       <c r="AS41" s="6">
         <f t="shared" si="16"/>
-        <v>6922</v>
+        <v>6924</v>
       </c>
       <c r="AT41" s="15">
-        <v>17369</v>
+        <v>17371</v>
       </c>
       <c r="AU41" s="7">
         <f t="shared" si="17"/>
-        <v>0.85179736158108965</v>
+        <v>0.85189544406846163</v>
       </c>
       <c r="AV41" s="13">
         <v>13562</v>
@@ -8010,14 +8010,14 @@
       </c>
       <c r="AX41" s="6">
         <f t="shared" si="18"/>
-        <v>5910</v>
+        <v>5911</v>
       </c>
       <c r="AY41" s="14">
-        <v>11993</v>
+        <v>11994</v>
       </c>
       <c r="AZ41" s="7">
         <f t="shared" si="19"/>
-        <v>0.88430909895295684</v>
+        <v>0.88438283439020793</v>
       </c>
       <c r="BA41" s="13">
         <v>13336</v>
@@ -8027,14 +8027,14 @@
       </c>
       <c r="BC41" s="6">
         <f t="shared" si="20"/>
-        <v>2430</v>
+        <v>2431</v>
       </c>
       <c r="BD41" s="14">
-        <v>11993</v>
+        <v>11994</v>
       </c>
       <c r="BE41" s="7">
         <f t="shared" si="21"/>
-        <v>0.89929514097180563</v>
+        <v>0.89937012597480503</v>
       </c>
       <c r="BF41" s="13">
         <v>19681</v>
@@ -8044,14 +8044,14 @@
       </c>
       <c r="BH41" s="6">
         <f t="shared" si="22"/>
-        <v>4506</v>
+        <v>4508</v>
       </c>
       <c r="BI41" s="15">
-        <v>17111</v>
+        <v>17113</v>
       </c>
       <c r="BJ41" s="7">
         <f t="shared" si="23"/>
-        <v>0.86941720441034498</v>
+        <v>0.869518825262944</v>
       </c>
     </row>
     <row r="42" spans="1:62" x14ac:dyDescent="0.3">
@@ -8281,14 +8281,14 @@
       </c>
       <c r="E43" s="6">
         <f t="shared" si="0"/>
-        <v>128414</v>
+        <v>128415</v>
       </c>
       <c r="F43" s="14">
-        <v>171675</v>
+        <v>171676</v>
       </c>
       <c r="G43" s="7">
         <f t="shared" si="1"/>
-        <v>0.6947170345790421</v>
+        <v>0.69472108127794752</v>
       </c>
       <c r="H43" s="13">
         <v>243625</v>
@@ -8298,14 +8298,14 @@
       </c>
       <c r="J43" s="6">
         <f t="shared" si="2"/>
-        <v>131244</v>
+        <v>131245</v>
       </c>
       <c r="K43" s="14">
-        <v>173066</v>
+        <v>173067</v>
       </c>
       <c r="L43" s="7">
         <f t="shared" si="3"/>
-        <v>0.71037865572088255</v>
+        <v>0.71038276038994352</v>
       </c>
       <c r="M43" s="13">
         <v>327844</v>
@@ -8315,14 +8315,14 @@
       </c>
       <c r="O43" s="6">
         <f t="shared" si="4"/>
-        <v>177494</v>
+        <v>177496</v>
       </c>
       <c r="P43" s="15">
-        <v>265580</v>
+        <v>265582</v>
       </c>
       <c r="Q43" s="7">
         <f t="shared" si="5"/>
-        <v>0.81008040409463034</v>
+        <v>0.81008650455704545</v>
       </c>
       <c r="R43" s="13">
         <v>238294</v>
@@ -8366,14 +8366,14 @@
       </c>
       <c r="AD43" s="6">
         <f t="shared" si="10"/>
-        <v>202419</v>
+        <v>202420</v>
       </c>
       <c r="AE43" s="15">
-        <v>274794</v>
+        <v>274795</v>
       </c>
       <c r="AF43" s="7">
         <f t="shared" si="11"/>
-        <v>0.81390058822484046</v>
+        <v>0.8139035500820434</v>
       </c>
       <c r="AG43" s="13">
         <v>239475</v>
@@ -8417,14 +8417,14 @@
       </c>
       <c r="AS43" s="6">
         <f t="shared" si="16"/>
-        <v>129099</v>
+        <v>129102</v>
       </c>
       <c r="AT43" s="15">
-        <v>284207</v>
+        <v>284210</v>
       </c>
       <c r="AU43" s="7">
         <f t="shared" si="17"/>
-        <v>0.81147746934906373</v>
+        <v>0.81148603505085171</v>
       </c>
       <c r="AV43" s="13">
         <v>239471</v>
@@ -8434,14 +8434,14 @@
       </c>
       <c r="AX43" s="6">
         <f t="shared" si="18"/>
-        <v>103608</v>
+        <v>103610</v>
       </c>
       <c r="AY43" s="14">
-        <v>186003</v>
+        <v>186005</v>
       </c>
       <c r="AZ43" s="7">
         <f t="shared" si="19"/>
-        <v>0.77672453031891131</v>
+        <v>0.77673288206087587</v>
       </c>
       <c r="BA43" s="13">
         <v>238143</v>
@@ -8451,14 +8451,14 @@
       </c>
       <c r="BC43" s="6">
         <f t="shared" si="20"/>
-        <v>50109</v>
+        <v>50112</v>
       </c>
       <c r="BD43" s="14">
-        <v>185995</v>
+        <v>185998</v>
       </c>
       <c r="BE43" s="7">
         <f t="shared" si="21"/>
-        <v>0.78102232692121965</v>
+        <v>0.78103492439416655</v>
       </c>
       <c r="BF43" s="13">
         <v>357819</v>
@@ -8468,14 +8468,14 @@
       </c>
       <c r="BH43" s="6">
         <f t="shared" si="22"/>
-        <v>87523</v>
+        <v>87526</v>
       </c>
       <c r="BI43" s="15">
-        <v>282584</v>
+        <v>282587</v>
       </c>
       <c r="BJ43" s="7">
         <f t="shared" si="23"/>
-        <v>0.78974006411062581</v>
+        <v>0.78974844823779622</v>
       </c>
     </row>
     <row r="44" spans="1:62" x14ac:dyDescent="0.3">
@@ -8493,14 +8493,14 @@
       </c>
       <c r="E44" s="6">
         <f t="shared" si="0"/>
-        <v>115163</v>
+        <v>115167</v>
       </c>
       <c r="F44" s="14">
-        <v>155111</v>
+        <v>155115</v>
       </c>
       <c r="G44" s="7">
         <f t="shared" si="1"/>
-        <v>0.73195949261957793</v>
+        <v>0.73197836837932728</v>
       </c>
       <c r="H44" s="13">
         <v>206448</v>
@@ -8510,14 +8510,14 @@
       </c>
       <c r="J44" s="6">
         <f t="shared" si="2"/>
-        <v>114663</v>
+        <v>114666</v>
       </c>
       <c r="K44" s="14">
-        <v>155636</v>
+        <v>155639</v>
       </c>
       <c r="L44" s="7">
         <f t="shared" si="3"/>
-        <v>0.75387506781368674</v>
+        <v>0.75388959931798805</v>
       </c>
       <c r="M44" s="13">
         <v>281946</v>
@@ -8527,14 +8527,14 @@
       </c>
       <c r="O44" s="6">
         <f t="shared" si="4"/>
-        <v>154654</v>
+        <v>154659</v>
       </c>
       <c r="P44" s="15">
-        <v>236532</v>
+        <v>236537</v>
       </c>
       <c r="Q44" s="7">
         <f t="shared" si="5"/>
-        <v>0.83892660296652555</v>
+        <v>0.83894433685883107</v>
       </c>
       <c r="R44" s="13">
         <v>201438</v>
@@ -8544,14 +8544,14 @@
       </c>
       <c r="T44" s="6">
         <f t="shared" si="6"/>
-        <v>120068</v>
+        <v>120072</v>
       </c>
       <c r="U44" s="14">
-        <v>157826</v>
+        <v>157830</v>
       </c>
       <c r="V44" s="7">
         <f t="shared" si="7"/>
-        <v>0.78349665902163446</v>
+        <v>0.78351651624817564</v>
       </c>
       <c r="W44" s="13">
         <v>199209</v>
@@ -8561,14 +8561,14 @@
       </c>
       <c r="Y44" s="6">
         <f t="shared" si="8"/>
-        <v>119408</v>
+        <v>119412</v>
       </c>
       <c r="Z44" s="14">
-        <v>158779</v>
+        <v>158783</v>
       </c>
       <c r="AA44" s="7">
         <f t="shared" si="9"/>
-        <v>0.79704732215913943</v>
+        <v>0.79706740157322209</v>
       </c>
       <c r="AB44" s="13">
         <v>287263</v>
@@ -8578,14 +8578,14 @@
       </c>
       <c r="AD44" s="6">
         <f t="shared" si="10"/>
-        <v>175610</v>
+        <v>175616</v>
       </c>
       <c r="AE44" s="15">
-        <v>241470</v>
+        <v>241476</v>
       </c>
       <c r="AF44" s="7">
         <f t="shared" si="11"/>
-        <v>0.84058858955034232</v>
+        <v>0.84060947633353411</v>
       </c>
       <c r="AG44" s="13">
         <v>197620</v>
@@ -8595,14 +8595,14 @@
       </c>
       <c r="AI44" s="6">
         <f t="shared" si="12"/>
-        <v>124459</v>
+        <v>124462</v>
       </c>
       <c r="AJ44" s="14">
-        <v>160857</v>
+        <v>160860</v>
       </c>
       <c r="AK44" s="7">
         <f t="shared" si="13"/>
-        <v>0.81397125796984116</v>
+        <v>0.81398643861957287</v>
       </c>
       <c r="AL44" s="13">
         <v>193704</v>
@@ -8612,14 +8612,14 @@
       </c>
       <c r="AN44" s="6">
         <f t="shared" si="14"/>
-        <v>115474</v>
+        <v>115479</v>
       </c>
       <c r="AO44" s="14">
-        <v>162829</v>
+        <v>162834</v>
       </c>
       <c r="AP44" s="7">
         <f t="shared" si="15"/>
-        <v>0.84060731838268699</v>
+        <v>0.84063313096270598</v>
       </c>
       <c r="AQ44" s="13">
         <v>286760</v>
@@ -8629,14 +8629,14 @@
       </c>
       <c r="AS44" s="6">
         <f t="shared" si="16"/>
-        <v>94935</v>
+        <v>94941</v>
       </c>
       <c r="AT44" s="15">
-        <v>246406</v>
+        <v>246412</v>
       </c>
       <c r="AU44" s="7">
         <f t="shared" si="17"/>
-        <v>0.85927604965825077</v>
+        <v>0.85929697307853259</v>
       </c>
       <c r="AV44" s="13">
         <v>192119</v>
@@ -8646,14 +8646,14 @@
       </c>
       <c r="AX44" s="6">
         <f t="shared" si="18"/>
-        <v>83610</v>
+        <v>83614</v>
       </c>
       <c r="AY44" s="14">
-        <v>163483</v>
+        <v>163487</v>
       </c>
       <c r="AZ44" s="7">
         <f t="shared" si="19"/>
-        <v>0.85094654875363707</v>
+        <v>0.85096736918264204</v>
       </c>
       <c r="BA44" s="13">
         <v>188319</v>
@@ -8663,14 +8663,14 @@
       </c>
       <c r="BC44" s="6">
         <f t="shared" si="20"/>
-        <v>34270</v>
+        <v>34274</v>
       </c>
       <c r="BD44" s="14">
-        <v>162911</v>
+        <v>162915</v>
       </c>
       <c r="BE44" s="7">
         <f t="shared" si="21"/>
-        <v>0.86507999723872786</v>
+        <v>0.86510123779331882</v>
       </c>
       <c r="BF44" s="13">
         <v>283250</v>
@@ -8680,14 +8680,14 @@
       </c>
       <c r="BH44" s="6">
         <f t="shared" si="22"/>
-        <v>65571</v>
+        <v>65578</v>
       </c>
       <c r="BI44" s="15">
-        <v>240374</v>
+        <v>240381</v>
       </c>
       <c r="BJ44" s="7">
         <f t="shared" si="23"/>
-        <v>0.84862842012356576</v>
+        <v>0.84865313327449254</v>
       </c>
     </row>
     <row r="45" spans="1:62" x14ac:dyDescent="0.3">
@@ -8874,14 +8874,14 @@
       </c>
       <c r="BH45" s="17">
         <f t="shared" si="22"/>
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="BI45" s="15">
-        <v>2681</v>
+        <v>2682</v>
       </c>
       <c r="BJ45" s="7">
         <f t="shared" si="23"/>
-        <v>0.88951559389515589</v>
+        <v>0.88984737889847376</v>
       </c>
     </row>
     <row r="46" spans="1:62" x14ac:dyDescent="0.3">
@@ -9111,15 +9111,15 @@
       </c>
       <c r="E47" s="8">
         <f>F47-D47</f>
-        <v>2360026</v>
+        <v>2360143</v>
       </c>
       <c r="F47" s="10">
         <f>SUM(F9:F46)</f>
-        <v>3455744</v>
+        <v>3455861</v>
       </c>
       <c r="G47" s="9">
         <f>F47/C47</f>
-        <v>0.600064421409787</v>
+        <v>0.60008473759562286</v>
       </c>
       <c r="H47" s="10">
         <f>SUM(H9:H46)</f>
@@ -9131,15 +9131,15 @@
       </c>
       <c r="J47" s="8">
         <f>K47-I47</f>
-        <v>2353472</v>
+        <v>2353585</v>
       </c>
       <c r="K47" s="10">
         <f>SUM(K9:K46)</f>
-        <v>3468704</v>
+        <v>3468817</v>
       </c>
       <c r="L47" s="9">
         <f>K47/H47</f>
-        <v>0.62336265730063267</v>
+        <v>0.62338296459127351</v>
       </c>
       <c r="M47" s="10">
         <f>SUM(M9:M46)</f>
@@ -9151,15 +9151,15 @@
       </c>
       <c r="O47" s="8">
         <f>P47-N47</f>
-        <v>4976126</v>
+        <v>4976308</v>
       </c>
       <c r="P47" s="10">
         <f>SUM(P9:P46)</f>
-        <v>8855067</v>
+        <v>8855249</v>
       </c>
       <c r="Q47" s="9">
         <f>P47/M47</f>
-        <v>0.85486830542055781</v>
+        <v>0.85488587570337848</v>
       </c>
       <c r="R47" s="10">
         <f>SUM(R9:R46)</f>
@@ -9171,15 +9171,15 @@
       </c>
       <c r="T47" s="8">
         <f>U47-S47</f>
-        <v>2484223</v>
+        <v>2484340</v>
       </c>
       <c r="U47" s="10">
         <f>SUM(U9:U46)</f>
-        <v>3513793</v>
+        <v>3513910</v>
       </c>
       <c r="V47" s="9">
         <f>U47/R47</f>
-        <v>0.68452370979939581</v>
+        <v>0.68454650262585048</v>
       </c>
       <c r="W47" s="10">
         <f>SUM(W9:W46)</f>
@@ -9191,15 +9191,15 @@
       </c>
       <c r="Y47" s="8">
         <f>Z47-X47</f>
-        <v>2446416</v>
+        <v>2446523</v>
       </c>
       <c r="Z47" s="10">
         <f>SUM(Z9:Z46)</f>
-        <v>3535344</v>
+        <v>3535451</v>
       </c>
       <c r="AA47" s="9">
         <f>Z47/W47</f>
-        <v>0.70910165261772451</v>
+        <v>0.70912311414362694</v>
       </c>
       <c r="AB47" s="10">
         <f>SUM(AB9:AB46)</f>
@@ -9211,15 +9211,15 @@
       </c>
       <c r="AD47" s="8">
         <f>AE47-AC47</f>
-        <v>5974089</v>
+        <v>5974282</v>
       </c>
       <c r="AE47" s="10">
         <f>SUM(AE9:AE46)</f>
-        <v>9059092</v>
+        <v>9059285</v>
       </c>
       <c r="AF47" s="9">
         <f>AE47/AB47</f>
-        <v>0.86492771401134294</v>
+        <v>0.86494614091867583</v>
       </c>
       <c r="AG47" s="10">
         <f>SUM(AG9:AG46)</f>
@@ -9231,15 +9231,15 @@
       </c>
       <c r="AI47" s="8">
         <f>AJ47-AH47</f>
-        <v>2598061</v>
+        <v>2598176</v>
       </c>
       <c r="AJ47" s="10">
         <f>SUM(AJ9:AJ46)</f>
-        <v>3583808</v>
+        <v>3583923</v>
       </c>
       <c r="AK47" s="9">
         <f>AJ47/AG47</f>
-        <v>0.73960717820617494</v>
+        <v>0.73963091129273917</v>
       </c>
       <c r="AL47" s="10">
         <f>SUM(AL9:AL46)</f>
@@ -9251,15 +9251,15 @@
       </c>
       <c r="AN47" s="8">
         <f>AO47-AM47</f>
-        <v>2369098</v>
+        <v>2369221</v>
       </c>
       <c r="AO47" s="10">
         <f>SUM(AO9:AO46)</f>
-        <v>3627180</v>
+        <v>3627303</v>
       </c>
       <c r="AP47" s="9">
         <f>AO47/AL47</f>
-        <v>0.77190548191687802</v>
+        <v>0.77193165772681183</v>
       </c>
       <c r="AQ47" s="10">
         <f>SUM(AQ9:AQ46)</f>
@@ -9271,15 +9271,15 @@
       </c>
       <c r="AS47" s="8">
         <f>AT47-AR47</f>
-        <v>3170777</v>
+        <v>3170972</v>
       </c>
       <c r="AT47" s="10">
         <f>SUM(AT9:AT46)</f>
-        <v>9226659</v>
+        <v>9226854</v>
       </c>
       <c r="AU47" s="9">
         <f>AT47/AQ47</f>
-        <v>0.88968132090015506</v>
+        <v>0.88970012379051611</v>
       </c>
       <c r="AV47" s="10">
         <f>SUM(AV9:AV46)</f>
@@ -9291,15 +9291,15 @@
       </c>
       <c r="AX47" s="8">
         <f>AY47-AW47</f>
-        <v>1737464</v>
+        <v>1737570</v>
       </c>
       <c r="AY47" s="10">
         <f>SUM(AY9:AY46)</f>
-        <v>3649801</v>
+        <v>3649907</v>
       </c>
       <c r="AZ47" s="9">
         <f>AY47/AV47</f>
-        <v>0.81787927802195981</v>
+        <v>0.81790303142754828</v>
       </c>
       <c r="BA47" s="10">
         <f>SUM(BA9:BA46)</f>
@@ -9311,15 +9311,15 @@
       </c>
       <c r="BC47" s="8">
         <f>BD47-BB47</f>
-        <v>869036</v>
+        <v>869149</v>
       </c>
       <c r="BD47" s="10">
         <f>SUM(BD9:BD46)</f>
-        <v>3647662</v>
+        <v>3647775</v>
       </c>
       <c r="BE47" s="9">
         <f>BD47/BA47</f>
-        <v>0.83393430329855234</v>
+        <v>0.83396013753875131</v>
       </c>
       <c r="BF47" s="10">
         <f>SUM(BF9:BF46)</f>
@@ -9331,15 +9331,15 @@
       </c>
       <c r="BH47" s="8">
         <f>BI47-BG47</f>
-        <v>2887354</v>
+        <v>2887636</v>
       </c>
       <c r="BI47" s="10">
         <f>SUM(BI9:BI46)</f>
-        <v>9179748</v>
+        <v>9180030</v>
       </c>
       <c r="BJ47" s="9">
         <f>BI47/BF47</f>
-        <v>0.88006140274517664</v>
+        <v>0.88008843805328907</v>
       </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.3">

--- a/gstdatabase/GSTR-1-2019-2020.xlsx
+++ b/gstdatabase/GSTR-1-2019-2020.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\May-26\GST Statistics Downloads 31st May 26\Downloads\GSTR 1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Jun-26\GST Statistics Downloads 31st May 26\Downloads\GSTR 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8763A217-B6B4-4FF8-9138-2DC3F70EEE84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BA013F5-61A0-43F3-821C-A173470FDBA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -185,10 +185,10 @@
     <t>Andaman and Nicobar Islands</t>
   </si>
   <si>
-    <t>Data Considered upto 31st May 2026</t>
+    <t>Data Considered upto 30th Jun 2026</t>
   </si>
   <si>
-    <t>Filing %age as on 31st May 2026</t>
+    <t>Filing %age as on 30th Jun 2026</t>
   </si>
 </sst>
 </file>
@@ -1107,14 +1107,14 @@
       </c>
       <c r="O9" s="6">
         <f>P9-N9</f>
-        <v>48847</v>
+        <v>48848</v>
       </c>
       <c r="P9" s="15">
-        <v>73788</v>
+        <v>73789</v>
       </c>
       <c r="Q9" s="7">
         <f>P9/M9</f>
-        <v>0.81198142482998437</v>
+        <v>0.81199242907762392</v>
       </c>
       <c r="R9" s="13">
         <v>43438</v>
@@ -1158,14 +1158,14 @@
       </c>
       <c r="AD9" s="6">
         <f>AE9-AC9</f>
-        <v>65089</v>
+        <v>65090</v>
       </c>
       <c r="AE9" s="15">
-        <v>73401</v>
+        <v>73402</v>
       </c>
       <c r="AF9" s="7">
         <f>AE9/AB9</f>
-        <v>0.79385044666998339</v>
+        <v>0.79386126192381734</v>
       </c>
       <c r="AG9" s="13">
         <v>42646</v>
@@ -1209,14 +1209,14 @@
       </c>
       <c r="AS9" s="6">
         <f>AT9-AR9</f>
-        <v>48895</v>
+        <v>48896</v>
       </c>
       <c r="AT9" s="15">
-        <v>73779</v>
+        <v>73780</v>
       </c>
       <c r="AU9" s="7">
         <f>AT9/AQ9</f>
-        <v>0.80025815128967182</v>
+        <v>0.80026899798251516</v>
       </c>
       <c r="AV9" s="13">
         <v>39353</v>
@@ -1472,14 +1472,14 @@
       </c>
       <c r="BH10" s="6">
         <f t="shared" ref="BH10:BH46" si="22">BI10-BG10</f>
-        <v>21750</v>
+        <v>21751</v>
       </c>
       <c r="BI10" s="15">
-        <v>78851</v>
+        <v>78852</v>
       </c>
       <c r="BJ10" s="7">
         <f t="shared" ref="BJ10:BJ46" si="23">BI10/BF10</f>
-        <v>0.91383306677792453</v>
+        <v>0.91384465614352273</v>
       </c>
     </row>
     <row r="11" spans="1:62" x14ac:dyDescent="0.3">
@@ -1582,14 +1582,14 @@
       </c>
       <c r="AD11" s="6">
         <f t="shared" si="10"/>
-        <v>145906</v>
+        <v>145907</v>
       </c>
       <c r="AE11" s="15">
-        <v>283050</v>
+        <v>283051</v>
       </c>
       <c r="AF11" s="7">
         <f t="shared" si="11"/>
-        <v>0.90986823706399134</v>
+        <v>0.90987145157816574</v>
       </c>
       <c r="AG11" s="13">
         <v>101504</v>
@@ -1921,14 +1921,14 @@
       </c>
       <c r="E13" s="6">
         <f t="shared" si="0"/>
-        <v>21649</v>
+        <v>21651</v>
       </c>
       <c r="F13" s="14">
-        <v>30725</v>
+        <v>30727</v>
       </c>
       <c r="G13" s="7">
         <f t="shared" si="1"/>
-        <v>0.48093479009485646</v>
+        <v>0.48096609585824751</v>
       </c>
       <c r="H13" s="13">
         <v>59731</v>
@@ -1955,14 +1955,14 @@
       </c>
       <c r="O13" s="6">
         <f t="shared" si="4"/>
-        <v>68074</v>
+        <v>68076</v>
       </c>
       <c r="P13" s="15">
-        <v>110022</v>
+        <v>110024</v>
       </c>
       <c r="Q13" s="7">
         <f t="shared" si="5"/>
-        <v>0.85010276459952716</v>
+        <v>0.85011821792276432</v>
       </c>
       <c r="R13" s="13">
         <v>54062</v>
@@ -1972,14 +1972,14 @@
       </c>
       <c r="T13" s="6">
         <f t="shared" si="6"/>
-        <v>22610</v>
+        <v>22611</v>
       </c>
       <c r="U13" s="14">
-        <v>31332</v>
+        <v>31333</v>
       </c>
       <c r="V13" s="7">
         <f t="shared" si="7"/>
-        <v>0.57955680514964303</v>
+        <v>0.57957530243054267</v>
       </c>
       <c r="W13" s="13">
         <v>51426</v>
@@ -1989,14 +1989,14 @@
       </c>
       <c r="Y13" s="6">
         <f t="shared" si="8"/>
-        <v>22436</v>
+        <v>22437</v>
       </c>
       <c r="Z13" s="14">
-        <v>31585</v>
+        <v>31586</v>
       </c>
       <c r="AA13" s="7">
         <f t="shared" si="9"/>
-        <v>0.61418348695212543</v>
+        <v>0.61420293236884071</v>
       </c>
       <c r="AB13" s="13">
         <v>131532</v>
@@ -2006,14 +2006,14 @@
       </c>
       <c r="AD13" s="6">
         <f t="shared" si="10"/>
-        <v>76398</v>
+        <v>76400</v>
       </c>
       <c r="AE13" s="15">
-        <v>113204</v>
+        <v>113206</v>
       </c>
       <c r="AF13" s="7">
         <f t="shared" si="11"/>
-        <v>0.86065748258978803</v>
+        <v>0.86067268801508379</v>
       </c>
       <c r="AG13" s="13">
         <v>48183</v>
@@ -2023,14 +2023,14 @@
       </c>
       <c r="AI13" s="6">
         <f t="shared" si="12"/>
-        <v>23605</v>
+        <v>23606</v>
       </c>
       <c r="AJ13" s="14">
-        <v>32141</v>
+        <v>32142</v>
       </c>
       <c r="AK13" s="7">
         <f t="shared" si="13"/>
-        <v>0.66706099661706408</v>
+        <v>0.66708175082497978</v>
       </c>
       <c r="AL13" s="13">
         <v>44607</v>
@@ -2040,14 +2040,14 @@
       </c>
       <c r="AN13" s="6">
         <f t="shared" si="14"/>
-        <v>21902</v>
+        <v>21904</v>
       </c>
       <c r="AO13" s="14">
-        <v>32581</v>
+        <v>32583</v>
       </c>
       <c r="AP13" s="7">
         <f t="shared" si="15"/>
-        <v>0.73040105812988998</v>
+        <v>0.73044589414217498</v>
       </c>
       <c r="AQ13" s="13">
         <v>128458</v>
@@ -2057,14 +2057,14 @@
       </c>
       <c r="AS13" s="6">
         <f t="shared" si="16"/>
-        <v>42773</v>
+        <v>42776</v>
       </c>
       <c r="AT13" s="15">
-        <v>115600</v>
+        <v>115603</v>
       </c>
       <c r="AU13" s="7">
         <f t="shared" si="17"/>
-        <v>0.89990502732410593</v>
+        <v>0.89992838126080121</v>
       </c>
       <c r="AV13" s="13">
         <v>43497</v>
@@ -2074,14 +2074,14 @@
       </c>
       <c r="AX13" s="6">
         <f t="shared" si="18"/>
-        <v>16346</v>
+        <v>16348</v>
       </c>
       <c r="AY13" s="14">
-        <v>32538</v>
+        <v>32540</v>
       </c>
       <c r="AZ13" s="7">
         <f t="shared" si="19"/>
-        <v>0.74805158976481134</v>
+        <v>0.74809756994735266</v>
       </c>
       <c r="BA13" s="13">
         <v>42767</v>
@@ -2091,14 +2091,14 @@
       </c>
       <c r="BC13" s="6">
         <f t="shared" si="20"/>
-        <v>8689</v>
+        <v>8691</v>
       </c>
       <c r="BD13" s="14">
-        <v>32556</v>
+        <v>32558</v>
       </c>
       <c r="BE13" s="7">
         <f t="shared" si="21"/>
-        <v>0.7612411438726121</v>
+        <v>0.76128790890172326</v>
       </c>
       <c r="BF13" s="13">
         <v>131773</v>
@@ -2108,14 +2108,14 @@
       </c>
       <c r="BH13" s="6">
         <f t="shared" si="22"/>
-        <v>38731</v>
+        <v>38735</v>
       </c>
       <c r="BI13" s="15">
-        <v>114884</v>
+        <v>114888</v>
       </c>
       <c r="BJ13" s="7">
         <f t="shared" si="23"/>
-        <v>0.87183262125018024</v>
+        <v>0.87186297648228395</v>
       </c>
     </row>
     <row r="14" spans="1:62" x14ac:dyDescent="0.3">
@@ -2133,14 +2133,14 @@
       </c>
       <c r="E14" s="6">
         <f t="shared" si="0"/>
-        <v>63920</v>
+        <v>63921</v>
       </c>
       <c r="F14" s="14">
-        <v>118681</v>
+        <v>118682</v>
       </c>
       <c r="G14" s="7">
         <f t="shared" si="1"/>
-        <v>0.58963721817585624</v>
+        <v>0.58964218642872046</v>
       </c>
       <c r="H14" s="13">
         <v>192033</v>
@@ -2150,14 +2150,14 @@
       </c>
       <c r="J14" s="6">
         <f t="shared" si="2"/>
-        <v>61981</v>
+        <v>61982</v>
       </c>
       <c r="K14" s="14">
-        <v>119025</v>
+        <v>119026</v>
       </c>
       <c r="L14" s="7">
         <f t="shared" si="3"/>
-        <v>0.61981534423770912</v>
+        <v>0.61982055167601402</v>
       </c>
       <c r="M14" s="13">
         <v>423764</v>
@@ -2184,14 +2184,14 @@
       </c>
       <c r="T14" s="6">
         <f t="shared" si="6"/>
-        <v>66505</v>
+        <v>66506</v>
       </c>
       <c r="U14" s="14">
-        <v>120055</v>
+        <v>120056</v>
       </c>
       <c r="V14" s="7">
         <f t="shared" si="7"/>
-        <v>0.6938552587472403</v>
+        <v>0.69386103822546896</v>
       </c>
       <c r="W14" s="13">
         <v>166832</v>
@@ -2201,14 +2201,14 @@
       </c>
       <c r="Y14" s="6">
         <f t="shared" si="8"/>
-        <v>63304</v>
+        <v>63305</v>
       </c>
       <c r="Z14" s="14">
-        <v>120654</v>
+        <v>120655</v>
       </c>
       <c r="AA14" s="7">
         <f t="shared" si="9"/>
-        <v>0.72320657907355901</v>
+        <v>0.72321257312745757</v>
       </c>
       <c r="AB14" s="13">
         <v>423483</v>
@@ -2235,14 +2235,14 @@
       </c>
       <c r="AI14" s="6">
         <f t="shared" si="12"/>
-        <v>72583</v>
+        <v>72584</v>
       </c>
       <c r="AJ14" s="14">
-        <v>121782</v>
+        <v>121783</v>
       </c>
       <c r="AK14" s="7">
         <f t="shared" si="13"/>
-        <v>0.75982205806198022</v>
+        <v>0.75982829726036794</v>
       </c>
       <c r="AL14" s="13">
         <v>154903</v>
@@ -2252,14 +2252,14 @@
       </c>
       <c r="AN14" s="6">
         <f t="shared" si="14"/>
-        <v>64411</v>
+        <v>64412</v>
       </c>
       <c r="AO14" s="14">
-        <v>123133</v>
+        <v>123134</v>
       </c>
       <c r="AP14" s="7">
         <f t="shared" si="15"/>
-        <v>0.79490390760669583</v>
+        <v>0.7949103632595883</v>
       </c>
       <c r="AQ14" s="13">
         <v>424443</v>
@@ -2269,14 +2269,14 @@
       </c>
       <c r="AS14" s="6">
         <f t="shared" si="16"/>
-        <v>103993</v>
+        <v>103994</v>
       </c>
       <c r="AT14" s="15">
-        <v>383964</v>
+        <v>383965</v>
       </c>
       <c r="AU14" s="7">
         <f t="shared" si="17"/>
-        <v>0.90463030371569331</v>
+        <v>0.90463265974465357</v>
       </c>
       <c r="AV14" s="13">
         <v>153606</v>
@@ -2286,14 +2286,14 @@
       </c>
       <c r="AX14" s="6">
         <f t="shared" si="18"/>
-        <v>43831</v>
+        <v>43832</v>
       </c>
       <c r="AY14" s="14">
-        <v>123815</v>
+        <v>123816</v>
       </c>
       <c r="AZ14" s="7">
         <f t="shared" si="19"/>
-        <v>0.8060557530304806</v>
+        <v>0.80606226319284402</v>
       </c>
       <c r="BA14" s="13">
         <v>146565</v>
@@ -2303,14 +2303,14 @@
       </c>
       <c r="BC14" s="6">
         <f t="shared" si="20"/>
-        <v>21105</v>
+        <v>21106</v>
       </c>
       <c r="BD14" s="14">
-        <v>123748</v>
+        <v>123749</v>
       </c>
       <c r="BE14" s="7">
         <f t="shared" si="21"/>
-        <v>0.84432163204039168</v>
+        <v>0.84432845495172792</v>
       </c>
       <c r="BF14" s="13">
         <v>423351</v>
@@ -2320,14 +2320,14 @@
       </c>
       <c r="BH14" s="6">
         <f t="shared" si="22"/>
-        <v>88262</v>
+        <v>88265</v>
       </c>
       <c r="BI14" s="15">
-        <v>383341</v>
+        <v>383344</v>
       </c>
       <c r="BJ14" s="7">
         <f t="shared" si="23"/>
-        <v>0.90549213300547304</v>
+        <v>0.90549921932391797</v>
       </c>
     </row>
     <row r="15" spans="1:62" x14ac:dyDescent="0.3">
@@ -2430,14 +2430,14 @@
       </c>
       <c r="AD15" s="6">
         <f t="shared" si="10"/>
-        <v>363279</v>
+        <v>363280</v>
       </c>
       <c r="AE15" s="15">
-        <v>629777</v>
+        <v>629778</v>
       </c>
       <c r="AF15" s="7">
         <f t="shared" si="11"/>
-        <v>0.82186598318884685</v>
+        <v>0.82186728819995902</v>
       </c>
       <c r="AG15" s="13">
         <v>285320</v>
@@ -2557,14 +2557,14 @@
       </c>
       <c r="E16" s="6">
         <f t="shared" si="0"/>
-        <v>70972</v>
+        <v>70975</v>
       </c>
       <c r="F16" s="14">
-        <v>122150</v>
+        <v>122153</v>
       </c>
       <c r="G16" s="7">
         <f t="shared" si="1"/>
-        <v>0.49554154597603228</v>
+        <v>0.4955537164601741</v>
       </c>
       <c r="H16" s="13">
         <v>236220</v>
@@ -2574,14 +2574,14 @@
       </c>
       <c r="J16" s="6">
         <f t="shared" si="2"/>
-        <v>67808</v>
+        <v>67811</v>
       </c>
       <c r="K16" s="14">
-        <v>122235</v>
+        <v>122238</v>
       </c>
       <c r="L16" s="7">
         <f t="shared" si="3"/>
-        <v>0.51746253492506988</v>
+        <v>0.51747523495046988</v>
       </c>
       <c r="M16" s="13">
         <v>560439</v>
@@ -2591,14 +2591,14 @@
       </c>
       <c r="O16" s="6">
         <f t="shared" si="4"/>
-        <v>226145</v>
+        <v>226150</v>
       </c>
       <c r="P16" s="15">
-        <v>489306</v>
+        <v>489311</v>
       </c>
       <c r="Q16" s="7">
         <f t="shared" si="5"/>
-        <v>0.87307628484099076</v>
+        <v>0.87308520641853971</v>
       </c>
       <c r="R16" s="13">
         <v>205814</v>
@@ -2608,14 +2608,14 @@
       </c>
       <c r="T16" s="6">
         <f t="shared" si="6"/>
-        <v>72872</v>
+        <v>72875</v>
       </c>
       <c r="U16" s="14">
-        <v>123837</v>
+        <v>123840</v>
       </c>
       <c r="V16" s="7">
         <f t="shared" si="7"/>
-        <v>0.60169376232909322</v>
+        <v>0.60170833859698558</v>
       </c>
       <c r="W16" s="13">
         <v>193923</v>
@@ -2625,14 +2625,14 @@
       </c>
       <c r="Y16" s="6">
         <f t="shared" si="8"/>
-        <v>69745</v>
+        <v>69748</v>
       </c>
       <c r="Z16" s="14">
-        <v>123965</v>
+        <v>123968</v>
       </c>
       <c r="AA16" s="7">
         <f t="shared" si="9"/>
-        <v>0.63924856773049099</v>
+        <v>0.63926403778819429</v>
       </c>
       <c r="AB16" s="13">
         <v>559918</v>
@@ -2642,14 +2642,14 @@
       </c>
       <c r="AD16" s="6">
         <f t="shared" si="10"/>
-        <v>300033</v>
+        <v>300038</v>
       </c>
       <c r="AE16" s="15">
-        <v>499296</v>
+        <v>499301</v>
       </c>
       <c r="AF16" s="7">
         <f t="shared" si="11"/>
-        <v>0.89173057483417217</v>
+        <v>0.89173950471319019</v>
       </c>
       <c r="AG16" s="13">
         <v>184413</v>
@@ -2659,14 +2659,14 @@
       </c>
       <c r="AI16" s="6">
         <f t="shared" si="12"/>
-        <v>81875</v>
+        <v>81879</v>
       </c>
       <c r="AJ16" s="14">
-        <v>125169</v>
+        <v>125173</v>
       </c>
       <c r="AK16" s="7">
         <f t="shared" si="13"/>
-        <v>0.6787428218184185</v>
+        <v>0.6787645122632352</v>
       </c>
       <c r="AL16" s="13">
         <v>173833</v>
@@ -2676,14 +2676,14 @@
       </c>
       <c r="AN16" s="6">
         <f t="shared" si="14"/>
-        <v>72245</v>
+        <v>72250</v>
       </c>
       <c r="AO16" s="14">
-        <v>127956</v>
+        <v>127961</v>
       </c>
       <c r="AP16" s="7">
         <f t="shared" si="15"/>
-        <v>0.7360857834818475</v>
+        <v>0.73611454672012799</v>
       </c>
       <c r="AQ16" s="13">
         <v>541872</v>
@@ -2693,14 +2693,14 @@
       </c>
       <c r="AS16" s="6">
         <f t="shared" si="16"/>
-        <v>139194</v>
+        <v>139195</v>
       </c>
       <c r="AT16" s="15">
-        <v>507937</v>
+        <v>507938</v>
       </c>
       <c r="AU16" s="7">
         <f t="shared" si="17"/>
-        <v>0.93737450910916231</v>
+        <v>0.93737635456343937</v>
       </c>
       <c r="AV16" s="13">
         <v>152784</v>
@@ -2710,14 +2710,14 @@
       </c>
       <c r="AX16" s="6">
         <f t="shared" si="18"/>
-        <v>47564</v>
+        <v>47568</v>
       </c>
       <c r="AY16" s="14">
-        <v>126483</v>
+        <v>126487</v>
       </c>
       <c r="AZ16" s="7">
         <f t="shared" si="19"/>
-        <v>0.82785501099591585</v>
+        <v>0.82788119174782704</v>
       </c>
       <c r="BA16" s="13">
         <v>150750</v>
@@ -2727,14 +2727,14 @@
       </c>
       <c r="BC16" s="6">
         <f t="shared" si="20"/>
-        <v>24125</v>
+        <v>24129</v>
       </c>
       <c r="BD16" s="14">
-        <v>126193</v>
+        <v>126197</v>
       </c>
       <c r="BE16" s="7">
         <f t="shared" si="21"/>
-        <v>0.83710116086235486</v>
+        <v>0.83712769485903815</v>
       </c>
       <c r="BF16" s="13">
         <v>552190</v>
@@ -2744,14 +2744,14 @@
       </c>
       <c r="BH16" s="6">
         <f t="shared" si="22"/>
-        <v>134280</v>
+        <v>134282</v>
       </c>
       <c r="BI16" s="15">
-        <v>511735</v>
+        <v>511737</v>
       </c>
       <c r="BJ16" s="7">
         <f t="shared" si="23"/>
-        <v>0.92673717379887355</v>
+        <v>0.92674079574059653</v>
       </c>
     </row>
     <row r="17" spans="1:62" x14ac:dyDescent="0.3">
@@ -2769,14 +2769,14 @@
       </c>
       <c r="E17" s="6">
         <f t="shared" si="0"/>
-        <v>210829</v>
+        <v>210830</v>
       </c>
       <c r="F17" s="14">
-        <v>290687</v>
+        <v>290688</v>
       </c>
       <c r="G17" s="7">
         <f t="shared" si="1"/>
-        <v>0.55426384672880091</v>
+        <v>0.55426575346644902</v>
       </c>
       <c r="H17" s="13">
         <v>496559</v>
@@ -2786,14 +2786,14 @@
       </c>
       <c r="J17" s="6">
         <f t="shared" si="2"/>
-        <v>213169</v>
+        <v>213170</v>
       </c>
       <c r="K17" s="14">
-        <v>291885</v>
+        <v>291886</v>
       </c>
       <c r="L17" s="7">
         <f t="shared" si="3"/>
-        <v>0.58781534520570566</v>
+        <v>0.58781735906508592</v>
       </c>
       <c r="M17" s="13">
         <v>1118687</v>
@@ -2803,14 +2803,14 @@
       </c>
       <c r="O17" s="6">
         <f t="shared" si="4"/>
-        <v>588933</v>
+        <v>588935</v>
       </c>
       <c r="P17" s="15">
-        <v>956751</v>
+        <v>956753</v>
       </c>
       <c r="Q17" s="7">
         <f t="shared" si="5"/>
-        <v>0.85524458584036467</v>
+        <v>0.85524637365053857</v>
       </c>
       <c r="R17" s="13">
         <v>453407</v>
@@ -2854,14 +2854,14 @@
       </c>
       <c r="AD17" s="6">
         <f t="shared" si="10"/>
-        <v>697979</v>
+        <v>697983</v>
       </c>
       <c r="AE17" s="15">
-        <v>983313</v>
+        <v>983317</v>
       </c>
       <c r="AF17" s="7">
         <f t="shared" si="11"/>
-        <v>0.87318514335036523</v>
+        <v>0.87318869536337984</v>
       </c>
       <c r="AG17" s="13">
         <v>411675</v>
@@ -2905,14 +2905,14 @@
       </c>
       <c r="AS17" s="6">
         <f t="shared" si="16"/>
-        <v>381270</v>
+        <v>381274</v>
       </c>
       <c r="AT17" s="15">
-        <v>1005693</v>
+        <v>1005697</v>
       </c>
       <c r="AU17" s="7">
         <f t="shared" si="17"/>
-        <v>0.89208269984405963</v>
+        <v>0.89208624797534763</v>
       </c>
       <c r="AV17" s="13">
         <v>386848</v>
@@ -2939,14 +2939,14 @@
       </c>
       <c r="BC17" s="6">
         <f t="shared" si="20"/>
-        <v>93339</v>
+        <v>93340</v>
       </c>
       <c r="BD17" s="14">
-        <v>308645</v>
+        <v>308646</v>
       </c>
       <c r="BE17" s="7">
         <f t="shared" si="21"/>
-        <v>0.81255726034898534</v>
+        <v>0.81255989300870879</v>
       </c>
       <c r="BF17" s="13">
         <v>1155076</v>
@@ -2956,14 +2956,14 @@
       </c>
       <c r="BH17" s="6">
         <f t="shared" si="22"/>
-        <v>370536</v>
+        <v>370541</v>
       </c>
       <c r="BI17" s="15">
-        <v>1003169</v>
+        <v>1003174</v>
       </c>
       <c r="BJ17" s="7">
         <f t="shared" si="23"/>
-        <v>0.86848744151899959</v>
+        <v>0.86849177023849511</v>
       </c>
     </row>
     <row r="18" spans="1:62" x14ac:dyDescent="0.3">
@@ -3168,14 +3168,14 @@
       </c>
       <c r="BH18" s="6">
         <f t="shared" si="22"/>
-        <v>125697</v>
+        <v>125698</v>
       </c>
       <c r="BI18" s="15">
-        <v>270249</v>
+        <v>270250</v>
       </c>
       <c r="BJ18" s="7">
         <f t="shared" si="23"/>
-        <v>0.84363439980770372</v>
+        <v>0.84363752150066029</v>
       </c>
     </row>
     <row r="19" spans="1:62" x14ac:dyDescent="0.3">
@@ -3405,14 +3405,14 @@
       </c>
       <c r="E20" s="6">
         <f t="shared" si="0"/>
-        <v>2845</v>
+        <v>2846</v>
       </c>
       <c r="F20" s="14">
-        <v>3280</v>
+        <v>3281</v>
       </c>
       <c r="G20" s="7">
         <f t="shared" si="1"/>
-        <v>0.38862559241706163</v>
+        <v>0.38874407582938386</v>
       </c>
       <c r="H20" s="13">
         <v>8306</v>
@@ -3422,14 +3422,14 @@
       </c>
       <c r="J20" s="6">
         <f t="shared" si="2"/>
-        <v>2845</v>
+        <v>2846</v>
       </c>
       <c r="K20" s="14">
-        <v>3273</v>
+        <v>3274</v>
       </c>
       <c r="L20" s="7">
         <f t="shared" si="3"/>
-        <v>0.3940524921743318</v>
+        <v>0.39417288706958825</v>
       </c>
       <c r="M20" s="13">
         <v>11143</v>
@@ -3685,14 +3685,14 @@
       </c>
       <c r="Y21" s="6">
         <f t="shared" si="8"/>
-        <v>2754</v>
+        <v>2755</v>
       </c>
       <c r="Z21" s="14">
-        <v>3375</v>
+        <v>3376</v>
       </c>
       <c r="AA21" s="7">
         <f t="shared" si="9"/>
-        <v>0.65969507427677876</v>
+        <v>0.65989053948397181</v>
       </c>
       <c r="AB21" s="13">
         <v>6718</v>
@@ -3736,14 +3736,14 @@
       </c>
       <c r="AN21" s="6">
         <f t="shared" si="14"/>
-        <v>2790</v>
+        <v>2791</v>
       </c>
       <c r="AO21" s="14">
-        <v>3498</v>
+        <v>3499</v>
       </c>
       <c r="AP21" s="7">
         <f t="shared" si="15"/>
-        <v>0.69625796178343946</v>
+        <v>0.69645700636942676</v>
       </c>
       <c r="AQ21" s="13">
         <v>6694</v>
@@ -3770,14 +3770,14 @@
       </c>
       <c r="AX21" s="6">
         <f t="shared" si="18"/>
-        <v>2548</v>
+        <v>2549</v>
       </c>
       <c r="AY21" s="14">
-        <v>3546</v>
+        <v>3547</v>
       </c>
       <c r="AZ21" s="7">
         <f t="shared" si="19"/>
-        <v>0.72</v>
+        <v>0.72020304568527915</v>
       </c>
       <c r="BA21" s="13">
         <v>4794</v>
@@ -4109,14 +4109,14 @@
       </c>
       <c r="Y23" s="6">
         <f t="shared" si="8"/>
-        <v>2182</v>
+        <v>2183</v>
       </c>
       <c r="Z23" s="14">
-        <v>2726</v>
+        <v>2727</v>
       </c>
       <c r="AA23" s="7">
         <f t="shared" si="9"/>
-        <v>0.62941583929808353</v>
+        <v>0.62964673285615336</v>
       </c>
       <c r="AB23" s="13">
         <v>5800</v>
@@ -4126,14 +4126,14 @@
       </c>
       <c r="AD23" s="6">
         <f t="shared" si="10"/>
-        <v>2769</v>
+        <v>2770</v>
       </c>
       <c r="AE23" s="15">
-        <v>4168</v>
+        <v>4169</v>
       </c>
       <c r="AF23" s="7">
         <f t="shared" si="11"/>
-        <v>0.71862068965517245</v>
+        <v>0.71879310344827585</v>
       </c>
       <c r="AG23" s="13">
         <v>4378</v>
@@ -4143,14 +4143,14 @@
       </c>
       <c r="AI23" s="6">
         <f t="shared" si="12"/>
-        <v>2212</v>
+        <v>2213</v>
       </c>
       <c r="AJ23" s="14">
-        <v>2743</v>
+        <v>2744</v>
       </c>
       <c r="AK23" s="7">
         <f t="shared" si="13"/>
-        <v>0.62654179990863412</v>
+        <v>0.62677021470991323</v>
       </c>
       <c r="AL23" s="13">
         <v>4406</v>
@@ -4160,14 +4160,14 @@
       </c>
       <c r="AN23" s="6">
         <f t="shared" si="14"/>
-        <v>2129</v>
+        <v>2130</v>
       </c>
       <c r="AO23" s="14">
-        <v>2793</v>
+        <v>2794</v>
       </c>
       <c r="AP23" s="7">
         <f t="shared" si="15"/>
-        <v>0.63390830685428956</v>
+        <v>0.63413527008624604</v>
       </c>
       <c r="AQ23" s="13">
         <v>6083</v>
@@ -4177,14 +4177,14 @@
       </c>
       <c r="AS23" s="6">
         <f t="shared" si="16"/>
-        <v>2635</v>
+        <v>2636</v>
       </c>
       <c r="AT23" s="15">
-        <v>4303</v>
+        <v>4304</v>
       </c>
       <c r="AU23" s="7">
         <f t="shared" si="17"/>
-        <v>0.70738122636856815</v>
+        <v>0.70754561893802403</v>
       </c>
       <c r="AV23" s="13">
         <v>4479</v>
@@ -4194,14 +4194,14 @@
       </c>
       <c r="AX23" s="6">
         <f t="shared" si="18"/>
-        <v>2069</v>
+        <v>2070</v>
       </c>
       <c r="AY23" s="14">
-        <v>2873</v>
+        <v>2874</v>
       </c>
       <c r="AZ23" s="7">
         <f t="shared" si="19"/>
-        <v>0.64143782094217461</v>
+        <v>0.64166108506363029</v>
       </c>
       <c r="BA23" s="13">
         <v>4501</v>
@@ -4211,14 +4211,14 @@
       </c>
       <c r="BC23" s="6">
         <f t="shared" si="20"/>
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="BD23" s="14">
-        <v>2888</v>
+        <v>2889</v>
       </c>
       <c r="BE23" s="7">
         <f t="shared" si="21"/>
-        <v>0.6416351921795157</v>
+        <v>0.64185736502999335</v>
       </c>
       <c r="BF23" s="13">
         <v>6256</v>
@@ -4228,14 +4228,14 @@
       </c>
       <c r="BH23" s="6">
         <f t="shared" si="22"/>
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="BI23" s="15">
-        <v>4436</v>
+        <v>4437</v>
       </c>
       <c r="BJ23" s="7">
         <f t="shared" si="23"/>
-        <v>0.70907928388746799</v>
+        <v>0.70923913043478259</v>
       </c>
     </row>
     <row r="24" spans="1:62" x14ac:dyDescent="0.3">
@@ -4499,14 +4499,14 @@
       </c>
       <c r="O25" s="6">
         <f t="shared" si="4"/>
-        <v>11574</v>
+        <v>11576</v>
       </c>
       <c r="P25" s="15">
-        <v>17313</v>
+        <v>17315</v>
       </c>
       <c r="Q25" s="7">
         <f t="shared" si="5"/>
-        <v>0.69591607042366754</v>
+        <v>0.69599646273816218</v>
       </c>
       <c r="R25" s="13">
         <v>16556</v>
@@ -4550,14 +4550,14 @@
       </c>
       <c r="AD25" s="6">
         <f t="shared" si="10"/>
-        <v>12086</v>
+        <v>12089</v>
       </c>
       <c r="AE25" s="15">
-        <v>18079</v>
+        <v>18082</v>
       </c>
       <c r="AF25" s="7">
         <f t="shared" si="11"/>
-        <v>0.69162203519510324</v>
+        <v>0.69173680183626629</v>
       </c>
       <c r="AG25" s="13">
         <v>16090</v>
@@ -4601,14 +4601,14 @@
       </c>
       <c r="AS25" s="6">
         <f t="shared" si="16"/>
-        <v>10628</v>
+        <v>10630</v>
       </c>
       <c r="AT25" s="15">
-        <v>17984</v>
+        <v>17986</v>
       </c>
       <c r="AU25" s="7">
         <f t="shared" si="17"/>
-        <v>0.68049038898138337</v>
+        <v>0.68056606629332528</v>
       </c>
       <c r="AV25" s="13">
         <v>15911</v>
@@ -4652,14 +4652,14 @@
       </c>
       <c r="BH25" s="6">
         <f t="shared" si="22"/>
-        <v>7381</v>
+        <v>7384</v>
       </c>
       <c r="BI25" s="15">
-        <v>17608</v>
+        <v>17611</v>
       </c>
       <c r="BJ25" s="7">
         <f t="shared" si="23"/>
-        <v>0.65932749194937468</v>
+        <v>0.65943982625627195</v>
       </c>
     </row>
     <row r="26" spans="1:62" x14ac:dyDescent="0.3">
@@ -4762,14 +4762,14 @@
       </c>
       <c r="AD26" s="6">
         <f t="shared" si="10"/>
-        <v>96136</v>
+        <v>96137</v>
       </c>
       <c r="AE26" s="15">
-        <v>119662</v>
+        <v>119663</v>
       </c>
       <c r="AF26" s="7">
         <f t="shared" si="11"/>
-        <v>0.71628586307831366</v>
+        <v>0.71629184898748344</v>
       </c>
       <c r="AG26" s="13">
         <v>98900</v>
@@ -4813,14 +4813,14 @@
       </c>
       <c r="AS26" s="6">
         <f t="shared" si="16"/>
-        <v>62920</v>
+        <v>62922</v>
       </c>
       <c r="AT26" s="15">
-        <v>120758</v>
+        <v>120760</v>
       </c>
       <c r="AU26" s="7">
         <f t="shared" si="17"/>
-        <v>0.82594986491570055</v>
+        <v>0.82596354433842889</v>
       </c>
       <c r="AV26" s="13">
         <v>71728</v>
@@ -4864,14 +4864,14 @@
       </c>
       <c r="BH26" s="6">
         <f t="shared" si="22"/>
-        <v>57950</v>
+        <v>57954</v>
       </c>
       <c r="BI26" s="15">
-        <v>119805</v>
+        <v>119809</v>
       </c>
       <c r="BJ26" s="7">
         <f t="shared" si="23"/>
-        <v>0.82109959700633273</v>
+        <v>0.82112701154151935</v>
       </c>
     </row>
     <row r="27" spans="1:62" x14ac:dyDescent="0.3">
@@ -4889,14 +4889,14 @@
       </c>
       <c r="E27" s="6">
         <f t="shared" si="0"/>
-        <v>125131</v>
+        <v>125132</v>
       </c>
       <c r="F27" s="14">
-        <v>173522</v>
+        <v>173523</v>
       </c>
       <c r="G27" s="7">
         <f t="shared" si="1"/>
-        <v>0.56842512153255498</v>
+        <v>0.56842839734266282</v>
       </c>
       <c r="H27" s="13">
         <v>294634</v>
@@ -4906,14 +4906,14 @@
       </c>
       <c r="J27" s="6">
         <f t="shared" si="2"/>
-        <v>123782</v>
+        <v>123784</v>
       </c>
       <c r="K27" s="14">
-        <v>173882</v>
+        <v>173884</v>
       </c>
       <c r="L27" s="7">
         <f t="shared" si="3"/>
-        <v>0.5901627103457171</v>
+        <v>0.59016949842855881</v>
       </c>
       <c r="M27" s="13">
         <v>593424</v>
@@ -4923,14 +4923,14 @@
       </c>
       <c r="O27" s="6">
         <f t="shared" si="4"/>
-        <v>303566</v>
+        <v>303568</v>
       </c>
       <c r="P27" s="15">
-        <v>504383</v>
+        <v>504385</v>
       </c>
       <c r="Q27" s="7">
         <f t="shared" si="5"/>
-        <v>0.84995382728032576</v>
+        <v>0.84995719755183474</v>
       </c>
       <c r="R27" s="13">
         <v>274036</v>
@@ -4940,14 +4940,14 @@
       </c>
       <c r="T27" s="6">
         <f t="shared" si="6"/>
-        <v>126749</v>
+        <v>126751</v>
       </c>
       <c r="U27" s="14">
-        <v>176089</v>
+        <v>176091</v>
       </c>
       <c r="V27" s="7">
         <f t="shared" si="7"/>
-        <v>0.64257615787706723</v>
+        <v>0.64258345618823809</v>
       </c>
       <c r="W27" s="13">
         <v>268694</v>
@@ -4957,14 +4957,14 @@
       </c>
       <c r="Y27" s="6">
         <f t="shared" si="8"/>
-        <v>125987</v>
+        <v>125989</v>
       </c>
       <c r="Z27" s="14">
-        <v>177089</v>
+        <v>177091</v>
       </c>
       <c r="AA27" s="7">
         <f t="shared" si="9"/>
-        <v>0.65907314640446013</v>
+        <v>0.65908058981592443</v>
       </c>
       <c r="AB27" s="13">
         <v>607620</v>
@@ -4974,14 +4974,14 @@
       </c>
       <c r="AD27" s="6">
         <f t="shared" si="10"/>
-        <v>355304</v>
+        <v>355306</v>
       </c>
       <c r="AE27" s="15">
-        <v>515678</v>
+        <v>515680</v>
       </c>
       <c r="AF27" s="7">
         <f t="shared" si="11"/>
-        <v>0.84868503340903856</v>
+        <v>0.84868832493992952</v>
       </c>
       <c r="AG27" s="13">
         <v>264148</v>
@@ -4991,14 +4991,14 @@
       </c>
       <c r="AI27" s="6">
         <f t="shared" si="12"/>
-        <v>131916</v>
+        <v>131918</v>
       </c>
       <c r="AJ27" s="14">
-        <v>178851</v>
+        <v>178853</v>
       </c>
       <c r="AK27" s="7">
         <f t="shared" si="13"/>
-        <v>0.67708633039053867</v>
+        <v>0.6770939019034784</v>
       </c>
       <c r="AL27" s="13">
         <v>259704</v>
@@ -5008,14 +5008,14 @@
       </c>
       <c r="AN27" s="6">
         <f t="shared" si="14"/>
-        <v>122461</v>
+        <v>122463</v>
       </c>
       <c r="AO27" s="14">
-        <v>180534</v>
+        <v>180536</v>
       </c>
       <c r="AP27" s="7">
         <f t="shared" si="15"/>
-        <v>0.69515294335089184</v>
+        <v>0.69516064442596182</v>
       </c>
       <c r="AQ27" s="13">
         <v>611342</v>
@@ -5025,14 +5025,14 @@
       </c>
       <c r="AS27" s="6">
         <f t="shared" si="16"/>
-        <v>208699</v>
+        <v>208701</v>
       </c>
       <c r="AT27" s="15">
-        <v>521681</v>
+        <v>521683</v>
       </c>
       <c r="AU27" s="7">
         <f t="shared" si="17"/>
-        <v>0.85333741179241729</v>
+        <v>0.85334068328366119</v>
       </c>
       <c r="AV27" s="13">
         <v>246718</v>
@@ -5042,14 +5042,14 @@
       </c>
       <c r="AX27" s="6">
         <f t="shared" si="18"/>
-        <v>93713</v>
+        <v>93714</v>
       </c>
       <c r="AY27" s="14">
-        <v>181460</v>
+        <v>181461</v>
       </c>
       <c r="AZ27" s="7">
         <f t="shared" si="19"/>
-        <v>0.73549558605371312</v>
+        <v>0.73549963926426121</v>
       </c>
       <c r="BA27" s="13">
         <v>240337</v>
@@ -5059,14 +5059,14 @@
       </c>
       <c r="BC27" s="6">
         <f t="shared" si="20"/>
-        <v>51793</v>
+        <v>51794</v>
       </c>
       <c r="BD27" s="14">
-        <v>181278</v>
+        <v>181279</v>
       </c>
       <c r="BE27" s="7">
         <f t="shared" si="21"/>
-        <v>0.75426588498649816</v>
+        <v>0.75427004581067414</v>
       </c>
       <c r="BF27" s="13">
         <v>611625</v>
@@ -5076,14 +5076,14 @@
       </c>
       <c r="BH27" s="6">
         <f t="shared" si="22"/>
-        <v>179899</v>
+        <v>179900</v>
       </c>
       <c r="BI27" s="15">
-        <v>515498</v>
+        <v>515499</v>
       </c>
       <c r="BJ27" s="7">
         <f t="shared" si="23"/>
-        <v>0.84283343552013079</v>
+        <v>0.84283507050889028</v>
       </c>
     </row>
     <row r="28" spans="1:62" x14ac:dyDescent="0.3">
@@ -5135,14 +5135,14 @@
       </c>
       <c r="O28" s="6">
         <f t="shared" si="4"/>
-        <v>85478</v>
+        <v>85479</v>
       </c>
       <c r="P28" s="15">
-        <v>124079</v>
+        <v>124080</v>
       </c>
       <c r="Q28" s="7">
         <f t="shared" si="5"/>
-        <v>0.8282977303070761</v>
+        <v>0.82830440587449938</v>
       </c>
       <c r="R28" s="13">
         <v>79004</v>
@@ -5186,14 +5186,14 @@
       </c>
       <c r="AD28" s="6">
         <f t="shared" si="10"/>
-        <v>97401</v>
+        <v>97402</v>
       </c>
       <c r="AE28" s="15">
-        <v>127609</v>
+        <v>127610</v>
       </c>
       <c r="AF28" s="7">
         <f t="shared" si="11"/>
-        <v>0.84327214094075043</v>
+        <v>0.8432787491904894</v>
       </c>
       <c r="AG28" s="13">
         <v>73311</v>
@@ -5237,14 +5237,14 @@
       </c>
       <c r="AS28" s="6">
         <f t="shared" si="16"/>
-        <v>57297</v>
+        <v>57298</v>
       </c>
       <c r="AT28" s="15">
-        <v>129661</v>
+        <v>129662</v>
       </c>
       <c r="AU28" s="7">
         <f t="shared" si="17"/>
-        <v>0.87963013215380859</v>
+        <v>0.87963691623022444</v>
       </c>
       <c r="AV28" s="13">
         <v>63116</v>
@@ -5254,14 +5254,14 @@
       </c>
       <c r="AX28" s="6">
         <f t="shared" si="18"/>
-        <v>31289</v>
+        <v>31290</v>
       </c>
       <c r="AY28" s="14">
-        <v>54048</v>
+        <v>54049</v>
       </c>
       <c r="AZ28" s="7">
         <f t="shared" si="19"/>
-        <v>0.85632803092718168</v>
+        <v>0.8563438747702643</v>
       </c>
       <c r="BA28" s="13">
         <v>59716</v>
@@ -5271,14 +5271,14 @@
       </c>
       <c r="BC28" s="6">
         <f t="shared" si="20"/>
-        <v>17480</v>
+        <v>17481</v>
       </c>
       <c r="BD28" s="14">
-        <v>53758</v>
+        <v>53759</v>
       </c>
       <c r="BE28" s="7">
         <f t="shared" si="21"/>
-        <v>0.90022774465804811</v>
+        <v>0.90024449058878697</v>
       </c>
       <c r="BF28" s="13">
         <v>143561</v>
@@ -5288,14 +5288,14 @@
       </c>
       <c r="BH28" s="6">
         <f t="shared" si="22"/>
-        <v>48852</v>
+        <v>48854</v>
       </c>
       <c r="BI28" s="15">
-        <v>128168</v>
+        <v>128170</v>
       </c>
       <c r="BJ28" s="7">
         <f t="shared" si="23"/>
-        <v>0.89277728631034892</v>
+        <v>0.89279121767053726</v>
       </c>
     </row>
     <row r="29" spans="1:62" x14ac:dyDescent="0.3">
@@ -5500,14 +5500,14 @@
       </c>
       <c r="BH29" s="6">
         <f t="shared" si="22"/>
-        <v>74085</v>
+        <v>74086</v>
       </c>
       <c r="BI29" s="15">
-        <v>193575</v>
+        <v>193576</v>
       </c>
       <c r="BJ29" s="7">
         <f t="shared" si="23"/>
-        <v>0.86778082118089017</v>
+        <v>0.86778530409873178</v>
       </c>
     </row>
     <row r="30" spans="1:62" x14ac:dyDescent="0.3">
@@ -5525,14 +5525,14 @@
       </c>
       <c r="E30" s="6">
         <f t="shared" si="0"/>
-        <v>29502</v>
+        <v>29503</v>
       </c>
       <c r="F30" s="14">
-        <v>37489</v>
+        <v>37490</v>
       </c>
       <c r="G30" s="7">
         <f t="shared" si="1"/>
-        <v>0.59083387180659086</v>
+        <v>0.59084963199949569</v>
       </c>
       <c r="H30" s="13">
         <v>60187</v>
@@ -5542,14 +5542,14 @@
       </c>
       <c r="J30" s="6">
         <f t="shared" si="2"/>
-        <v>29153</v>
+        <v>29154</v>
       </c>
       <c r="K30" s="14">
-        <v>37678</v>
+        <v>37679</v>
       </c>
       <c r="L30" s="7">
         <f t="shared" si="3"/>
-        <v>0.62601558476082875</v>
+        <v>0.62603219964444146</v>
       </c>
       <c r="M30" s="13">
         <v>104773</v>
@@ -5559,14 +5559,14 @@
       </c>
       <c r="O30" s="6">
         <f t="shared" si="4"/>
-        <v>65841</v>
+        <v>65843</v>
       </c>
       <c r="P30" s="15">
-        <v>93523</v>
+        <v>93525</v>
       </c>
       <c r="Q30" s="7">
         <f t="shared" si="5"/>
-        <v>0.89262500835138825</v>
+        <v>0.89264409723879246</v>
       </c>
       <c r="R30" s="13">
         <v>53849</v>
@@ -5576,14 +5576,14 @@
       </c>
       <c r="T30" s="6">
         <f t="shared" si="6"/>
-        <v>30050</v>
+        <v>30051</v>
       </c>
       <c r="U30" s="14">
-        <v>38131</v>
+        <v>38132</v>
       </c>
       <c r="V30" s="7">
         <f t="shared" si="7"/>
-        <v>0.70810971420082081</v>
+        <v>0.70812828464781152</v>
       </c>
       <c r="W30" s="13">
         <v>52544</v>
@@ -5593,14 +5593,14 @@
       </c>
       <c r="Y30" s="6">
         <f t="shared" si="8"/>
-        <v>29905</v>
+        <v>29907</v>
       </c>
       <c r="Z30" s="14">
-        <v>38354</v>
+        <v>38356</v>
       </c>
       <c r="AA30" s="7">
         <f t="shared" si="9"/>
-        <v>0.72994062119366621</v>
+        <v>0.72997868453105963</v>
       </c>
       <c r="AB30" s="13">
         <v>107458</v>
@@ -5610,14 +5610,14 @@
       </c>
       <c r="AD30" s="6">
         <f t="shared" si="10"/>
-        <v>74170</v>
+        <v>74172</v>
       </c>
       <c r="AE30" s="15">
-        <v>95866</v>
+        <v>95868</v>
       </c>
       <c r="AF30" s="7">
         <f t="shared" si="11"/>
-        <v>0.89212529546427444</v>
+        <v>0.89214390738707217</v>
       </c>
       <c r="AG30" s="13">
         <v>51279</v>
@@ -5627,14 +5627,14 @@
       </c>
       <c r="AI30" s="6">
         <f t="shared" si="12"/>
-        <v>31066</v>
+        <v>31067</v>
       </c>
       <c r="AJ30" s="14">
-        <v>38902</v>
+        <v>38903</v>
       </c>
       <c r="AK30" s="7">
         <f t="shared" si="13"/>
-        <v>0.75863413873125451</v>
+        <v>0.75865363989157353</v>
       </c>
       <c r="AL30" s="13">
         <v>48984</v>
@@ -5644,14 +5644,14 @@
       </c>
       <c r="AN30" s="6">
         <f t="shared" si="14"/>
-        <v>28869</v>
+        <v>28871</v>
       </c>
       <c r="AO30" s="14">
-        <v>39188</v>
+        <v>39190</v>
       </c>
       <c r="AP30" s="7">
         <f t="shared" si="15"/>
-        <v>0.80001633186346566</v>
+        <v>0.80005716152212969</v>
       </c>
       <c r="AQ30" s="13">
         <v>105112</v>
@@ -5661,14 +5661,14 @@
       </c>
       <c r="AS30" s="6">
         <f t="shared" si="16"/>
-        <v>41215</v>
+        <v>41219</v>
       </c>
       <c r="AT30" s="15">
-        <v>97359</v>
+        <v>97363</v>
       </c>
       <c r="AU30" s="7">
         <f t="shared" si="17"/>
-        <v>0.9262405814749981</v>
+        <v>0.92627863612147043</v>
       </c>
       <c r="AV30" s="13">
         <v>46049</v>
@@ -5678,14 +5678,14 @@
       </c>
       <c r="AX30" s="6">
         <f t="shared" si="18"/>
-        <v>21822</v>
+        <v>21824</v>
       </c>
       <c r="AY30" s="14">
-        <v>39048</v>
+        <v>39050</v>
       </c>
       <c r="AZ30" s="7">
         <f t="shared" si="19"/>
-        <v>0.84796629677083102</v>
+        <v>0.84800972876718284</v>
       </c>
       <c r="BA30" s="13">
         <v>45889</v>
@@ -5695,14 +5695,14 @@
       </c>
       <c r="BC30" s="6">
         <f t="shared" si="20"/>
-        <v>13564</v>
+        <v>13565</v>
       </c>
       <c r="BD30" s="14">
-        <v>38971</v>
+        <v>38972</v>
       </c>
       <c r="BE30" s="7">
         <f t="shared" si="21"/>
-        <v>0.84924491708252525</v>
+        <v>0.84926670879731525</v>
       </c>
       <c r="BF30" s="13">
         <v>107069</v>
@@ -5712,14 +5712,14 @@
       </c>
       <c r="BH30" s="6">
         <f t="shared" si="22"/>
-        <v>37221</v>
+        <v>37223</v>
       </c>
       <c r="BI30" s="15">
-        <v>96264</v>
+        <v>96266</v>
       </c>
       <c r="BJ30" s="7">
         <f t="shared" si="23"/>
-        <v>0.89908376841102466</v>
+        <v>0.89910244795412309</v>
       </c>
     </row>
     <row r="31" spans="1:62" x14ac:dyDescent="0.3">
@@ -5754,14 +5754,14 @@
       </c>
       <c r="J31" s="6">
         <f t="shared" si="2"/>
-        <v>76090</v>
+        <v>76091</v>
       </c>
       <c r="K31" s="14">
-        <v>102643</v>
+        <v>102644</v>
       </c>
       <c r="L31" s="7">
         <f t="shared" si="3"/>
-        <v>0.61707487164688768</v>
+        <v>0.61708088350226642</v>
       </c>
       <c r="M31" s="13">
         <v>353290</v>
@@ -5873,14 +5873,14 @@
       </c>
       <c r="AS31" s="6">
         <f t="shared" si="16"/>
-        <v>115103</v>
+        <v>115104</v>
       </c>
       <c r="AT31" s="15">
-        <v>329434</v>
+        <v>329435</v>
       </c>
       <c r="AU31" s="7">
         <f t="shared" si="17"/>
-        <v>0.92863183294244989</v>
+        <v>0.92863465181309757</v>
       </c>
       <c r="AV31" s="13">
         <v>121996</v>
@@ -5890,14 +5890,14 @@
       </c>
       <c r="AX31" s="6">
         <f t="shared" si="18"/>
-        <v>53862</v>
+        <v>53863</v>
       </c>
       <c r="AY31" s="14">
-        <v>106632</v>
+        <v>106633</v>
       </c>
       <c r="AZ31" s="7">
         <f t="shared" si="19"/>
-        <v>0.87406144463752911</v>
+        <v>0.87406964162759437</v>
       </c>
       <c r="BA31" s="13">
         <v>118866</v>
@@ -5907,14 +5907,14 @@
       </c>
       <c r="BC31" s="6">
         <f t="shared" si="20"/>
-        <v>27959</v>
+        <v>27960</v>
       </c>
       <c r="BD31" s="14">
-        <v>105927</v>
+        <v>105928</v>
       </c>
       <c r="BE31" s="7">
         <f t="shared" si="21"/>
-        <v>0.89114633284538891</v>
+        <v>0.89115474568000941</v>
       </c>
       <c r="BF31" s="13">
         <v>351474</v>
@@ -5949,14 +5949,14 @@
       </c>
       <c r="E32" s="6">
         <f t="shared" si="0"/>
-        <v>139154</v>
+        <v>139156</v>
       </c>
       <c r="F32" s="14">
-        <v>250992</v>
+        <v>250994</v>
       </c>
       <c r="G32" s="7">
         <f t="shared" si="1"/>
-        <v>0.62873117503832632</v>
+        <v>0.6287361850081663</v>
       </c>
       <c r="H32" s="13">
         <v>382894</v>
@@ -5966,14 +5966,14 @@
       </c>
       <c r="J32" s="6">
         <f t="shared" si="2"/>
-        <v>135156</v>
+        <v>135158</v>
       </c>
       <c r="K32" s="14">
-        <v>251285</v>
+        <v>251287</v>
       </c>
       <c r="L32" s="7">
         <f t="shared" si="3"/>
-        <v>0.65627823888595804</v>
+        <v>0.65628346226370748</v>
       </c>
       <c r="M32" s="13">
         <v>877062</v>
@@ -5983,14 +5983,14 @@
       </c>
       <c r="O32" s="6">
         <f t="shared" si="4"/>
-        <v>334431</v>
+        <v>334438</v>
       </c>
       <c r="P32" s="15">
-        <v>803160</v>
+        <v>803167</v>
       </c>
       <c r="Q32" s="7">
         <f t="shared" si="5"/>
-        <v>0.91573913816811126</v>
+        <v>0.91574711935986286</v>
       </c>
       <c r="R32" s="13">
         <v>340947</v>
@@ -6000,14 +6000,14 @@
       </c>
       <c r="T32" s="6">
         <f t="shared" si="6"/>
-        <v>151423</v>
+        <v>151425</v>
       </c>
       <c r="U32" s="14">
-        <v>253232</v>
+        <v>253234</v>
       </c>
       <c r="V32" s="7">
         <f t="shared" si="7"/>
-        <v>0.74273127494889235</v>
+        <v>0.74273714096325827</v>
       </c>
       <c r="W32" s="13">
         <v>329795</v>
@@ -6017,14 +6017,14 @@
       </c>
       <c r="Y32" s="6">
         <f t="shared" si="8"/>
-        <v>140554</v>
+        <v>140556</v>
       </c>
       <c r="Z32" s="14">
-        <v>253987</v>
+        <v>253989</v>
       </c>
       <c r="AA32" s="7">
         <f t="shared" si="9"/>
-        <v>0.77013599357176432</v>
+        <v>0.77014205794508706</v>
       </c>
       <c r="AB32" s="13">
         <v>884817</v>
@@ -6034,14 +6034,14 @@
       </c>
       <c r="AD32" s="6">
         <f t="shared" si="10"/>
-        <v>442917</v>
+        <v>442924</v>
       </c>
       <c r="AE32" s="15">
-        <v>818558</v>
+        <v>818565</v>
       </c>
       <c r="AF32" s="7">
         <f t="shared" si="11"/>
-        <v>0.92511558887317946</v>
+        <v>0.9251235001135828</v>
       </c>
       <c r="AG32" s="13">
         <v>320380</v>
@@ -6051,14 +6051,14 @@
       </c>
       <c r="AI32" s="6">
         <f t="shared" si="12"/>
-        <v>164317</v>
+        <v>164321</v>
       </c>
       <c r="AJ32" s="14">
-        <v>256042</v>
+        <v>256046</v>
       </c>
       <c r="AK32" s="7">
         <f t="shared" si="13"/>
-        <v>0.79918222111242898</v>
+        <v>0.79919470628628508</v>
       </c>
       <c r="AL32" s="13">
         <v>311565</v>
@@ -6068,14 +6068,14 @@
       </c>
       <c r="AN32" s="6">
         <f t="shared" si="14"/>
-        <v>130385</v>
+        <v>130387</v>
       </c>
       <c r="AO32" s="14">
-        <v>258444</v>
+        <v>258446</v>
       </c>
       <c r="AP32" s="7">
         <f t="shared" si="15"/>
-        <v>0.82950267199460792</v>
+        <v>0.82950909120087302</v>
       </c>
       <c r="AQ32" s="13">
         <v>877839</v>
@@ -6085,14 +6085,14 @@
       </c>
       <c r="AS32" s="6">
         <f t="shared" si="16"/>
-        <v>171133</v>
+        <v>171137</v>
       </c>
       <c r="AT32" s="15">
-        <v>833005</v>
+        <v>833009</v>
       </c>
       <c r="AU32" s="7">
         <f t="shared" si="17"/>
-        <v>0.94892685332959692</v>
+        <v>0.94893140997381065</v>
       </c>
       <c r="AV32" s="13">
         <v>297941</v>
@@ -6102,14 +6102,14 @@
       </c>
       <c r="AX32" s="6">
         <f t="shared" si="18"/>
-        <v>79199</v>
+        <v>79200</v>
       </c>
       <c r="AY32" s="14">
-        <v>259933</v>
+        <v>259934</v>
       </c>
       <c r="AZ32" s="7">
         <f t="shared" si="19"/>
-        <v>0.87243111891280489</v>
+        <v>0.8724344752820189</v>
       </c>
       <c r="BA32" s="13">
         <v>294413</v>
@@ -6119,14 +6119,14 @@
       </c>
       <c r="BC32" s="6">
         <f t="shared" si="20"/>
-        <v>35889</v>
+        <v>35890</v>
       </c>
       <c r="BD32" s="14">
-        <v>260528</v>
+        <v>260529</v>
       </c>
       <c r="BE32" s="7">
         <f t="shared" si="21"/>
-        <v>0.88490657681556184</v>
+        <v>0.88490997340470701</v>
       </c>
       <c r="BF32" s="13">
         <v>893063</v>
@@ -6136,14 +6136,14 @@
       </c>
       <c r="BH32" s="6">
         <f t="shared" si="22"/>
-        <v>159648</v>
+        <v>159653</v>
       </c>
       <c r="BI32" s="15">
-        <v>839701</v>
+        <v>839706</v>
       </c>
       <c r="BJ32" s="7">
         <f t="shared" si="23"/>
-        <v>0.94024833634357263</v>
+        <v>0.94025393505273425</v>
       </c>
     </row>
     <row r="33" spans="1:62" x14ac:dyDescent="0.3">
@@ -6585,14 +6585,14 @@
       </c>
       <c r="E35" s="6">
         <f t="shared" si="0"/>
-        <v>222274</v>
+        <v>222275</v>
       </c>
       <c r="F35" s="14">
-        <v>358688</v>
+        <v>358689</v>
       </c>
       <c r="G35" s="7">
         <f t="shared" si="1"/>
-        <v>0.50862796313706471</v>
+        <v>0.50862938116042522</v>
       </c>
       <c r="H35" s="13">
         <v>678572</v>
@@ -6602,14 +6602,14 @@
       </c>
       <c r="J35" s="6">
         <f t="shared" si="2"/>
-        <v>218740</v>
+        <v>218741</v>
       </c>
       <c r="K35" s="14">
-        <v>358790</v>
+        <v>358791</v>
       </c>
       <c r="L35" s="7">
         <f t="shared" si="3"/>
-        <v>0.52874271263771566</v>
+        <v>0.52874418632068521</v>
       </c>
       <c r="M35" s="13">
         <v>1405014</v>
@@ -6619,14 +6619,14 @@
       </c>
       <c r="O35" s="6">
         <f t="shared" si="4"/>
-        <v>635991</v>
+        <v>635995</v>
       </c>
       <c r="P35" s="15">
-        <v>1205958</v>
+        <v>1205962</v>
       </c>
       <c r="Q35" s="7">
         <f t="shared" si="5"/>
-        <v>0.85832454338533282</v>
+        <v>0.85832739033205363</v>
       </c>
       <c r="R35" s="13">
         <v>600814</v>
@@ -6636,14 +6636,14 @@
       </c>
       <c r="T35" s="6">
         <f t="shared" si="6"/>
-        <v>231472</v>
+        <v>231474</v>
       </c>
       <c r="U35" s="14">
-        <v>362734</v>
+        <v>362736</v>
       </c>
       <c r="V35" s="7">
         <f t="shared" si="7"/>
-        <v>0.60373759599476706</v>
+        <v>0.60374092481200503</v>
       </c>
       <c r="W35" s="13">
         <v>577797</v>
@@ -6653,14 +6653,14 @@
       </c>
       <c r="Y35" s="6">
         <f t="shared" si="8"/>
-        <v>225106</v>
+        <v>225107</v>
       </c>
       <c r="Z35" s="14">
-        <v>364109</v>
+        <v>364110</v>
       </c>
       <c r="AA35" s="7">
         <f t="shared" si="9"/>
-        <v>0.63016768865189676</v>
+        <v>0.63016941936354809</v>
       </c>
       <c r="AB35" s="13">
         <v>1416919</v>
@@ -6670,14 +6670,14 @@
       </c>
       <c r="AD35" s="6">
         <f t="shared" si="10"/>
-        <v>775503</v>
+        <v>775506</v>
       </c>
       <c r="AE35" s="15">
-        <v>1227794</v>
+        <v>1227797</v>
       </c>
       <c r="AF35" s="7">
         <f t="shared" si="11"/>
-        <v>0.86652377447122952</v>
+        <v>0.86652589174116512</v>
       </c>
       <c r="AG35" s="13">
         <v>553324</v>
@@ -6687,14 +6687,14 @@
       </c>
       <c r="AI35" s="6">
         <f t="shared" si="12"/>
-        <v>245052</v>
+        <v>245054</v>
       </c>
       <c r="AJ35" s="14">
-        <v>367717</v>
+        <v>367719</v>
       </c>
       <c r="AK35" s="7">
         <f t="shared" si="13"/>
-        <v>0.66456000462658404</v>
+        <v>0.6645636191453832</v>
       </c>
       <c r="AL35" s="13">
         <v>528988</v>
@@ -6704,14 +6704,14 @@
       </c>
       <c r="AN35" s="6">
         <f t="shared" si="14"/>
-        <v>217296</v>
+        <v>217298</v>
       </c>
       <c r="AO35" s="14">
-        <v>372200</v>
+        <v>372202</v>
       </c>
       <c r="AP35" s="7">
         <f t="shared" si="15"/>
-        <v>0.70360764327357139</v>
+        <v>0.70361142407767285</v>
       </c>
       <c r="AQ35" s="13">
         <v>1379433</v>
@@ -6721,14 +6721,14 @@
       </c>
       <c r="AS35" s="6">
         <f t="shared" si="16"/>
-        <v>367234</v>
+        <v>367242</v>
       </c>
       <c r="AT35" s="15">
-        <v>1242130</v>
+        <v>1242138</v>
       </c>
       <c r="AU35" s="7">
         <f t="shared" si="17"/>
-        <v>0.90046417622312935</v>
+        <v>0.90046997570741016</v>
       </c>
       <c r="AV35" s="13">
         <v>465114</v>
@@ -6738,14 +6738,14 @@
       </c>
       <c r="AX35" s="6">
         <f t="shared" si="18"/>
-        <v>150899</v>
+        <v>150902</v>
       </c>
       <c r="AY35" s="14">
-        <v>372272</v>
+        <v>372275</v>
       </c>
       <c r="AZ35" s="7">
         <f t="shared" si="19"/>
-        <v>0.80038872190473731</v>
+        <v>0.80039517193634246</v>
       </c>
       <c r="BA35" s="13">
         <v>457177</v>
@@ -6755,14 +6755,14 @@
       </c>
       <c r="BC35" s="6">
         <f t="shared" si="20"/>
-        <v>87742</v>
+        <v>87745</v>
       </c>
       <c r="BD35" s="14">
-        <v>371925</v>
+        <v>371928</v>
       </c>
       <c r="BE35" s="7">
         <f t="shared" si="21"/>
-        <v>0.81352517733831753</v>
+        <v>0.81353173934821743</v>
       </c>
       <c r="BF35" s="13">
         <v>1380633</v>
@@ -6772,14 +6772,14 @@
       </c>
       <c r="BH35" s="6">
         <f t="shared" si="22"/>
-        <v>474405</v>
+        <v>474414</v>
       </c>
       <c r="BI35" s="15">
-        <v>1225967</v>
+        <v>1225976</v>
       </c>
       <c r="BJ35" s="7">
         <f t="shared" si="23"/>
-        <v>0.8879745739816447</v>
+        <v>0.88798109273065329</v>
       </c>
     </row>
     <row r="36" spans="1:62" x14ac:dyDescent="0.3">
@@ -6797,14 +6797,14 @@
       </c>
       <c r="E36" s="6">
         <f t="shared" si="0"/>
-        <v>256600</v>
+        <v>256603</v>
       </c>
       <c r="F36" s="14">
-        <v>364971</v>
+        <v>364974</v>
       </c>
       <c r="G36" s="7">
         <f t="shared" si="1"/>
-        <v>0.73408665324421685</v>
+        <v>0.73409268731256672</v>
       </c>
       <c r="H36" s="13">
         <v>485610</v>
@@ -6814,14 +6814,14 @@
       </c>
       <c r="J36" s="6">
         <f t="shared" si="2"/>
-        <v>259090</v>
+        <v>259093</v>
       </c>
       <c r="K36" s="14">
-        <v>366704</v>
+        <v>366707</v>
       </c>
       <c r="L36" s="7">
         <f t="shared" si="3"/>
-        <v>0.75514095673482839</v>
+        <v>0.75514713453182591</v>
       </c>
       <c r="M36" s="13">
         <v>710827</v>
@@ -6831,14 +6831,14 @@
       </c>
       <c r="O36" s="6">
         <f t="shared" si="4"/>
-        <v>374004</v>
+        <v>374009</v>
       </c>
       <c r="P36" s="15">
-        <v>612186</v>
+        <v>612191</v>
       </c>
       <c r="Q36" s="7">
         <f t="shared" si="5"/>
-        <v>0.86123065105855579</v>
+        <v>0.86123768511888266</v>
       </c>
       <c r="R36" s="13">
         <v>464623</v>
@@ -6848,14 +6848,14 @@
       </c>
       <c r="T36" s="6">
         <f t="shared" si="6"/>
-        <v>276273</v>
+        <v>276277</v>
       </c>
       <c r="U36" s="14">
-        <v>372859</v>
+        <v>372863</v>
       </c>
       <c r="V36" s="7">
         <f t="shared" si="7"/>
-        <v>0.80249793918940737</v>
+        <v>0.8025065483198206</v>
       </c>
       <c r="W36" s="13">
         <v>451202</v>
@@ -6865,14 +6865,14 @@
       </c>
       <c r="Y36" s="6">
         <f t="shared" si="8"/>
-        <v>271111</v>
+        <v>271115</v>
       </c>
       <c r="Z36" s="14">
-        <v>375734</v>
+        <v>375738</v>
       </c>
       <c r="AA36" s="7">
         <f t="shared" si="9"/>
-        <v>0.83274010310237989</v>
+        <v>0.83274896831131062</v>
       </c>
       <c r="AB36" s="13">
         <v>709880</v>
@@ -6882,14 +6882,14 @@
       </c>
       <c r="AD36" s="6">
         <f t="shared" si="10"/>
-        <v>427609</v>
+        <v>427615</v>
       </c>
       <c r="AE36" s="15">
-        <v>628839</v>
+        <v>628845</v>
       </c>
       <c r="AF36" s="7">
         <f t="shared" si="11"/>
-        <v>0.88583845156927932</v>
+        <v>0.88584690370203412</v>
       </c>
       <c r="AG36" s="13">
         <v>448411</v>
@@ -6899,14 +6899,14 @@
       </c>
       <c r="AI36" s="6">
         <f t="shared" si="12"/>
-        <v>282650</v>
+        <v>282654</v>
       </c>
       <c r="AJ36" s="14">
-        <v>381898</v>
+        <v>381902</v>
       </c>
       <c r="AK36" s="7">
         <f t="shared" si="13"/>
-        <v>0.85166956207586342</v>
+        <v>0.85167848246363265</v>
       </c>
       <c r="AL36" s="13">
         <v>443261</v>
@@ -6916,14 +6916,14 @@
       </c>
       <c r="AN36" s="6">
         <f t="shared" si="14"/>
-        <v>260456</v>
+        <v>260459</v>
       </c>
       <c r="AO36" s="14">
-        <v>386319</v>
+        <v>386322</v>
       </c>
       <c r="AP36" s="7">
         <f t="shared" si="15"/>
-        <v>0.87153843897838967</v>
+        <v>0.87154520699993909</v>
       </c>
       <c r="AQ36" s="13">
         <v>723207</v>
@@ -6933,14 +6933,14 @@
       </c>
       <c r="AS36" s="6">
         <f t="shared" si="16"/>
-        <v>261060</v>
+        <v>261068</v>
       </c>
       <c r="AT36" s="15">
-        <v>644764</v>
+        <v>644772</v>
       </c>
       <c r="AU36" s="7">
         <f t="shared" si="17"/>
-        <v>0.89153451224891356</v>
+        <v>0.89154557408874635</v>
       </c>
       <c r="AV36" s="13">
         <v>443230</v>
@@ -6950,14 +6950,14 @@
       </c>
       <c r="AX36" s="6">
         <f t="shared" si="18"/>
-        <v>196219</v>
+        <v>196222</v>
       </c>
       <c r="AY36" s="14">
-        <v>390289</v>
+        <v>390292</v>
       </c>
       <c r="AZ36" s="7">
         <f t="shared" si="19"/>
-        <v>0.88055637028179501</v>
+        <v>0.88056313877670733</v>
       </c>
       <c r="BA36" s="13">
         <v>443322</v>
@@ -6967,14 +6967,14 @@
       </c>
       <c r="BC36" s="6">
         <f t="shared" si="20"/>
-        <v>88456</v>
+        <v>88461</v>
       </c>
       <c r="BD36" s="14">
-        <v>389674</v>
+        <v>389679</v>
       </c>
       <c r="BE36" s="7">
         <f t="shared" si="21"/>
-        <v>0.87898638010295005</v>
+        <v>0.87899765858676082</v>
       </c>
       <c r="BF36" s="13">
         <v>734800</v>
@@ -6984,14 +6984,14 @@
       </c>
       <c r="BH36" s="6">
         <f t="shared" si="22"/>
-        <v>185095</v>
+        <v>185102</v>
       </c>
       <c r="BI36" s="15">
-        <v>637970</v>
+        <v>637977</v>
       </c>
       <c r="BJ36" s="7">
         <f t="shared" si="23"/>
-        <v>0.86822264561785523</v>
+        <v>0.86823217201959713</v>
       </c>
     </row>
     <row r="37" spans="1:62" x14ac:dyDescent="0.3">
@@ -7433,14 +7433,14 @@
       </c>
       <c r="E39" s="6">
         <f t="shared" si="0"/>
-        <v>107053</v>
+        <v>107054</v>
       </c>
       <c r="F39" s="14">
-        <v>146412</v>
+        <v>146413</v>
       </c>
       <c r="G39" s="7">
         <f t="shared" si="1"/>
-        <v>0.72367263416997007</v>
+        <v>0.72367757688391543</v>
       </c>
       <c r="H39" s="13">
         <v>195184</v>
@@ -7450,14 +7450,14 @@
       </c>
       <c r="J39" s="6">
         <f t="shared" si="2"/>
-        <v>109488</v>
+        <v>109489</v>
       </c>
       <c r="K39" s="14">
-        <v>147126</v>
+        <v>147127</v>
       </c>
       <c r="L39" s="7">
         <f t="shared" si="3"/>
-        <v>0.75378104762685461</v>
+        <v>0.7537861709976228</v>
       </c>
       <c r="M39" s="13">
         <v>295913</v>
@@ -7484,14 +7484,14 @@
       </c>
       <c r="T39" s="6">
         <f t="shared" si="6"/>
-        <v>118720</v>
+        <v>118723</v>
       </c>
       <c r="U39" s="14">
-        <v>149151</v>
+        <v>149154</v>
       </c>
       <c r="V39" s="7">
         <f t="shared" si="7"/>
-        <v>0.78842036822658146</v>
+        <v>0.78843622639115751</v>
       </c>
       <c r="W39" s="13">
         <v>187045</v>
@@ -7501,14 +7501,14 @@
       </c>
       <c r="Y39" s="6">
         <f t="shared" si="8"/>
-        <v>120608</v>
+        <v>120612</v>
       </c>
       <c r="Z39" s="14">
-        <v>150227</v>
+        <v>150231</v>
       </c>
       <c r="AA39" s="7">
         <f t="shared" si="9"/>
-        <v>0.80315966745970224</v>
+        <v>0.80318105268785589</v>
       </c>
       <c r="AB39" s="13">
         <v>301836</v>
@@ -7518,14 +7518,14 @@
       </c>
       <c r="AD39" s="6">
         <f t="shared" si="10"/>
-        <v>185924</v>
+        <v>185928</v>
       </c>
       <c r="AE39" s="15">
-        <v>268523</v>
+        <v>268527</v>
       </c>
       <c r="AF39" s="7">
         <f t="shared" si="11"/>
-        <v>0.88963211810387099</v>
+        <v>0.88964537033355862</v>
       </c>
       <c r="AG39" s="13">
         <v>184754</v>
@@ -7535,14 +7535,14 @@
       </c>
       <c r="AI39" s="6">
         <f t="shared" si="12"/>
-        <v>115707</v>
+        <v>115710</v>
       </c>
       <c r="AJ39" s="14">
-        <v>152277</v>
+        <v>152280</v>
       </c>
       <c r="AK39" s="7">
         <f t="shared" si="13"/>
-        <v>0.82421490197776504</v>
+        <v>0.82423113978587748</v>
       </c>
       <c r="AL39" s="13">
         <v>180486</v>
@@ -7552,14 +7552,14 @@
       </c>
       <c r="AN39" s="6">
         <f t="shared" si="14"/>
-        <v>98542</v>
+        <v>98545</v>
       </c>
       <c r="AO39" s="14">
-        <v>153968</v>
+        <v>153971</v>
       </c>
       <c r="AP39" s="7">
         <f t="shared" si="15"/>
-        <v>0.8530744766907129</v>
+        <v>0.85309109847855236</v>
       </c>
       <c r="AQ39" s="13">
         <v>302709</v>
@@ -7569,14 +7569,14 @@
       </c>
       <c r="AS39" s="6">
         <f t="shared" si="16"/>
-        <v>112536</v>
+        <v>112539</v>
       </c>
       <c r="AT39" s="15">
-        <v>273386</v>
+        <v>273389</v>
       </c>
       <c r="AU39" s="7">
         <f t="shared" si="17"/>
-        <v>0.90313139021304289</v>
+        <v>0.90314130072115462</v>
       </c>
       <c r="AV39" s="13">
         <v>175450</v>
@@ -7586,14 +7586,14 @@
       </c>
       <c r="AX39" s="6">
         <f t="shared" si="18"/>
-        <v>78380</v>
+        <v>78383</v>
       </c>
       <c r="AY39" s="14">
-        <v>155015</v>
+        <v>155018</v>
       </c>
       <c r="AZ39" s="7">
         <f t="shared" si="19"/>
-        <v>0.88352807067540606</v>
+        <v>0.88354516956397833</v>
       </c>
       <c r="BA39" s="13">
         <v>174499</v>
@@ -7603,14 +7603,14 @@
       </c>
       <c r="BC39" s="6">
         <f t="shared" si="20"/>
-        <v>36470</v>
+        <v>36472</v>
       </c>
       <c r="BD39" s="14">
-        <v>155250</v>
+        <v>155252</v>
       </c>
       <c r="BE39" s="7">
         <f t="shared" si="21"/>
-        <v>0.88968991226310756</v>
+        <v>0.88970137364684043</v>
       </c>
       <c r="BF39" s="13">
         <v>304085</v>
@@ -7620,14 +7620,14 @@
       </c>
       <c r="BH39" s="6">
         <f t="shared" si="22"/>
-        <v>83593</v>
+        <v>83598</v>
       </c>
       <c r="BI39" s="15">
-        <v>273279</v>
+        <v>273284</v>
       </c>
       <c r="BJ39" s="7">
         <f t="shared" si="23"/>
-        <v>0.89869279971060723</v>
+        <v>0.89870924248154294</v>
       </c>
     </row>
     <row r="40" spans="1:62" x14ac:dyDescent="0.3">
@@ -7645,14 +7645,14 @@
       </c>
       <c r="E40" s="6">
         <f t="shared" si="0"/>
-        <v>374865</v>
+        <v>374874</v>
       </c>
       <c r="F40" s="14">
-        <v>520742</v>
+        <v>520751</v>
       </c>
       <c r="G40" s="7">
         <f t="shared" si="1"/>
-        <v>0.76428871257019237</v>
+        <v>0.76430192179551537</v>
       </c>
       <c r="H40" s="13">
         <v>679109</v>
@@ -7662,14 +7662,14 @@
       </c>
       <c r="J40" s="6">
         <f t="shared" si="2"/>
-        <v>379415</v>
+        <v>379426</v>
       </c>
       <c r="K40" s="14">
-        <v>523709</v>
+        <v>523720</v>
       </c>
       <c r="L40" s="7">
         <f t="shared" si="3"/>
-        <v>0.77117075462112861</v>
+        <v>0.77118695231546042</v>
       </c>
       <c r="M40" s="13">
         <v>894344</v>
@@ -7679,14 +7679,14 @@
       </c>
       <c r="O40" s="6">
         <f t="shared" si="4"/>
-        <v>479407</v>
+        <v>479426</v>
       </c>
       <c r="P40" s="15">
-        <v>752503</v>
+        <v>752522</v>
       </c>
       <c r="Q40" s="7">
         <f t="shared" si="5"/>
-        <v>0.84140218976143411</v>
+        <v>0.84142343438319034</v>
       </c>
       <c r="R40" s="13">
         <v>670695</v>
@@ -7696,14 +7696,14 @@
       </c>
       <c r="T40" s="6">
         <f t="shared" si="6"/>
-        <v>398490</v>
+        <v>398503</v>
       </c>
       <c r="U40" s="14">
-        <v>530967</v>
+        <v>530980</v>
       </c>
       <c r="V40" s="7">
         <f t="shared" si="7"/>
-        <v>0.79166685304050277</v>
+        <v>0.79168623591945664</v>
       </c>
       <c r="W40" s="13">
         <v>664170</v>
@@ -7713,14 +7713,14 @@
       </c>
       <c r="Y40" s="6">
         <f t="shared" si="8"/>
-        <v>396971</v>
+        <v>396985</v>
       </c>
       <c r="Z40" s="14">
-        <v>534908</v>
+        <v>534922</v>
       </c>
       <c r="AA40" s="7">
         <f t="shared" si="9"/>
-        <v>0.80537814113856387</v>
+        <v>0.80539922007919662</v>
       </c>
       <c r="AB40" s="13">
         <v>900385</v>
@@ -7730,14 +7730,14 @@
       </c>
       <c r="AD40" s="6">
         <f t="shared" si="10"/>
-        <v>541852</v>
+        <v>541877</v>
       </c>
       <c r="AE40" s="15">
-        <v>769328</v>
+        <v>769353</v>
       </c>
       <c r="AF40" s="7">
         <f t="shared" si="11"/>
-        <v>0.85444337699983897</v>
+        <v>0.85447114289998172</v>
       </c>
       <c r="AG40" s="13">
         <v>654051</v>
@@ -7747,14 +7747,14 @@
       </c>
       <c r="AI40" s="6">
         <f t="shared" si="12"/>
-        <v>407259</v>
+        <v>407274</v>
       </c>
       <c r="AJ40" s="14">
-        <v>542092</v>
+        <v>542107</v>
       </c>
       <c r="AK40" s="7">
         <f t="shared" si="13"/>
-        <v>0.82882221722770855</v>
+        <v>0.82884515121909452</v>
       </c>
       <c r="AL40" s="13">
         <v>640748</v>
@@ -7764,14 +7764,14 @@
       </c>
       <c r="AN40" s="6">
         <f t="shared" si="14"/>
-        <v>372381</v>
+        <v>372392</v>
       </c>
       <c r="AO40" s="14">
-        <v>547325</v>
+        <v>547336</v>
       </c>
       <c r="AP40" s="7">
         <f t="shared" si="15"/>
-        <v>0.85419696979155613</v>
+        <v>0.85421413722711581</v>
       </c>
       <c r="AQ40" s="13">
         <v>877850</v>
@@ -7781,14 +7781,14 @@
       </c>
       <c r="AS40" s="6">
         <f t="shared" si="16"/>
-        <v>284003</v>
+        <v>284021</v>
       </c>
       <c r="AT40" s="15">
-        <v>786519</v>
+        <v>786537</v>
       </c>
       <c r="AU40" s="7">
         <f t="shared" si="17"/>
-        <v>0.89596058552144442</v>
+        <v>0.89598109016346761</v>
       </c>
       <c r="AV40" s="13">
         <v>620078</v>
@@ -7798,14 +7798,14 @@
       </c>
       <c r="AX40" s="6">
         <f t="shared" si="18"/>
-        <v>257012</v>
+        <v>257026</v>
       </c>
       <c r="AY40" s="14">
-        <v>553858</v>
+        <v>553872</v>
       </c>
       <c r="AZ40" s="7">
         <f t="shared" si="19"/>
-        <v>0.89320698363754236</v>
+        <v>0.89322956144227017</v>
       </c>
       <c r="BA40" s="13">
         <v>613352</v>
@@ -7815,14 +7815,14 @@
       </c>
       <c r="BC40" s="6">
         <f t="shared" si="20"/>
-        <v>101357</v>
+        <v>101371</v>
       </c>
       <c r="BD40" s="14">
-        <v>555591</v>
+        <v>555605</v>
       </c>
       <c r="BE40" s="7">
         <f t="shared" si="21"/>
-        <v>0.90582732264670207</v>
+        <v>0.90585014803897268</v>
       </c>
       <c r="BF40" s="13">
         <v>876639</v>
@@ -7832,14 +7832,14 @@
       </c>
       <c r="BH40" s="6">
         <f t="shared" si="22"/>
-        <v>217596</v>
+        <v>217634</v>
       </c>
       <c r="BI40" s="15">
-        <v>785627</v>
+        <v>785665</v>
       </c>
       <c r="BJ40" s="7">
         <f t="shared" si="23"/>
-        <v>0.89618075399337693</v>
+        <v>0.89622410136897857</v>
       </c>
     </row>
     <row r="41" spans="1:62" x14ac:dyDescent="0.3">
@@ -7857,14 +7857,14 @@
       </c>
       <c r="E41" s="6">
         <f t="shared" si="0"/>
-        <v>8015</v>
+        <v>8016</v>
       </c>
       <c r="F41" s="14">
-        <v>11520</v>
+        <v>11521</v>
       </c>
       <c r="G41" s="7">
         <f t="shared" si="1"/>
-        <v>0.70145527613712477</v>
+        <v>0.70151616635206726</v>
       </c>
       <c r="H41" s="13">
         <v>16070</v>
@@ -7891,14 +7891,14 @@
       </c>
       <c r="O41" s="6">
         <f t="shared" si="4"/>
-        <v>10847</v>
+        <v>10849</v>
       </c>
       <c r="P41" s="15">
-        <v>16899</v>
+        <v>16901</v>
       </c>
       <c r="Q41" s="7">
         <f t="shared" si="5"/>
-        <v>0.80937784376646393</v>
+        <v>0.80947363379472193</v>
       </c>
       <c r="R41" s="13">
         <v>15621</v>
@@ -7942,14 +7942,14 @@
       </c>
       <c r="AD41" s="6">
         <f t="shared" si="10"/>
-        <v>11894</v>
+        <v>11897</v>
       </c>
       <c r="AE41" s="15">
-        <v>17191</v>
+        <v>17194</v>
       </c>
       <c r="AF41" s="7">
         <f t="shared" si="11"/>
-        <v>0.81764565992865634</v>
+        <v>0.81778834720570748</v>
       </c>
       <c r="AG41" s="13">
         <v>15000</v>
@@ -7993,14 +7993,14 @@
       </c>
       <c r="AS41" s="6">
         <f t="shared" si="16"/>
-        <v>6924</v>
+        <v>6925</v>
       </c>
       <c r="AT41" s="15">
-        <v>17371</v>
+        <v>17372</v>
       </c>
       <c r="AU41" s="7">
         <f t="shared" si="17"/>
-        <v>0.85189544406846163</v>
+        <v>0.8519444853121475</v>
       </c>
       <c r="AV41" s="13">
         <v>13562</v>
@@ -8010,14 +8010,14 @@
       </c>
       <c r="AX41" s="6">
         <f t="shared" si="18"/>
-        <v>5911</v>
+        <v>5912</v>
       </c>
       <c r="AY41" s="14">
-        <v>11994</v>
+        <v>11995</v>
       </c>
       <c r="AZ41" s="7">
         <f t="shared" si="19"/>
-        <v>0.88438283439020793</v>
+        <v>0.88445656982745913</v>
       </c>
       <c r="BA41" s="13">
         <v>13336</v>
@@ -8044,14 +8044,14 @@
       </c>
       <c r="BH41" s="6">
         <f t="shared" si="22"/>
-        <v>4508</v>
+        <v>4509</v>
       </c>
       <c r="BI41" s="15">
-        <v>17113</v>
+        <v>17114</v>
       </c>
       <c r="BJ41" s="7">
         <f t="shared" si="23"/>
-        <v>0.869518825262944</v>
+        <v>0.86956963568924339</v>
       </c>
     </row>
     <row r="42" spans="1:62" x14ac:dyDescent="0.3">
@@ -8315,14 +8315,14 @@
       </c>
       <c r="O43" s="6">
         <f t="shared" si="4"/>
-        <v>177496</v>
+        <v>177497</v>
       </c>
       <c r="P43" s="15">
-        <v>265582</v>
+        <v>265583</v>
       </c>
       <c r="Q43" s="7">
         <f t="shared" si="5"/>
-        <v>0.81008650455704545</v>
+        <v>0.81008955478825295</v>
       </c>
       <c r="R43" s="13">
         <v>238294</v>
@@ -8646,14 +8646,14 @@
       </c>
       <c r="AX44" s="6">
         <f t="shared" si="18"/>
-        <v>83614</v>
+        <v>83615</v>
       </c>
       <c r="AY44" s="14">
-        <v>163487</v>
+        <v>163488</v>
       </c>
       <c r="AZ44" s="7">
         <f t="shared" si="19"/>
-        <v>0.85096736918264204</v>
+        <v>0.85097257428989326</v>
       </c>
       <c r="BA44" s="13">
         <v>188319</v>
@@ -9111,15 +9111,15 @@
       </c>
       <c r="E47" s="8">
         <f>F47-D47</f>
-        <v>2360143</v>
+        <v>2360170</v>
       </c>
       <c r="F47" s="10">
         <f>SUM(F9:F46)</f>
-        <v>3455861</v>
+        <v>3455888</v>
       </c>
       <c r="G47" s="9">
         <f>F47/C47</f>
-        <v>0.60008473759562286</v>
+        <v>0.60008942594620029</v>
       </c>
       <c r="H47" s="10">
         <f>SUM(H9:H46)</f>
@@ -9131,15 +9131,15 @@
       </c>
       <c r="J47" s="8">
         <f>K47-I47</f>
-        <v>2353585</v>
+        <v>2353613</v>
       </c>
       <c r="K47" s="10">
         <f>SUM(K9:K46)</f>
-        <v>3468817</v>
+        <v>3468845</v>
       </c>
       <c r="L47" s="9">
         <f>K47/H47</f>
-        <v>0.62338296459127351</v>
+        <v>0.62338799648629961</v>
       </c>
       <c r="M47" s="10">
         <f>SUM(M9:M46)</f>
@@ -9151,15 +9151,15 @@
       </c>
       <c r="O47" s="8">
         <f>P47-N47</f>
-        <v>4976308</v>
+        <v>4976363</v>
       </c>
       <c r="P47" s="10">
         <f>SUM(P9:P46)</f>
-        <v>8855249</v>
+        <v>8855304</v>
       </c>
       <c r="Q47" s="9">
         <f>P47/M47</f>
-        <v>0.85488587570337848</v>
+        <v>0.85489118540423092</v>
       </c>
       <c r="R47" s="10">
         <f>SUM(R9:R46)</f>
@@ -9171,15 +9171,15 @@
       </c>
       <c r="T47" s="8">
         <f>U47-S47</f>
-        <v>2484340</v>
+        <v>2484372</v>
       </c>
       <c r="U47" s="10">
         <f>SUM(U9:U46)</f>
-        <v>3513910</v>
+        <v>3513942</v>
       </c>
       <c r="V47" s="9">
         <f>U47/R47</f>
-        <v>0.68454650262585048</v>
+        <v>0.68455273656129112</v>
       </c>
       <c r="W47" s="10">
         <f>SUM(W9:W46)</f>
@@ -9191,15 +9191,15 @@
       </c>
       <c r="Y47" s="8">
         <f>Z47-X47</f>
-        <v>2446523</v>
+        <v>2446559</v>
       </c>
       <c r="Z47" s="10">
         <f>SUM(Z9:Z46)</f>
-        <v>3535451</v>
+        <v>3535487</v>
       </c>
       <c r="AA47" s="9">
         <f>Z47/W47</f>
-        <v>0.70912311414362694</v>
+        <v>0.70913033484393062</v>
       </c>
       <c r="AB47" s="10">
         <f>SUM(AB9:AB46)</f>
@@ -9211,15 +9211,15 @@
       </c>
       <c r="AD47" s="8">
         <f>AE47-AC47</f>
-        <v>5974282</v>
+        <v>5974354</v>
       </c>
       <c r="AE47" s="10">
         <f>SUM(AE9:AE46)</f>
-        <v>9059285</v>
+        <v>9059357</v>
       </c>
       <c r="AF47" s="9">
         <f>AE47/AB47</f>
-        <v>0.86494614091867583</v>
+        <v>0.86495301520534928</v>
       </c>
       <c r="AG47" s="10">
         <f>SUM(AG9:AG46)</f>
@@ -9231,15 +9231,15 @@
       </c>
       <c r="AI47" s="8">
         <f>AJ47-AH47</f>
-        <v>2598176</v>
+        <v>2598214</v>
       </c>
       <c r="AJ47" s="10">
         <f>SUM(AJ9:AJ46)</f>
-        <v>3583923</v>
+        <v>3583961</v>
       </c>
       <c r="AK47" s="9">
         <f>AJ47/AG47</f>
-        <v>0.73963091129273917</v>
+        <v>0.73963875353003861</v>
       </c>
       <c r="AL47" s="10">
         <f>SUM(AL9:AL46)</f>
@@ -9251,15 +9251,15 @@
       </c>
       <c r="AN47" s="8">
         <f>AO47-AM47</f>
-        <v>2369221</v>
+        <v>2369256</v>
       </c>
       <c r="AO47" s="10">
         <f>SUM(AO9:AO46)</f>
-        <v>3627303</v>
+        <v>3627338</v>
       </c>
       <c r="AP47" s="9">
         <f>AO47/AL47</f>
-        <v>0.77193165772681183</v>
+        <v>0.77193910612801253</v>
       </c>
       <c r="AQ47" s="10">
         <f>SUM(AQ9:AQ46)</f>
@@ -9271,15 +9271,15 @@
       </c>
       <c r="AS47" s="8">
         <f>AT47-AR47</f>
-        <v>3170972</v>
+        <v>3171037</v>
       </c>
       <c r="AT47" s="10">
         <f>SUM(AT9:AT46)</f>
-        <v>9226854</v>
+        <v>9226919</v>
       </c>
       <c r="AU47" s="9">
         <f>AT47/AQ47</f>
-        <v>0.88970012379051611</v>
+        <v>0.88970639142063646</v>
       </c>
       <c r="AV47" s="10">
         <f>SUM(AV9:AV46)</f>
@@ -9291,15 +9291,15 @@
       </c>
       <c r="AX47" s="8">
         <f>AY47-AW47</f>
-        <v>1737570</v>
+        <v>1737610</v>
       </c>
       <c r="AY47" s="10">
         <f>SUM(AY9:AY46)</f>
-        <v>3649907</v>
+        <v>3649947</v>
       </c>
       <c r="AZ47" s="9">
         <f>AY47/AV47</f>
-        <v>0.81790303142754828</v>
+        <v>0.81791199497682698</v>
       </c>
       <c r="BA47" s="10">
         <f>SUM(BA9:BA46)</f>
@@ -9311,15 +9311,15 @@
       </c>
       <c r="BC47" s="8">
         <f>BD47-BB47</f>
-        <v>869149</v>
+        <v>869187</v>
       </c>
       <c r="BD47" s="10">
         <f>SUM(BD9:BD46)</f>
-        <v>3647775</v>
+        <v>3647813</v>
       </c>
       <c r="BE47" s="9">
         <f>BD47/BA47</f>
-        <v>0.83396013753875131</v>
+        <v>0.83396882515934923</v>
       </c>
       <c r="BF47" s="10">
         <f>SUM(BF9:BF46)</f>
@@ -9331,15 +9331,15 @@
       </c>
       <c r="BH47" s="8">
         <f>BI47-BG47</f>
-        <v>2887636</v>
+        <v>2887731</v>
       </c>
       <c r="BI47" s="10">
         <f>SUM(BI9:BI46)</f>
-        <v>9180030</v>
+        <v>9180125</v>
       </c>
       <c r="BJ47" s="9">
         <f>BI47/BF47</f>
-        <v>0.88008843805328907</v>
+        <v>0.88009754569254683</v>
       </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.3">

--- a/gstdatabase/GSTR-1-2019-2020.xlsx
+++ b/gstdatabase/GSTR-1-2019-2020.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Jun-26\GST Statistics Downloads 31st May 26\Downloads\GSTR 1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Jul-26\GST Statistics Downloads 31st Jul 26\Downloads\GSTR 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BA013F5-61A0-43F3-821C-A173470FDBA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34EBA763-5FD2-4412-BE5B-5FC541D0ED28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -185,10 +185,10 @@
     <t>Andaman and Nicobar Islands</t>
   </si>
   <si>
-    <t>Data Considered upto 30th Jun 2026</t>
+    <t>Data Considered upto 31st Jul 2026</t>
   </si>
   <si>
-    <t>Filing %age as on 30th Jun 2026</t>
+    <t>Filing %age as on 31st Jul 2026</t>
   </si>
 </sst>
 </file>
@@ -724,7 +724,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BJ62"/>
+  <dimension ref="A1:BJ60"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="26.77734375" bestFit="1" customWidth="1"/>
@@ -1107,14 +1107,14 @@
       </c>
       <c r="O9" s="6">
         <f>P9-N9</f>
-        <v>48848</v>
+        <v>48849</v>
       </c>
       <c r="P9" s="15">
-        <v>73789</v>
+        <v>73790</v>
       </c>
       <c r="Q9" s="7">
         <f>P9/M9</f>
-        <v>0.81199242907762392</v>
+        <v>0.81200343332526359</v>
       </c>
       <c r="R9" s="13">
         <v>43438</v>
@@ -1158,14 +1158,14 @@
       </c>
       <c r="AD9" s="6">
         <f>AE9-AC9</f>
-        <v>65090</v>
+        <v>65091</v>
       </c>
       <c r="AE9" s="15">
-        <v>73402</v>
+        <v>73403</v>
       </c>
       <c r="AF9" s="7">
         <f>AE9/AB9</f>
-        <v>0.79386126192381734</v>
+        <v>0.7938720771776514</v>
       </c>
       <c r="AG9" s="13">
         <v>42646</v>
@@ -1209,14 +1209,14 @@
       </c>
       <c r="AS9" s="6">
         <f>AT9-AR9</f>
-        <v>48896</v>
+        <v>48897</v>
       </c>
       <c r="AT9" s="15">
-        <v>73780</v>
+        <v>73781</v>
       </c>
       <c r="AU9" s="7">
         <f>AT9/AQ9</f>
-        <v>0.80026899798251516</v>
+        <v>0.80027984467535851</v>
       </c>
       <c r="AV9" s="13">
         <v>39353</v>
@@ -1955,14 +1955,14 @@
       </c>
       <c r="O13" s="6">
         <f t="shared" si="4"/>
-        <v>68076</v>
+        <v>68079</v>
       </c>
       <c r="P13" s="15">
-        <v>110024</v>
+        <v>110027</v>
       </c>
       <c r="Q13" s="7">
         <f t="shared" si="5"/>
-        <v>0.85011821792276432</v>
+        <v>0.85014139790762</v>
       </c>
       <c r="R13" s="13">
         <v>54062</v>
@@ -2006,14 +2006,14 @@
       </c>
       <c r="AD13" s="6">
         <f t="shared" si="10"/>
-        <v>76400</v>
+        <v>76401</v>
       </c>
       <c r="AE13" s="15">
-        <v>113206</v>
+        <v>113207</v>
       </c>
       <c r="AF13" s="7">
         <f t="shared" si="11"/>
-        <v>0.86067268801508379</v>
+        <v>0.86068029072773167</v>
       </c>
       <c r="AG13" s="13">
         <v>48183</v>
@@ -2057,14 +2057,14 @@
       </c>
       <c r="AS13" s="6">
         <f t="shared" si="16"/>
-        <v>42776</v>
+        <v>42778</v>
       </c>
       <c r="AT13" s="15">
-        <v>115603</v>
+        <v>115605</v>
       </c>
       <c r="AU13" s="7">
         <f t="shared" si="17"/>
-        <v>0.89992838126080121</v>
+        <v>0.89994395055193133</v>
       </c>
       <c r="AV13" s="13">
         <v>43497</v>
@@ -2074,14 +2074,14 @@
       </c>
       <c r="AX13" s="6">
         <f t="shared" si="18"/>
-        <v>16348</v>
+        <v>16349</v>
       </c>
       <c r="AY13" s="14">
-        <v>32540</v>
+        <v>32541</v>
       </c>
       <c r="AZ13" s="7">
         <f t="shared" si="19"/>
-        <v>0.74809756994735266</v>
+        <v>0.74812056003862337</v>
       </c>
       <c r="BA13" s="13">
         <v>42767</v>
@@ -2091,14 +2091,14 @@
       </c>
       <c r="BC13" s="6">
         <f t="shared" si="20"/>
-        <v>8691</v>
+        <v>8693</v>
       </c>
       <c r="BD13" s="14">
-        <v>32558</v>
+        <v>32560</v>
       </c>
       <c r="BE13" s="7">
         <f t="shared" si="21"/>
-        <v>0.76128790890172326</v>
+        <v>0.76133467393083454</v>
       </c>
       <c r="BF13" s="13">
         <v>131773</v>
@@ -2108,14 +2108,14 @@
       </c>
       <c r="BH13" s="6">
         <f t="shared" si="22"/>
-        <v>38735</v>
+        <v>38738</v>
       </c>
       <c r="BI13" s="15">
-        <v>114888</v>
+        <v>114891</v>
       </c>
       <c r="BJ13" s="7">
         <f t="shared" si="23"/>
-        <v>0.87186297648228395</v>
+        <v>0.87188574290636167</v>
       </c>
     </row>
     <row r="14" spans="1:62" x14ac:dyDescent="0.3">
@@ -2379,14 +2379,14 @@
       </c>
       <c r="O15" s="6">
         <f t="shared" si="4"/>
-        <v>279884</v>
+        <v>279886</v>
       </c>
       <c r="P15" s="15">
-        <v>617107</v>
+        <v>617109</v>
       </c>
       <c r="Q15" s="7">
         <f t="shared" si="5"/>
-        <v>0.81288455484175215</v>
+        <v>0.81288718934291593</v>
       </c>
       <c r="R15" s="13">
         <v>323034</v>
@@ -2430,14 +2430,14 @@
       </c>
       <c r="AD15" s="6">
         <f t="shared" si="10"/>
-        <v>363280</v>
+        <v>363283</v>
       </c>
       <c r="AE15" s="15">
-        <v>629778</v>
+        <v>629781</v>
       </c>
       <c r="AF15" s="7">
         <f t="shared" si="11"/>
-        <v>0.82186728819995902</v>
+        <v>0.82187120323329554</v>
       </c>
       <c r="AG15" s="13">
         <v>285320</v>
@@ -2481,14 +2481,14 @@
       </c>
       <c r="AS15" s="6">
         <f t="shared" si="16"/>
-        <v>180118</v>
+        <v>180119</v>
       </c>
       <c r="AT15" s="15">
-        <v>640153</v>
+        <v>640154</v>
       </c>
       <c r="AU15" s="7">
         <f t="shared" si="17"/>
-        <v>0.85747141217238021</v>
+        <v>0.85747275165124259</v>
       </c>
       <c r="AV15" s="13">
         <v>253369</v>
@@ -2532,14 +2532,14 @@
       </c>
       <c r="BH15" s="6">
         <f t="shared" si="22"/>
-        <v>177750</v>
+        <v>177751</v>
       </c>
       <c r="BI15" s="15">
-        <v>634475</v>
+        <v>634476</v>
       </c>
       <c r="BJ15" s="7">
         <f t="shared" si="23"/>
-        <v>0.84359335735464225</v>
+        <v>0.84359468694738804</v>
       </c>
     </row>
     <row r="16" spans="1:62" x14ac:dyDescent="0.3">
@@ -2557,14 +2557,14 @@
       </c>
       <c r="E16" s="6">
         <f t="shared" si="0"/>
-        <v>70975</v>
+        <v>70976</v>
       </c>
       <c r="F16" s="14">
-        <v>122153</v>
+        <v>122154</v>
       </c>
       <c r="G16" s="7">
         <f t="shared" si="1"/>
-        <v>0.4955537164601741</v>
+        <v>0.49555777328822143</v>
       </c>
       <c r="H16" s="13">
         <v>236220</v>
@@ -2574,14 +2574,14 @@
       </c>
       <c r="J16" s="6">
         <f t="shared" si="2"/>
-        <v>67811</v>
+        <v>67812</v>
       </c>
       <c r="K16" s="14">
-        <v>122238</v>
+        <v>122239</v>
       </c>
       <c r="L16" s="7">
         <f t="shared" si="3"/>
-        <v>0.51747523495046988</v>
+        <v>0.51747946829226987</v>
       </c>
       <c r="M16" s="13">
         <v>560439</v>
@@ -2591,14 +2591,14 @@
       </c>
       <c r="O16" s="6">
         <f t="shared" si="4"/>
-        <v>226150</v>
+        <v>226152</v>
       </c>
       <c r="P16" s="15">
-        <v>489311</v>
+        <v>489313</v>
       </c>
       <c r="Q16" s="7">
         <f t="shared" si="5"/>
-        <v>0.87308520641853971</v>
+        <v>0.8730887750495594</v>
       </c>
       <c r="R16" s="13">
         <v>205814</v>
@@ -2642,14 +2642,14 @@
       </c>
       <c r="AD16" s="6">
         <f t="shared" si="10"/>
-        <v>300038</v>
+        <v>300040</v>
       </c>
       <c r="AE16" s="15">
-        <v>499301</v>
+        <v>499303</v>
       </c>
       <c r="AF16" s="7">
         <f t="shared" si="11"/>
-        <v>0.89173950471319019</v>
+        <v>0.89174307666479735</v>
       </c>
       <c r="AG16" s="13">
         <v>184413</v>
@@ -2693,14 +2693,14 @@
       </c>
       <c r="AS16" s="6">
         <f t="shared" si="16"/>
-        <v>139195</v>
+        <v>139196</v>
       </c>
       <c r="AT16" s="15">
-        <v>507938</v>
+        <v>507939</v>
       </c>
       <c r="AU16" s="7">
         <f t="shared" si="17"/>
-        <v>0.93737635456343937</v>
+        <v>0.93737820001771632</v>
       </c>
       <c r="AV16" s="13">
         <v>152784</v>
@@ -2744,14 +2744,14 @@
       </c>
       <c r="BH16" s="6">
         <f t="shared" si="22"/>
-        <v>134282</v>
+        <v>134288</v>
       </c>
       <c r="BI16" s="15">
-        <v>511737</v>
+        <v>511743</v>
       </c>
       <c r="BJ16" s="7">
         <f t="shared" si="23"/>
-        <v>0.92674079574059653</v>
+        <v>0.92675166156576538</v>
       </c>
     </row>
     <row r="17" spans="1:62" x14ac:dyDescent="0.3">
@@ -2769,14 +2769,14 @@
       </c>
       <c r="E17" s="6">
         <f t="shared" si="0"/>
-        <v>210830</v>
+        <v>210831</v>
       </c>
       <c r="F17" s="14">
-        <v>290688</v>
+        <v>290689</v>
       </c>
       <c r="G17" s="7">
         <f t="shared" si="1"/>
-        <v>0.55426575346644902</v>
+        <v>0.55426766020409723</v>
       </c>
       <c r="H17" s="13">
         <v>496559</v>
@@ -2786,14 +2786,14 @@
       </c>
       <c r="J17" s="6">
         <f t="shared" si="2"/>
-        <v>213170</v>
+        <v>213171</v>
       </c>
       <c r="K17" s="14">
-        <v>291886</v>
+        <v>291887</v>
       </c>
       <c r="L17" s="7">
         <f t="shared" si="3"/>
-        <v>0.58781735906508592</v>
+        <v>0.58781937292446618</v>
       </c>
       <c r="M17" s="13">
         <v>1118687</v>
@@ -2803,14 +2803,14 @@
       </c>
       <c r="O17" s="6">
         <f t="shared" si="4"/>
-        <v>588935</v>
+        <v>588938</v>
       </c>
       <c r="P17" s="15">
-        <v>956753</v>
+        <v>956756</v>
       </c>
       <c r="Q17" s="7">
         <f t="shared" si="5"/>
-        <v>0.85524637365053857</v>
+        <v>0.85524905536579932</v>
       </c>
       <c r="R17" s="13">
         <v>453407</v>
@@ -2820,14 +2820,14 @@
       </c>
       <c r="T17" s="6">
         <f t="shared" si="6"/>
-        <v>222425</v>
+        <v>222426</v>
       </c>
       <c r="U17" s="14">
-        <v>295663</v>
+        <v>295664</v>
       </c>
       <c r="V17" s="7">
         <f t="shared" si="7"/>
-        <v>0.65209182919540276</v>
+        <v>0.65209403471935812</v>
       </c>
       <c r="W17" s="13">
         <v>432883</v>
@@ -2837,14 +2837,14 @@
       </c>
       <c r="Y17" s="6">
         <f t="shared" si="8"/>
-        <v>221222</v>
+        <v>221223</v>
       </c>
       <c r="Z17" s="14">
-        <v>298025</v>
+        <v>298026</v>
       </c>
       <c r="AA17" s="7">
         <f t="shared" si="9"/>
-        <v>0.68846547450465834</v>
+        <v>0.68846778459768576</v>
       </c>
       <c r="AB17" s="13">
         <v>1126122</v>
@@ -2854,14 +2854,14 @@
       </c>
       <c r="AD17" s="6">
         <f t="shared" si="10"/>
-        <v>697983</v>
+        <v>697987</v>
       </c>
       <c r="AE17" s="15">
-        <v>983317</v>
+        <v>983321</v>
       </c>
       <c r="AF17" s="7">
         <f t="shared" si="11"/>
-        <v>0.87318869536337984</v>
+        <v>0.87319224737639434</v>
       </c>
       <c r="AG17" s="13">
         <v>411675</v>
@@ -2871,14 +2871,14 @@
       </c>
       <c r="AI17" s="6">
         <f t="shared" si="12"/>
-        <v>236497</v>
+        <v>236499</v>
       </c>
       <c r="AJ17" s="14">
-        <v>303065</v>
+        <v>303067</v>
       </c>
       <c r="AK17" s="7">
         <f t="shared" si="13"/>
-        <v>0.73617538106516067</v>
+        <v>0.73618023926641163</v>
       </c>
       <c r="AL17" s="13">
         <v>391787</v>
@@ -2888,14 +2888,14 @@
       </c>
       <c r="AN17" s="6">
         <f t="shared" si="14"/>
-        <v>224656</v>
+        <v>224658</v>
       </c>
       <c r="AO17" s="14">
-        <v>307343</v>
+        <v>307345</v>
       </c>
       <c r="AP17" s="7">
         <f t="shared" si="15"/>
-        <v>0.78446451770987802</v>
+        <v>0.78446962252448393</v>
       </c>
       <c r="AQ17" s="13">
         <v>1127354</v>
@@ -2905,14 +2905,14 @@
       </c>
       <c r="AS17" s="6">
         <f t="shared" si="16"/>
-        <v>381274</v>
+        <v>381277</v>
       </c>
       <c r="AT17" s="15">
-        <v>1005697</v>
+        <v>1005700</v>
       </c>
       <c r="AU17" s="7">
         <f t="shared" si="17"/>
-        <v>0.89208624797534763</v>
+        <v>0.89208890907381355</v>
       </c>
       <c r="AV17" s="13">
         <v>386848</v>
@@ -2922,14 +2922,14 @@
       </c>
       <c r="AX17" s="6">
         <f t="shared" si="18"/>
-        <v>170741</v>
+        <v>170743</v>
       </c>
       <c r="AY17" s="14">
-        <v>308731</v>
+        <v>308733</v>
       </c>
       <c r="AZ17" s="7">
         <f t="shared" si="19"/>
-        <v>0.79806797501861193</v>
+        <v>0.79807314500785842</v>
       </c>
       <c r="BA17" s="13">
         <v>379844</v>
@@ -2939,14 +2939,14 @@
       </c>
       <c r="BC17" s="6">
         <f t="shared" si="20"/>
-        <v>93340</v>
+        <v>93342</v>
       </c>
       <c r="BD17" s="14">
-        <v>308646</v>
+        <v>308648</v>
       </c>
       <c r="BE17" s="7">
         <f t="shared" si="21"/>
-        <v>0.81255989300870879</v>
+        <v>0.81256515832815579</v>
       </c>
       <c r="BF17" s="13">
         <v>1155076</v>
@@ -2956,14 +2956,14 @@
       </c>
       <c r="BH17" s="6">
         <f t="shared" si="22"/>
-        <v>370541</v>
+        <v>370545</v>
       </c>
       <c r="BI17" s="15">
-        <v>1003174</v>
+        <v>1003178</v>
       </c>
       <c r="BJ17" s="7">
         <f t="shared" si="23"/>
-        <v>0.86849177023849511</v>
+        <v>0.8684952332140915</v>
       </c>
     </row>
     <row r="18" spans="1:62" x14ac:dyDescent="0.3">
@@ -3151,14 +3151,14 @@
       </c>
       <c r="BC18" s="6">
         <f t="shared" si="20"/>
-        <v>35930</v>
+        <v>35931</v>
       </c>
       <c r="BD18" s="14">
-        <v>86217</v>
+        <v>86218</v>
       </c>
       <c r="BE18" s="7">
         <f t="shared" si="21"/>
-        <v>0.7942680264212475</v>
+        <v>0.79427723885065726</v>
       </c>
       <c r="BF18" s="13">
         <v>320339</v>
@@ -3261,14 +3261,14 @@
       </c>
       <c r="Y19" s="6">
         <f t="shared" si="8"/>
-        <v>1931</v>
+        <v>1932</v>
       </c>
       <c r="Z19" s="14">
-        <v>2746</v>
+        <v>2747</v>
       </c>
       <c r="AA19" s="7">
         <f t="shared" si="9"/>
-        <v>0.6738650306748466</v>
+        <v>0.67411042944785271</v>
       </c>
       <c r="AB19" s="13">
         <v>7195</v>
@@ -3405,14 +3405,14 @@
       </c>
       <c r="E20" s="6">
         <f t="shared" si="0"/>
-        <v>2846</v>
+        <v>2847</v>
       </c>
       <c r="F20" s="14">
-        <v>3281</v>
+        <v>3282</v>
       </c>
       <c r="G20" s="7">
         <f t="shared" si="1"/>
-        <v>0.38874407582938386</v>
+        <v>0.38886255924170615</v>
       </c>
       <c r="H20" s="13">
         <v>8306</v>
@@ -3422,14 +3422,14 @@
       </c>
       <c r="J20" s="6">
         <f t="shared" si="2"/>
-        <v>2846</v>
+        <v>2847</v>
       </c>
       <c r="K20" s="14">
-        <v>3274</v>
+        <v>3275</v>
       </c>
       <c r="L20" s="7">
         <f t="shared" si="3"/>
-        <v>0.39417288706958825</v>
+        <v>0.3942932819648447</v>
       </c>
       <c r="M20" s="13">
         <v>11143</v>
@@ -3439,14 +3439,14 @@
       </c>
       <c r="O20" s="6">
         <f t="shared" si="4"/>
-        <v>6285</v>
+        <v>6286</v>
       </c>
       <c r="P20" s="15">
-        <v>7675</v>
+        <v>7676</v>
       </c>
       <c r="Q20" s="7">
         <f t="shared" si="5"/>
-        <v>0.6887732208561429</v>
+        <v>0.68886296329534236</v>
       </c>
       <c r="R20" s="13">
         <v>7639</v>
@@ -3456,14 +3456,14 @@
       </c>
       <c r="T20" s="6">
         <f t="shared" si="6"/>
-        <v>2767</v>
+        <v>2768</v>
       </c>
       <c r="U20" s="14">
-        <v>3336</v>
+        <v>3337</v>
       </c>
       <c r="V20" s="7">
         <f t="shared" si="7"/>
-        <v>0.43670637517999739</v>
+        <v>0.43683728236680192</v>
       </c>
       <c r="W20" s="13">
         <v>7528</v>
@@ -3473,14 +3473,14 @@
       </c>
       <c r="Y20" s="6">
         <f t="shared" si="8"/>
-        <v>2784</v>
+        <v>2785</v>
       </c>
       <c r="Z20" s="14">
-        <v>3386</v>
+        <v>3387</v>
       </c>
       <c r="AA20" s="7">
         <f t="shared" si="9"/>
-        <v>0.44978746014877791</v>
+        <v>0.44992029755579172</v>
       </c>
       <c r="AB20" s="13">
         <v>11960</v>
@@ -3490,14 +3490,14 @@
       </c>
       <c r="AD20" s="6">
         <f t="shared" si="10"/>
-        <v>6803</v>
+        <v>6804</v>
       </c>
       <c r="AE20" s="15">
-        <v>8152</v>
+        <v>8153</v>
       </c>
       <c r="AF20" s="7">
         <f t="shared" si="11"/>
-        <v>0.68160535117056853</v>
+        <v>0.68168896321070238</v>
       </c>
       <c r="AG20" s="13">
         <v>7480</v>
@@ -3507,14 +3507,14 @@
       </c>
       <c r="AI20" s="6">
         <f t="shared" si="12"/>
-        <v>2964</v>
+        <v>2965</v>
       </c>
       <c r="AJ20" s="14">
-        <v>3502</v>
+        <v>3503</v>
       </c>
       <c r="AK20" s="7">
         <f t="shared" si="13"/>
-        <v>0.4681818181818182</v>
+        <v>0.46831550802139038</v>
       </c>
       <c r="AL20" s="13">
         <v>7440</v>
@@ -3524,14 +3524,14 @@
       </c>
       <c r="AN20" s="6">
         <f t="shared" si="14"/>
-        <v>2934</v>
+        <v>2935</v>
       </c>
       <c r="AO20" s="14">
-        <v>3529</v>
+        <v>3530</v>
       </c>
       <c r="AP20" s="7">
         <f t="shared" si="15"/>
-        <v>0.47432795698924729</v>
+        <v>0.47446236559139787</v>
       </c>
       <c r="AQ20" s="13">
         <v>12515</v>
@@ -3541,14 +3541,14 @@
       </c>
       <c r="AS20" s="6">
         <f t="shared" si="16"/>
-        <v>5065</v>
+        <v>5066</v>
       </c>
       <c r="AT20" s="15">
-        <v>8492</v>
+        <v>8493</v>
       </c>
       <c r="AU20" s="7">
         <f t="shared" si="17"/>
-        <v>0.67854574510587295</v>
+        <v>0.67862564922093482</v>
       </c>
       <c r="AV20" s="13">
         <v>7275</v>
@@ -3558,14 +3558,14 @@
       </c>
       <c r="AX20" s="6">
         <f t="shared" si="18"/>
-        <v>2662</v>
+        <v>2663</v>
       </c>
       <c r="AY20" s="14">
-        <v>3585</v>
+        <v>3586</v>
       </c>
       <c r="AZ20" s="7">
         <f t="shared" si="19"/>
-        <v>0.4927835051546392</v>
+        <v>0.4929209621993127</v>
       </c>
       <c r="BA20" s="13">
         <v>7020</v>
@@ -3575,14 +3575,14 @@
       </c>
       <c r="BC20" s="6">
         <f t="shared" si="20"/>
-        <v>1830</v>
+        <v>1831</v>
       </c>
       <c r="BD20" s="14">
-        <v>3612</v>
+        <v>3613</v>
       </c>
       <c r="BE20" s="7">
         <f t="shared" si="21"/>
-        <v>0.51452991452991448</v>
+        <v>0.51467236467236466</v>
       </c>
       <c r="BF20" s="13">
         <v>12538</v>
@@ -3592,14 +3592,14 @@
       </c>
       <c r="BH20" s="6">
         <f t="shared" si="22"/>
-        <v>4691</v>
+        <v>4693</v>
       </c>
       <c r="BI20" s="15">
-        <v>8672</v>
+        <v>8674</v>
       </c>
       <c r="BJ20" s="7">
         <f t="shared" si="23"/>
-        <v>0.69165736162067315</v>
+        <v>0.6918168766948477</v>
       </c>
     </row>
     <row r="21" spans="1:62" x14ac:dyDescent="0.3">
@@ -3702,14 +3702,14 @@
       </c>
       <c r="AD21" s="6">
         <f t="shared" si="10"/>
-        <v>4095</v>
+        <v>4096</v>
       </c>
       <c r="AE21" s="15">
-        <v>5093</v>
+        <v>5094</v>
       </c>
       <c r="AF21" s="7">
         <f t="shared" si="11"/>
-        <v>0.75811253349211072</v>
+        <v>0.75826138731765402</v>
       </c>
       <c r="AG21" s="13">
         <v>5117</v>
@@ -4041,14 +4041,14 @@
       </c>
       <c r="E23" s="6">
         <f t="shared" si="0"/>
-        <v>2101</v>
+        <v>2104</v>
       </c>
       <c r="F23" s="14">
-        <v>2621</v>
+        <v>2624</v>
       </c>
       <c r="G23" s="7">
         <f t="shared" si="1"/>
-        <v>0.60826177767463452</v>
+        <v>0.60895799489440705</v>
       </c>
       <c r="H23" s="13">
         <v>4314</v>
@@ -4058,14 +4058,14 @@
       </c>
       <c r="J23" s="6">
         <f t="shared" si="2"/>
-        <v>2038</v>
+        <v>2041</v>
       </c>
       <c r="K23" s="14">
-        <v>2623</v>
+        <v>2626</v>
       </c>
       <c r="L23" s="7">
         <f t="shared" si="3"/>
-        <v>0.60802039870190083</v>
+        <v>0.60871580899397315</v>
       </c>
       <c r="M23" s="13">
         <v>5454</v>
@@ -4075,14 +4075,14 @@
       </c>
       <c r="O23" s="6">
         <f t="shared" si="4"/>
-        <v>2704</v>
+        <v>2706</v>
       </c>
       <c r="P23" s="15">
-        <v>4001</v>
+        <v>4003</v>
       </c>
       <c r="Q23" s="7">
         <f t="shared" si="5"/>
-        <v>0.73359002566923359</v>
+        <v>0.73395672900623399</v>
       </c>
       <c r="R23" s="13">
         <v>4339</v>
@@ -4092,14 +4092,14 @@
       </c>
       <c r="T23" s="6">
         <f t="shared" si="6"/>
-        <v>2185</v>
+        <v>2188</v>
       </c>
       <c r="U23" s="14">
-        <v>2710</v>
+        <v>2713</v>
       </c>
       <c r="V23" s="7">
         <f t="shared" si="7"/>
-        <v>0.62456787278174697</v>
+        <v>0.6252592763309518</v>
       </c>
       <c r="W23" s="13">
         <v>4331</v>
@@ -4109,14 +4109,14 @@
       </c>
       <c r="Y23" s="6">
         <f t="shared" si="8"/>
-        <v>2183</v>
+        <v>2186</v>
       </c>
       <c r="Z23" s="14">
-        <v>2727</v>
+        <v>2730</v>
       </c>
       <c r="AA23" s="7">
         <f t="shared" si="9"/>
-        <v>0.62964673285615336</v>
+        <v>0.63033941353036249</v>
       </c>
       <c r="AB23" s="13">
         <v>5800</v>
@@ -4126,14 +4126,14 @@
       </c>
       <c r="AD23" s="6">
         <f t="shared" si="10"/>
-        <v>2770</v>
+        <v>2773</v>
       </c>
       <c r="AE23" s="15">
-        <v>4169</v>
+        <v>4172</v>
       </c>
       <c r="AF23" s="7">
         <f t="shared" si="11"/>
-        <v>0.71879310344827585</v>
+        <v>0.71931034482758616</v>
       </c>
       <c r="AG23" s="13">
         <v>4378</v>
@@ -4143,14 +4143,14 @@
       </c>
       <c r="AI23" s="6">
         <f t="shared" si="12"/>
-        <v>2213</v>
+        <v>2216</v>
       </c>
       <c r="AJ23" s="14">
-        <v>2744</v>
+        <v>2747</v>
       </c>
       <c r="AK23" s="7">
         <f t="shared" si="13"/>
-        <v>0.62677021470991323</v>
+        <v>0.62745545911375056</v>
       </c>
       <c r="AL23" s="13">
         <v>4406</v>
@@ -4160,14 +4160,14 @@
       </c>
       <c r="AN23" s="6">
         <f t="shared" si="14"/>
-        <v>2130</v>
+        <v>2134</v>
       </c>
       <c r="AO23" s="14">
-        <v>2794</v>
+        <v>2798</v>
       </c>
       <c r="AP23" s="7">
         <f t="shared" si="15"/>
-        <v>0.63413527008624604</v>
+        <v>0.63504312301407173</v>
       </c>
       <c r="AQ23" s="13">
         <v>6083</v>
@@ -4177,14 +4177,14 @@
       </c>
       <c r="AS23" s="6">
         <f t="shared" si="16"/>
-        <v>2636</v>
+        <v>2641</v>
       </c>
       <c r="AT23" s="15">
-        <v>4304</v>
+        <v>4309</v>
       </c>
       <c r="AU23" s="7">
         <f t="shared" si="17"/>
-        <v>0.70754561893802403</v>
+        <v>0.70836758178530335</v>
       </c>
       <c r="AV23" s="13">
         <v>4479</v>
@@ -4194,14 +4194,14 @@
       </c>
       <c r="AX23" s="6">
         <f t="shared" si="18"/>
-        <v>2070</v>
+        <v>2073</v>
       </c>
       <c r="AY23" s="14">
-        <v>2874</v>
+        <v>2877</v>
       </c>
       <c r="AZ23" s="7">
         <f t="shared" si="19"/>
-        <v>0.64166108506363029</v>
+        <v>0.64233087742799733</v>
       </c>
       <c r="BA23" s="13">
         <v>4501</v>
@@ -4211,14 +4211,14 @@
       </c>
       <c r="BC23" s="6">
         <f t="shared" si="20"/>
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="BD23" s="14">
-        <v>2889</v>
+        <v>2893</v>
       </c>
       <c r="BE23" s="7">
         <f t="shared" si="21"/>
-        <v>0.64185736502999335</v>
+        <v>0.64274605643190397</v>
       </c>
       <c r="BF23" s="13">
         <v>6256</v>
@@ -4228,14 +4228,14 @@
       </c>
       <c r="BH23" s="6">
         <f t="shared" si="22"/>
-        <v>1170</v>
+        <v>1172</v>
       </c>
       <c r="BI23" s="15">
-        <v>4437</v>
+        <v>4439</v>
       </c>
       <c r="BJ23" s="7">
         <f t="shared" si="23"/>
-        <v>0.70923913043478259</v>
+        <v>0.7095588235294118</v>
       </c>
     </row>
     <row r="24" spans="1:62" x14ac:dyDescent="0.3">
@@ -4465,14 +4465,14 @@
       </c>
       <c r="E25" s="6">
         <f t="shared" si="0"/>
-        <v>6507</v>
+        <v>6510</v>
       </c>
       <c r="F25" s="14">
-        <v>7898</v>
+        <v>7901</v>
       </c>
       <c r="G25" s="7">
         <f t="shared" si="1"/>
-        <v>0.47884079059051776</v>
+        <v>0.47902267491208922</v>
       </c>
       <c r="H25" s="13">
         <v>16584</v>
@@ -4482,14 +4482,14 @@
       </c>
       <c r="J25" s="6">
         <f t="shared" si="2"/>
-        <v>6406</v>
+        <v>6409</v>
       </c>
       <c r="K25" s="14">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="L25" s="7">
         <f t="shared" si="3"/>
-        <v>0.48245296671490595</v>
+        <v>0.48263386396526775</v>
       </c>
       <c r="M25" s="13">
         <v>24878</v>
@@ -4499,14 +4499,14 @@
       </c>
       <c r="O25" s="6">
         <f t="shared" si="4"/>
-        <v>11576</v>
+        <v>11580</v>
       </c>
       <c r="P25" s="15">
-        <v>17315</v>
+        <v>17319</v>
       </c>
       <c r="Q25" s="7">
         <f t="shared" si="5"/>
-        <v>0.69599646273816218</v>
+        <v>0.69615724736715168</v>
       </c>
       <c r="R25" s="13">
         <v>16556</v>
@@ -4516,14 +4516,14 @@
       </c>
       <c r="T25" s="6">
         <f t="shared" si="6"/>
-        <v>6771</v>
+        <v>6773</v>
       </c>
       <c r="U25" s="14">
-        <v>8316</v>
+        <v>8318</v>
       </c>
       <c r="V25" s="7">
         <f t="shared" si="7"/>
-        <v>0.50229524039623097</v>
+        <v>0.50241604252234839</v>
       </c>
       <c r="W25" s="13">
         <v>16201</v>
@@ -4533,14 +4533,14 @@
       </c>
       <c r="Y25" s="6">
         <f t="shared" si="8"/>
-        <v>6526</v>
+        <v>6530</v>
       </c>
       <c r="Z25" s="14">
-        <v>8355</v>
+        <v>8359</v>
       </c>
       <c r="AA25" s="7">
         <f t="shared" si="9"/>
-        <v>0.5157089068576014</v>
+        <v>0.51595580519721007</v>
       </c>
       <c r="AB25" s="13">
         <v>26140</v>
@@ -4550,14 +4550,14 @@
       </c>
       <c r="AD25" s="6">
         <f t="shared" si="10"/>
-        <v>12089</v>
+        <v>12093</v>
       </c>
       <c r="AE25" s="15">
-        <v>18082</v>
+        <v>18086</v>
       </c>
       <c r="AF25" s="7">
         <f t="shared" si="11"/>
-        <v>0.69173680183626629</v>
+        <v>0.69188982402448351</v>
       </c>
       <c r="AG25" s="13">
         <v>16090</v>
@@ -4567,14 +4567,14 @@
       </c>
       <c r="AI25" s="6">
         <f t="shared" si="12"/>
-        <v>6883</v>
+        <v>6888</v>
       </c>
       <c r="AJ25" s="14">
-        <v>8407</v>
+        <v>8412</v>
       </c>
       <c r="AK25" s="7">
         <f t="shared" si="13"/>
-        <v>0.5224984462399006</v>
+        <v>0.52280919825978867</v>
       </c>
       <c r="AL25" s="13">
         <v>15981</v>
@@ -4584,14 +4584,14 @@
       </c>
       <c r="AN25" s="6">
         <f t="shared" si="14"/>
-        <v>6626</v>
+        <v>6630</v>
       </c>
       <c r="AO25" s="14">
-        <v>8373</v>
+        <v>8377</v>
       </c>
       <c r="AP25" s="7">
         <f t="shared" si="15"/>
-        <v>0.52393467242350289</v>
+        <v>0.52418496965146111</v>
       </c>
       <c r="AQ25" s="13">
         <v>26428</v>
@@ -4601,14 +4601,14 @@
       </c>
       <c r="AS25" s="6">
         <f t="shared" si="16"/>
-        <v>10630</v>
+        <v>10635</v>
       </c>
       <c r="AT25" s="15">
-        <v>17986</v>
+        <v>17991</v>
       </c>
       <c r="AU25" s="7">
         <f t="shared" si="17"/>
-        <v>0.68056606629332528</v>
+        <v>0.68075525957317995</v>
       </c>
       <c r="AV25" s="13">
         <v>15911</v>
@@ -4618,14 +4618,14 @@
       </c>
       <c r="AX25" s="6">
         <f t="shared" si="18"/>
-        <v>6035</v>
+        <v>6037</v>
       </c>
       <c r="AY25" s="14">
-        <v>8512</v>
+        <v>8514</v>
       </c>
       <c r="AZ25" s="7">
         <f t="shared" si="19"/>
-        <v>0.53497580290365154</v>
+        <v>0.53510150210546159</v>
       </c>
       <c r="BA25" s="13">
         <v>15896</v>
@@ -4635,14 +4635,14 @@
       </c>
       <c r="BC25" s="6">
         <f t="shared" si="20"/>
-        <v>3839</v>
+        <v>3842</v>
       </c>
       <c r="BD25" s="14">
-        <v>8386</v>
+        <v>8389</v>
       </c>
       <c r="BE25" s="7">
         <f t="shared" si="21"/>
-        <v>0.52755410166079519</v>
+        <v>0.52774282838449926</v>
       </c>
       <c r="BF25" s="13">
         <v>26706</v>
@@ -4652,14 +4652,14 @@
       </c>
       <c r="BH25" s="6">
         <f t="shared" si="22"/>
-        <v>7384</v>
+        <v>7389</v>
       </c>
       <c r="BI25" s="15">
-        <v>17611</v>
+        <v>17616</v>
       </c>
       <c r="BJ25" s="7">
         <f t="shared" si="23"/>
-        <v>0.65943982625627195</v>
+        <v>0.6596270501011009</v>
       </c>
     </row>
     <row r="26" spans="1:62" x14ac:dyDescent="0.3">
@@ -4711,14 +4711,14 @@
       </c>
       <c r="O26" s="6">
         <f t="shared" si="4"/>
-        <v>84818</v>
+        <v>84820</v>
       </c>
       <c r="P26" s="15">
-        <v>115386</v>
+        <v>115388</v>
       </c>
       <c r="Q26" s="7">
         <f t="shared" si="5"/>
-        <v>0.71590507212657051</v>
+        <v>0.71591748099891417</v>
       </c>
       <c r="R26" s="13">
         <v>103195</v>
@@ -4745,14 +4745,14 @@
       </c>
       <c r="Y26" s="6">
         <f t="shared" si="8"/>
-        <v>40869</v>
+        <v>40870</v>
       </c>
       <c r="Z26" s="14">
-        <v>49981</v>
+        <v>49982</v>
       </c>
       <c r="AA26" s="7">
         <f t="shared" si="9"/>
-        <v>0.49481239481239481</v>
+        <v>0.49482229482229484</v>
       </c>
       <c r="AB26" s="13">
         <v>167059</v>
@@ -4762,14 +4762,14 @@
       </c>
       <c r="AD26" s="6">
         <f t="shared" si="10"/>
-        <v>96137</v>
+        <v>96140</v>
       </c>
       <c r="AE26" s="15">
-        <v>119663</v>
+        <v>119666</v>
       </c>
       <c r="AF26" s="7">
         <f t="shared" si="11"/>
-        <v>0.71629184898748344</v>
+        <v>0.71630980671499289</v>
       </c>
       <c r="AG26" s="13">
         <v>98900</v>
@@ -4779,14 +4779,14 @@
       </c>
       <c r="AI26" s="6">
         <f t="shared" si="12"/>
-        <v>42354</v>
+        <v>42355</v>
       </c>
       <c r="AJ26" s="14">
-        <v>50962</v>
+        <v>50963</v>
       </c>
       <c r="AK26" s="7">
         <f t="shared" si="13"/>
-        <v>0.51528816986855408</v>
+        <v>0.51529828109201214</v>
       </c>
       <c r="AL26" s="13">
         <v>94250</v>
@@ -4796,14 +4796,14 @@
       </c>
       <c r="AN26" s="6">
         <f t="shared" si="14"/>
-        <v>43786</v>
+        <v>43787</v>
       </c>
       <c r="AO26" s="14">
-        <v>53051</v>
+        <v>53052</v>
       </c>
       <c r="AP26" s="7">
         <f t="shared" si="15"/>
-        <v>0.5628753315649867</v>
+        <v>0.56288594164456229</v>
       </c>
       <c r="AQ26" s="13">
         <v>146205</v>
@@ -4813,14 +4813,14 @@
       </c>
       <c r="AS26" s="6">
         <f t="shared" si="16"/>
-        <v>62922</v>
+        <v>62925</v>
       </c>
       <c r="AT26" s="15">
-        <v>120760</v>
+        <v>120763</v>
       </c>
       <c r="AU26" s="7">
         <f t="shared" si="17"/>
-        <v>0.82596354433842889</v>
+        <v>0.82598406347252151</v>
       </c>
       <c r="AV26" s="13">
         <v>71728</v>
@@ -4830,14 +4830,14 @@
       </c>
       <c r="AX26" s="6">
         <f t="shared" si="18"/>
-        <v>33622</v>
+        <v>33623</v>
       </c>
       <c r="AY26" s="14">
-        <v>51515</v>
+        <v>51516</v>
       </c>
       <c r="AZ26" s="7">
         <f t="shared" si="19"/>
-        <v>0.71819930849877311</v>
+        <v>0.71821325005576619</v>
       </c>
       <c r="BA26" s="13">
         <v>70808</v>
@@ -4847,14 +4847,14 @@
       </c>
       <c r="BC26" s="6">
         <f t="shared" si="20"/>
-        <v>21396</v>
+        <v>21397</v>
       </c>
       <c r="BD26" s="14">
-        <v>51520</v>
+        <v>51521</v>
       </c>
       <c r="BE26" s="7">
         <f t="shared" si="21"/>
-        <v>0.72760140097164161</v>
+        <v>0.72761552366964188</v>
       </c>
       <c r="BF26" s="13">
         <v>145908</v>
@@ -4864,14 +4864,14 @@
       </c>
       <c r="BH26" s="6">
         <f t="shared" si="22"/>
-        <v>57954</v>
+        <v>57957</v>
       </c>
       <c r="BI26" s="15">
-        <v>119809</v>
+        <v>119812</v>
       </c>
       <c r="BJ26" s="7">
         <f t="shared" si="23"/>
-        <v>0.82112701154151935</v>
+        <v>0.82114757244290926</v>
       </c>
     </row>
     <row r="27" spans="1:62" x14ac:dyDescent="0.3">
@@ -5025,14 +5025,14 @@
       </c>
       <c r="AS27" s="6">
         <f t="shared" si="16"/>
-        <v>208701</v>
+        <v>208702</v>
       </c>
       <c r="AT27" s="15">
-        <v>521683</v>
+        <v>521684</v>
       </c>
       <c r="AU27" s="7">
         <f t="shared" si="17"/>
-        <v>0.85334068328366119</v>
+        <v>0.85334231902928315</v>
       </c>
       <c r="AV27" s="13">
         <v>246718</v>
@@ -5059,14 +5059,14 @@
       </c>
       <c r="BC27" s="6">
         <f t="shared" si="20"/>
-        <v>51794</v>
+        <v>51795</v>
       </c>
       <c r="BD27" s="14">
-        <v>181279</v>
+        <v>181280</v>
       </c>
       <c r="BE27" s="7">
         <f t="shared" si="21"/>
-        <v>0.75427004581067414</v>
+        <v>0.75427420663485023</v>
       </c>
       <c r="BF27" s="13">
         <v>611625</v>
@@ -5076,14 +5076,14 @@
       </c>
       <c r="BH27" s="6">
         <f t="shared" si="22"/>
-        <v>179900</v>
+        <v>179902</v>
       </c>
       <c r="BI27" s="15">
-        <v>515499</v>
+        <v>515501</v>
       </c>
       <c r="BJ27" s="7">
         <f t="shared" si="23"/>
-        <v>0.84283507050889028</v>
+        <v>0.84283834048640915</v>
       </c>
     </row>
     <row r="28" spans="1:62" x14ac:dyDescent="0.3">
@@ -5347,14 +5347,14 @@
       </c>
       <c r="O29" s="6">
         <f t="shared" si="4"/>
-        <v>127844</v>
+        <v>127845</v>
       </c>
       <c r="P29" s="15">
-        <v>184060</v>
+        <v>184061</v>
       </c>
       <c r="Q29" s="7">
         <f t="shared" si="5"/>
-        <v>0.83751575517930188</v>
+        <v>0.83752030541159128</v>
       </c>
       <c r="R29" s="13">
         <v>104974</v>
@@ -5398,14 +5398,14 @@
       </c>
       <c r="AD29" s="6">
         <f t="shared" si="10"/>
-        <v>139535</v>
+        <v>139536</v>
       </c>
       <c r="AE29" s="15">
-        <v>190131</v>
+        <v>190132</v>
       </c>
       <c r="AF29" s="7">
         <f t="shared" si="11"/>
-        <v>0.86094067677650432</v>
+        <v>0.86094520492118765</v>
       </c>
       <c r="AG29" s="13">
         <v>96497</v>
@@ -5415,14 +5415,14 @@
       </c>
       <c r="AI29" s="6">
         <f t="shared" si="12"/>
-        <v>56623</v>
+        <v>56624</v>
       </c>
       <c r="AJ29" s="14">
-        <v>70156</v>
+        <v>70157</v>
       </c>
       <c r="AK29" s="7">
         <f t="shared" si="13"/>
-        <v>0.72702778324714756</v>
+        <v>0.7270381462636144</v>
       </c>
       <c r="AL29" s="13">
         <v>92661</v>
@@ -5432,14 +5432,14 @@
       </c>
       <c r="AN29" s="6">
         <f t="shared" si="14"/>
-        <v>55024</v>
+        <v>55025</v>
       </c>
       <c r="AO29" s="14">
-        <v>71192</v>
+        <v>71193</v>
       </c>
       <c r="AP29" s="7">
         <f t="shared" si="15"/>
-        <v>0.76830597554526714</v>
+        <v>0.76831676757211775</v>
       </c>
       <c r="AQ29" s="13">
         <v>222288</v>
@@ -5449,14 +5449,14 @@
       </c>
       <c r="AS29" s="6">
         <f t="shared" si="16"/>
-        <v>93480</v>
+        <v>93482</v>
       </c>
       <c r="AT29" s="15">
-        <v>195630</v>
+        <v>195632</v>
       </c>
       <c r="AU29" s="7">
         <f t="shared" si="17"/>
-        <v>0.88007449794860726</v>
+        <v>0.88008349528539553</v>
       </c>
       <c r="AV29" s="13">
         <v>91315</v>
@@ -5466,14 +5466,14 @@
       </c>
       <c r="AX29" s="6">
         <f t="shared" si="18"/>
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="AY29" s="14">
-        <v>71961</v>
+        <v>71962</v>
       </c>
       <c r="AZ29" s="7">
         <f t="shared" si="19"/>
-        <v>0.78805234627388709</v>
+        <v>0.7880632973772107</v>
       </c>
       <c r="BA29" s="13">
         <v>88358</v>
@@ -5483,14 +5483,14 @@
       </c>
       <c r="BC29" s="6">
         <f t="shared" si="20"/>
-        <v>26367</v>
+        <v>26368</v>
       </c>
       <c r="BD29" s="14">
-        <v>72198</v>
+        <v>72199</v>
       </c>
       <c r="BE29" s="7">
         <f t="shared" si="21"/>
-        <v>0.8171076755924761</v>
+        <v>0.81711899318680825</v>
       </c>
       <c r="BF29" s="13">
         <v>223069</v>
@@ -5500,14 +5500,14 @@
       </c>
       <c r="BH29" s="6">
         <f t="shared" si="22"/>
-        <v>74086</v>
+        <v>74090</v>
       </c>
       <c r="BI29" s="15">
-        <v>193576</v>
+        <v>193580</v>
       </c>
       <c r="BJ29" s="7">
         <f t="shared" si="23"/>
-        <v>0.86778530409873178</v>
+        <v>0.86780323577009799</v>
       </c>
     </row>
     <row r="30" spans="1:62" x14ac:dyDescent="0.3">
@@ -5559,14 +5559,14 @@
       </c>
       <c r="O30" s="6">
         <f t="shared" si="4"/>
-        <v>65843</v>
+        <v>65845</v>
       </c>
       <c r="P30" s="15">
-        <v>93525</v>
+        <v>93527</v>
       </c>
       <c r="Q30" s="7">
         <f t="shared" si="5"/>
-        <v>0.89264409723879246</v>
+        <v>0.89266318612619666</v>
       </c>
       <c r="R30" s="13">
         <v>53849</v>
@@ -5610,14 +5610,14 @@
       </c>
       <c r="AD30" s="6">
         <f t="shared" si="10"/>
-        <v>74172</v>
+        <v>74175</v>
       </c>
       <c r="AE30" s="15">
-        <v>95868</v>
+        <v>95871</v>
       </c>
       <c r="AF30" s="7">
         <f t="shared" si="11"/>
-        <v>0.89214390738707217</v>
+        <v>0.89217182527126881</v>
       </c>
       <c r="AG30" s="13">
         <v>51279</v>
@@ -5627,14 +5627,14 @@
       </c>
       <c r="AI30" s="6">
         <f t="shared" si="12"/>
-        <v>31067</v>
+        <v>31069</v>
       </c>
       <c r="AJ30" s="14">
-        <v>38903</v>
+        <v>38905</v>
       </c>
       <c r="AK30" s="7">
         <f t="shared" si="13"/>
-        <v>0.75865363989157353</v>
+        <v>0.75869264221221167</v>
       </c>
       <c r="AL30" s="13">
         <v>48984</v>
@@ -5644,14 +5644,14 @@
       </c>
       <c r="AN30" s="6">
         <f t="shared" si="14"/>
-        <v>28871</v>
+        <v>28872</v>
       </c>
       <c r="AO30" s="14">
-        <v>39190</v>
+        <v>39191</v>
       </c>
       <c r="AP30" s="7">
         <f t="shared" si="15"/>
-        <v>0.80005716152212969</v>
+        <v>0.80007757635146171</v>
       </c>
       <c r="AQ30" s="13">
         <v>105112</v>
@@ -5661,14 +5661,14 @@
       </c>
       <c r="AS30" s="6">
         <f t="shared" si="16"/>
-        <v>41219</v>
+        <v>41222</v>
       </c>
       <c r="AT30" s="15">
-        <v>97363</v>
+        <v>97366</v>
       </c>
       <c r="AU30" s="7">
         <f t="shared" si="17"/>
-        <v>0.92627863612147043</v>
+        <v>0.92630717710632471</v>
       </c>
       <c r="AV30" s="13">
         <v>46049</v>
@@ -5678,14 +5678,14 @@
       </c>
       <c r="AX30" s="6">
         <f t="shared" si="18"/>
-        <v>21824</v>
+        <v>21825</v>
       </c>
       <c r="AY30" s="14">
-        <v>39050</v>
+        <v>39051</v>
       </c>
       <c r="AZ30" s="7">
         <f t="shared" si="19"/>
-        <v>0.84800972876718284</v>
+        <v>0.84803144476535863</v>
       </c>
       <c r="BA30" s="13">
         <v>45889</v>
@@ -5695,14 +5695,14 @@
       </c>
       <c r="BC30" s="6">
         <f t="shared" si="20"/>
-        <v>13565</v>
+        <v>13566</v>
       </c>
       <c r="BD30" s="14">
-        <v>38972</v>
+        <v>38973</v>
       </c>
       <c r="BE30" s="7">
         <f t="shared" si="21"/>
-        <v>0.84926670879731525</v>
+        <v>0.84928850051210525</v>
       </c>
       <c r="BF30" s="13">
         <v>107069</v>
@@ -5712,14 +5712,14 @@
       </c>
       <c r="BH30" s="6">
         <f t="shared" si="22"/>
-        <v>37223</v>
+        <v>37226</v>
       </c>
       <c r="BI30" s="15">
-        <v>96266</v>
+        <v>96269</v>
       </c>
       <c r="BJ30" s="7">
         <f t="shared" si="23"/>
-        <v>0.89910244795412309</v>
+        <v>0.89913046726877066</v>
       </c>
     </row>
     <row r="31" spans="1:62" x14ac:dyDescent="0.3">
@@ -5737,14 +5737,14 @@
       </c>
       <c r="E31" s="6">
         <f t="shared" si="0"/>
-        <v>77511</v>
+        <v>77512</v>
       </c>
       <c r="F31" s="14">
-        <v>102641</v>
+        <v>102642</v>
       </c>
       <c r="G31" s="7">
         <f t="shared" si="1"/>
-        <v>0.57882983222895812</v>
+        <v>0.57883547159171012</v>
       </c>
       <c r="H31" s="13">
         <v>166338</v>
@@ -5754,14 +5754,14 @@
       </c>
       <c r="J31" s="6">
         <f t="shared" si="2"/>
-        <v>76091</v>
+        <v>76092</v>
       </c>
       <c r="K31" s="14">
-        <v>102644</v>
+        <v>102645</v>
       </c>
       <c r="L31" s="7">
         <f t="shared" si="3"/>
-        <v>0.61708088350226642</v>
+        <v>0.61708689535764527</v>
       </c>
       <c r="M31" s="13">
         <v>353290</v>
@@ -5788,14 +5788,14 @@
       </c>
       <c r="T31" s="6">
         <f t="shared" si="6"/>
-        <v>78520</v>
+        <v>78521</v>
       </c>
       <c r="U31" s="14">
-        <v>103538</v>
+        <v>103539</v>
       </c>
       <c r="V31" s="7">
         <f t="shared" si="7"/>
-        <v>0.69121642822332452</v>
+        <v>0.69122310419184063</v>
       </c>
       <c r="W31" s="13">
         <v>145173</v>
@@ -5805,14 +5805,14 @@
       </c>
       <c r="Y31" s="6">
         <f t="shared" si="8"/>
-        <v>77968</v>
+        <v>77969</v>
       </c>
       <c r="Z31" s="14">
-        <v>103934</v>
+        <v>103935</v>
       </c>
       <c r="AA31" s="7">
         <f t="shared" si="9"/>
-        <v>0.71593202592768623</v>
+        <v>0.71593891426091627</v>
       </c>
       <c r="AB31" s="13">
         <v>359995</v>
@@ -5839,14 +5839,14 @@
       </c>
       <c r="AI31" s="6">
         <f t="shared" si="12"/>
-        <v>83177</v>
+        <v>83178</v>
       </c>
       <c r="AJ31" s="14">
-        <v>105194</v>
+        <v>105195</v>
       </c>
       <c r="AK31" s="7">
         <f t="shared" si="13"/>
-        <v>0.7380170623561767</v>
+        <v>0.73802407812763093</v>
       </c>
       <c r="AL31" s="13">
         <v>138001</v>
@@ -5873,14 +5873,14 @@
       </c>
       <c r="AS31" s="6">
         <f t="shared" si="16"/>
-        <v>115104</v>
+        <v>115106</v>
       </c>
       <c r="AT31" s="15">
-        <v>329435</v>
+        <v>329437</v>
       </c>
       <c r="AU31" s="7">
         <f t="shared" si="17"/>
-        <v>0.92863465181309757</v>
+        <v>0.92864028955439293</v>
       </c>
       <c r="AV31" s="13">
         <v>121996</v>
@@ -5924,14 +5924,14 @@
       </c>
       <c r="BH31" s="6">
         <f t="shared" si="22"/>
-        <v>114613</v>
+        <v>114615</v>
       </c>
       <c r="BI31" s="15">
-        <v>325341</v>
+        <v>325343</v>
       </c>
       <c r="BJ31" s="7">
         <f t="shared" si="23"/>
-        <v>0.92564741630959901</v>
+        <v>0.92565310663093148</v>
       </c>
     </row>
     <row r="32" spans="1:62" x14ac:dyDescent="0.3">
@@ -5949,14 +5949,14 @@
       </c>
       <c r="E32" s="6">
         <f t="shared" si="0"/>
-        <v>139156</v>
+        <v>139160</v>
       </c>
       <c r="F32" s="14">
-        <v>250994</v>
+        <v>250998</v>
       </c>
       <c r="G32" s="7">
         <f t="shared" si="1"/>
-        <v>0.6287361850081663</v>
+        <v>0.62874620494784617</v>
       </c>
       <c r="H32" s="13">
         <v>382894</v>
@@ -5966,14 +5966,14 @@
       </c>
       <c r="J32" s="6">
         <f t="shared" si="2"/>
-        <v>135158</v>
+        <v>135161</v>
       </c>
       <c r="K32" s="14">
-        <v>251287</v>
+        <v>251290</v>
       </c>
       <c r="L32" s="7">
         <f t="shared" si="3"/>
-        <v>0.65628346226370748</v>
+        <v>0.65629129733033165</v>
       </c>
       <c r="M32" s="13">
         <v>877062</v>
@@ -5983,14 +5983,14 @@
       </c>
       <c r="O32" s="6">
         <f t="shared" si="4"/>
-        <v>334438</v>
+        <v>334444</v>
       </c>
       <c r="P32" s="15">
-        <v>803167</v>
+        <v>803173</v>
       </c>
       <c r="Q32" s="7">
         <f t="shared" si="5"/>
-        <v>0.91574711935986286</v>
+        <v>0.91575396038136414</v>
       </c>
       <c r="R32" s="13">
         <v>340947</v>
@@ -6000,14 +6000,14 @@
       </c>
       <c r="T32" s="6">
         <f t="shared" si="6"/>
-        <v>151425</v>
+        <v>151428</v>
       </c>
       <c r="U32" s="14">
-        <v>253234</v>
+        <v>253237</v>
       </c>
       <c r="V32" s="7">
         <f t="shared" si="7"/>
-        <v>0.74273714096325827</v>
+        <v>0.74274593998480698</v>
       </c>
       <c r="W32" s="13">
         <v>329795</v>
@@ -6017,14 +6017,14 @@
       </c>
       <c r="Y32" s="6">
         <f t="shared" si="8"/>
-        <v>140556</v>
+        <v>140559</v>
       </c>
       <c r="Z32" s="14">
-        <v>253989</v>
+        <v>253992</v>
       </c>
       <c r="AA32" s="7">
         <f t="shared" si="9"/>
-        <v>0.77014205794508706</v>
+        <v>0.77015115450507132</v>
       </c>
       <c r="AB32" s="13">
         <v>884817</v>
@@ -6034,14 +6034,14 @@
       </c>
       <c r="AD32" s="6">
         <f t="shared" si="10"/>
-        <v>442924</v>
+        <v>442933</v>
       </c>
       <c r="AE32" s="15">
-        <v>818565</v>
+        <v>818574</v>
       </c>
       <c r="AF32" s="7">
         <f t="shared" si="11"/>
-        <v>0.9251235001135828</v>
+        <v>0.92513367170838712</v>
       </c>
       <c r="AG32" s="13">
         <v>320380</v>
@@ -6051,14 +6051,14 @@
       </c>
       <c r="AI32" s="6">
         <f t="shared" si="12"/>
-        <v>164321</v>
+        <v>164325</v>
       </c>
       <c r="AJ32" s="14">
-        <v>256046</v>
+        <v>256050</v>
       </c>
       <c r="AK32" s="7">
         <f t="shared" si="13"/>
-        <v>0.79919470628628508</v>
+        <v>0.79920719146014108</v>
       </c>
       <c r="AL32" s="13">
         <v>311565</v>
@@ -6068,14 +6068,14 @@
       </c>
       <c r="AN32" s="6">
         <f t="shared" si="14"/>
-        <v>130387</v>
+        <v>130391</v>
       </c>
       <c r="AO32" s="14">
-        <v>258446</v>
+        <v>258450</v>
       </c>
       <c r="AP32" s="7">
         <f t="shared" si="15"/>
-        <v>0.82950909120087302</v>
+        <v>0.82952192961340332</v>
       </c>
       <c r="AQ32" s="13">
         <v>877839</v>
@@ -6085,14 +6085,14 @@
       </c>
       <c r="AS32" s="6">
         <f t="shared" si="16"/>
-        <v>171137</v>
+        <v>171144</v>
       </c>
       <c r="AT32" s="15">
-        <v>833009</v>
+        <v>833016</v>
       </c>
       <c r="AU32" s="7">
         <f t="shared" si="17"/>
-        <v>0.94893140997381065</v>
+        <v>0.94893938410118484</v>
       </c>
       <c r="AV32" s="13">
         <v>297941</v>
@@ -6102,14 +6102,14 @@
       </c>
       <c r="AX32" s="6">
         <f t="shared" si="18"/>
-        <v>79200</v>
+        <v>79205</v>
       </c>
       <c r="AY32" s="14">
-        <v>259934</v>
+        <v>259939</v>
       </c>
       <c r="AZ32" s="7">
         <f t="shared" si="19"/>
-        <v>0.8724344752820189</v>
+        <v>0.87245125712808913</v>
       </c>
       <c r="BA32" s="13">
         <v>294413</v>
@@ -6119,14 +6119,14 @@
       </c>
       <c r="BC32" s="6">
         <f t="shared" si="20"/>
-        <v>35890</v>
+        <v>35894</v>
       </c>
       <c r="BD32" s="14">
-        <v>260529</v>
+        <v>260533</v>
       </c>
       <c r="BE32" s="7">
         <f t="shared" si="21"/>
-        <v>0.88490997340470701</v>
+        <v>0.88492355976128767</v>
       </c>
       <c r="BF32" s="13">
         <v>893063</v>
@@ -6136,14 +6136,14 @@
       </c>
       <c r="BH32" s="6">
         <f t="shared" si="22"/>
-        <v>159653</v>
+        <v>159662</v>
       </c>
       <c r="BI32" s="15">
-        <v>839706</v>
+        <v>839715</v>
       </c>
       <c r="BJ32" s="7">
         <f t="shared" si="23"/>
-        <v>0.94025393505273425</v>
+        <v>0.94026401272922511</v>
       </c>
     </row>
     <row r="33" spans="1:62" x14ac:dyDescent="0.3">
@@ -6585,14 +6585,14 @@
       </c>
       <c r="E35" s="6">
         <f t="shared" si="0"/>
-        <v>222275</v>
+        <v>222277</v>
       </c>
       <c r="F35" s="14">
-        <v>358689</v>
+        <v>358691</v>
       </c>
       <c r="G35" s="7">
         <f t="shared" si="1"/>
-        <v>0.50862938116042522</v>
+        <v>0.50863221720714624</v>
       </c>
       <c r="H35" s="13">
         <v>678572</v>
@@ -6602,14 +6602,14 @@
       </c>
       <c r="J35" s="6">
         <f t="shared" si="2"/>
-        <v>218741</v>
+        <v>218744</v>
       </c>
       <c r="K35" s="14">
-        <v>358791</v>
+        <v>358794</v>
       </c>
       <c r="L35" s="7">
         <f t="shared" si="3"/>
-        <v>0.52874418632068521</v>
+        <v>0.52874860736959384</v>
       </c>
       <c r="M35" s="13">
         <v>1405014</v>
@@ -6619,14 +6619,14 @@
       </c>
       <c r="O35" s="6">
         <f t="shared" si="4"/>
-        <v>635995</v>
+        <v>636003</v>
       </c>
       <c r="P35" s="15">
-        <v>1205962</v>
+        <v>1205970</v>
       </c>
       <c r="Q35" s="7">
         <f t="shared" si="5"/>
-        <v>0.85832739033205363</v>
+        <v>0.85833308422549526</v>
       </c>
       <c r="R35" s="13">
         <v>600814</v>
@@ -6636,14 +6636,14 @@
       </c>
       <c r="T35" s="6">
         <f t="shared" si="6"/>
-        <v>231474</v>
+        <v>231478</v>
       </c>
       <c r="U35" s="14">
-        <v>362736</v>
+        <v>362740</v>
       </c>
       <c r="V35" s="7">
         <f t="shared" si="7"/>
-        <v>0.60374092481200503</v>
+        <v>0.60374758244648097</v>
       </c>
       <c r="W35" s="13">
         <v>577797</v>
@@ -6653,14 +6653,14 @@
       </c>
       <c r="Y35" s="6">
         <f t="shared" si="8"/>
-        <v>225107</v>
+        <v>225110</v>
       </c>
       <c r="Z35" s="14">
-        <v>364110</v>
+        <v>364113</v>
       </c>
       <c r="AA35" s="7">
         <f t="shared" si="9"/>
-        <v>0.63016941936354809</v>
+        <v>0.63017461149850207</v>
       </c>
       <c r="AB35" s="13">
         <v>1416919</v>
@@ -6670,14 +6670,14 @@
       </c>
       <c r="AD35" s="6">
         <f t="shared" si="10"/>
-        <v>775506</v>
+        <v>775516</v>
       </c>
       <c r="AE35" s="15">
-        <v>1227797</v>
+        <v>1227807</v>
       </c>
       <c r="AF35" s="7">
         <f t="shared" si="11"/>
-        <v>0.86652589174116512</v>
+        <v>0.86653294930761748</v>
       </c>
       <c r="AG35" s="13">
         <v>553324</v>
@@ -6687,14 +6687,14 @@
       </c>
       <c r="AI35" s="6">
         <f t="shared" si="12"/>
-        <v>245054</v>
+        <v>245058</v>
       </c>
       <c r="AJ35" s="14">
-        <v>367719</v>
+        <v>367723</v>
       </c>
       <c r="AK35" s="7">
         <f t="shared" si="13"/>
-        <v>0.6645636191453832</v>
+        <v>0.6645708481829814</v>
       </c>
       <c r="AL35" s="13">
         <v>528988</v>
@@ -6704,14 +6704,14 @@
       </c>
       <c r="AN35" s="6">
         <f t="shared" si="14"/>
-        <v>217298</v>
+        <v>217300</v>
       </c>
       <c r="AO35" s="14">
-        <v>372202</v>
+        <v>372204</v>
       </c>
       <c r="AP35" s="7">
         <f t="shared" si="15"/>
-        <v>0.70361142407767285</v>
+        <v>0.7036152048817742</v>
       </c>
       <c r="AQ35" s="13">
         <v>1379433</v>
@@ -6721,14 +6721,14 @@
       </c>
       <c r="AS35" s="6">
         <f t="shared" si="16"/>
-        <v>367242</v>
+        <v>367247</v>
       </c>
       <c r="AT35" s="15">
-        <v>1242138</v>
+        <v>1242143</v>
       </c>
       <c r="AU35" s="7">
         <f t="shared" si="17"/>
-        <v>0.90046997570741016</v>
+        <v>0.90047360038508573</v>
       </c>
       <c r="AV35" s="13">
         <v>465114</v>
@@ -6738,14 +6738,14 @@
       </c>
       <c r="AX35" s="6">
         <f t="shared" si="18"/>
-        <v>150902</v>
+        <v>150906</v>
       </c>
       <c r="AY35" s="14">
-        <v>372275</v>
+        <v>372279</v>
       </c>
       <c r="AZ35" s="7">
         <f t="shared" si="19"/>
-        <v>0.80039517193634246</v>
+        <v>0.80040377197848267</v>
       </c>
       <c r="BA35" s="13">
         <v>457177</v>
@@ -6755,14 +6755,14 @@
       </c>
       <c r="BC35" s="6">
         <f t="shared" si="20"/>
-        <v>87745</v>
+        <v>87748</v>
       </c>
       <c r="BD35" s="14">
-        <v>371928</v>
+        <v>371931</v>
       </c>
       <c r="BE35" s="7">
         <f t="shared" si="21"/>
-        <v>0.81353173934821743</v>
+        <v>0.81353830135811733</v>
       </c>
       <c r="BF35" s="13">
         <v>1380633</v>
@@ -6772,14 +6772,14 @@
       </c>
       <c r="BH35" s="6">
         <f t="shared" si="22"/>
-        <v>474414</v>
+        <v>474425</v>
       </c>
       <c r="BI35" s="15">
-        <v>1225976</v>
+        <v>1225987</v>
       </c>
       <c r="BJ35" s="7">
         <f t="shared" si="23"/>
-        <v>0.88798109273065329</v>
+        <v>0.88798906009055267</v>
       </c>
     </row>
     <row r="36" spans="1:62" x14ac:dyDescent="0.3">
@@ -6797,14 +6797,14 @@
       </c>
       <c r="E36" s="6">
         <f t="shared" si="0"/>
-        <v>256603</v>
+        <v>256607</v>
       </c>
       <c r="F36" s="14">
-        <v>364974</v>
+        <v>364978</v>
       </c>
       <c r="G36" s="7">
         <f t="shared" si="1"/>
-        <v>0.73409268731256672</v>
+        <v>0.73410073273703325</v>
       </c>
       <c r="H36" s="13">
         <v>485610</v>
@@ -6814,14 +6814,14 @@
       </c>
       <c r="J36" s="6">
         <f t="shared" si="2"/>
-        <v>259093</v>
+        <v>259097</v>
       </c>
       <c r="K36" s="14">
-        <v>366707</v>
+        <v>366711</v>
       </c>
       <c r="L36" s="7">
         <f t="shared" si="3"/>
-        <v>0.75514713453182591</v>
+        <v>0.75515537159448942</v>
       </c>
       <c r="M36" s="13">
         <v>710827</v>
@@ -6831,14 +6831,14 @@
       </c>
       <c r="O36" s="6">
         <f t="shared" si="4"/>
-        <v>374009</v>
+        <v>374019</v>
       </c>
       <c r="P36" s="15">
-        <v>612191</v>
+        <v>612201</v>
       </c>
       <c r="Q36" s="7">
         <f t="shared" si="5"/>
-        <v>0.86123768511888266</v>
+        <v>0.86125175323953651</v>
       </c>
       <c r="R36" s="13">
         <v>464623</v>
@@ -6848,14 +6848,14 @@
       </c>
       <c r="T36" s="6">
         <f t="shared" si="6"/>
-        <v>276277</v>
+        <v>276282</v>
       </c>
       <c r="U36" s="14">
-        <v>372863</v>
+        <v>372868</v>
       </c>
       <c r="V36" s="7">
         <f t="shared" si="7"/>
-        <v>0.8025065483198206</v>
+        <v>0.80251730973283719</v>
       </c>
       <c r="W36" s="13">
         <v>451202</v>
@@ -6865,14 +6865,14 @@
       </c>
       <c r="Y36" s="6">
         <f t="shared" si="8"/>
-        <v>271115</v>
+        <v>271119</v>
       </c>
       <c r="Z36" s="14">
-        <v>375738</v>
+        <v>375742</v>
       </c>
       <c r="AA36" s="7">
         <f t="shared" si="9"/>
-        <v>0.83274896831131062</v>
+        <v>0.83275783352024146</v>
       </c>
       <c r="AB36" s="13">
         <v>709880</v>
@@ -6882,14 +6882,14 @@
       </c>
       <c r="AD36" s="6">
         <f t="shared" si="10"/>
-        <v>427615</v>
+        <v>427625</v>
       </c>
       <c r="AE36" s="15">
-        <v>628845</v>
+        <v>628855</v>
       </c>
       <c r="AF36" s="7">
         <f t="shared" si="11"/>
-        <v>0.88584690370203412</v>
+        <v>0.88586099058995882</v>
       </c>
       <c r="AG36" s="13">
         <v>448411</v>
@@ -6899,14 +6899,14 @@
       </c>
       <c r="AI36" s="6">
         <f t="shared" si="12"/>
-        <v>282654</v>
+        <v>282659</v>
       </c>
       <c r="AJ36" s="14">
-        <v>381902</v>
+        <v>381907</v>
       </c>
       <c r="AK36" s="7">
         <f t="shared" si="13"/>
-        <v>0.85167848246363265</v>
+        <v>0.85168963294834421</v>
       </c>
       <c r="AL36" s="13">
         <v>443261</v>
@@ -6916,14 +6916,14 @@
       </c>
       <c r="AN36" s="6">
         <f t="shared" si="14"/>
-        <v>260459</v>
+        <v>260466</v>
       </c>
       <c r="AO36" s="14">
-        <v>386322</v>
+        <v>386329</v>
       </c>
       <c r="AP36" s="7">
         <f t="shared" si="15"/>
-        <v>0.87154520699993909</v>
+        <v>0.871560999050221</v>
       </c>
       <c r="AQ36" s="13">
         <v>723207</v>
@@ -6933,14 +6933,14 @@
       </c>
       <c r="AS36" s="6">
         <f t="shared" si="16"/>
-        <v>261068</v>
+        <v>261080</v>
       </c>
       <c r="AT36" s="15">
-        <v>644772</v>
+        <v>644784</v>
       </c>
       <c r="AU36" s="7">
         <f t="shared" si="17"/>
-        <v>0.89154557408874635</v>
+        <v>0.89156216684849565</v>
       </c>
       <c r="AV36" s="13">
         <v>443230</v>
@@ -6950,14 +6950,14 @@
       </c>
       <c r="AX36" s="6">
         <f t="shared" si="18"/>
-        <v>196222</v>
+        <v>196229</v>
       </c>
       <c r="AY36" s="14">
-        <v>390292</v>
+        <v>390299</v>
       </c>
       <c r="AZ36" s="7">
         <f t="shared" si="19"/>
-        <v>0.88056313877670733</v>
+        <v>0.88057893193150283</v>
       </c>
       <c r="BA36" s="13">
         <v>443322</v>
@@ -6967,14 +6967,14 @@
       </c>
       <c r="BC36" s="6">
         <f t="shared" si="20"/>
-        <v>88461</v>
+        <v>88469</v>
       </c>
       <c r="BD36" s="14">
-        <v>389679</v>
+        <v>389687</v>
       </c>
       <c r="BE36" s="7">
         <f t="shared" si="21"/>
-        <v>0.87899765858676082</v>
+        <v>0.87901570416085828</v>
       </c>
       <c r="BF36" s="13">
         <v>734800</v>
@@ -6984,14 +6984,14 @@
       </c>
       <c r="BH36" s="6">
         <f t="shared" si="22"/>
-        <v>185102</v>
+        <v>185117</v>
       </c>
       <c r="BI36" s="15">
-        <v>637977</v>
+        <v>637992</v>
       </c>
       <c r="BJ36" s="7">
         <f t="shared" si="23"/>
-        <v>0.86823217201959713</v>
+        <v>0.86825258573761566</v>
       </c>
     </row>
     <row r="37" spans="1:62" x14ac:dyDescent="0.3">
@@ -7433,14 +7433,14 @@
       </c>
       <c r="E39" s="6">
         <f t="shared" si="0"/>
-        <v>107054</v>
+        <v>107055</v>
       </c>
       <c r="F39" s="14">
-        <v>146413</v>
+        <v>146414</v>
       </c>
       <c r="G39" s="7">
         <f t="shared" si="1"/>
-        <v>0.72367757688391543</v>
+        <v>0.72368251959786078</v>
       </c>
       <c r="H39" s="13">
         <v>195184</v>
@@ -7450,14 +7450,14 @@
       </c>
       <c r="J39" s="6">
         <f t="shared" si="2"/>
-        <v>109489</v>
+        <v>109490</v>
       </c>
       <c r="K39" s="14">
-        <v>147127</v>
+        <v>147128</v>
       </c>
       <c r="L39" s="7">
         <f t="shared" si="3"/>
-        <v>0.7537861709976228</v>
+        <v>0.75379129436839087</v>
       </c>
       <c r="M39" s="13">
         <v>295913</v>
@@ -7467,14 +7467,14 @@
       </c>
       <c r="O39" s="6">
         <f t="shared" si="4"/>
-        <v>164047</v>
+        <v>164050</v>
       </c>
       <c r="P39" s="15">
-        <v>262820</v>
+        <v>262823</v>
       </c>
       <c r="Q39" s="7">
         <f t="shared" si="5"/>
-        <v>0.88816645432948194</v>
+        <v>0.88817659244440084</v>
       </c>
       <c r="R39" s="13">
         <v>189177</v>
@@ -7484,14 +7484,14 @@
       </c>
       <c r="T39" s="6">
         <f t="shared" si="6"/>
-        <v>118723</v>
+        <v>118727</v>
       </c>
       <c r="U39" s="14">
-        <v>149154</v>
+        <v>149158</v>
       </c>
       <c r="V39" s="7">
         <f t="shared" si="7"/>
-        <v>0.78843622639115751</v>
+        <v>0.78845737061059218</v>
       </c>
       <c r="W39" s="13">
         <v>187045</v>
@@ -7501,14 +7501,14 @@
       </c>
       <c r="Y39" s="6">
         <f t="shared" si="8"/>
-        <v>120612</v>
+        <v>120616</v>
       </c>
       <c r="Z39" s="14">
-        <v>150231</v>
+        <v>150235</v>
       </c>
       <c r="AA39" s="7">
         <f t="shared" si="9"/>
-        <v>0.80318105268785589</v>
+        <v>0.80320243791600954</v>
       </c>
       <c r="AB39" s="13">
         <v>301836</v>
@@ -7518,14 +7518,14 @@
       </c>
       <c r="AD39" s="6">
         <f t="shared" si="10"/>
-        <v>185928</v>
+        <v>185931</v>
       </c>
       <c r="AE39" s="15">
-        <v>268527</v>
+        <v>268530</v>
       </c>
       <c r="AF39" s="7">
         <f t="shared" si="11"/>
-        <v>0.88964537033355862</v>
+        <v>0.88965530950582439</v>
       </c>
       <c r="AG39" s="13">
         <v>184754</v>
@@ -7535,14 +7535,14 @@
       </c>
       <c r="AI39" s="6">
         <f t="shared" si="12"/>
-        <v>115710</v>
+        <v>115713</v>
       </c>
       <c r="AJ39" s="14">
-        <v>152280</v>
+        <v>152283</v>
       </c>
       <c r="AK39" s="7">
         <f t="shared" si="13"/>
-        <v>0.82423113978587748</v>
+        <v>0.82424737759398981</v>
       </c>
       <c r="AL39" s="13">
         <v>180486</v>
@@ -7552,14 +7552,14 @@
       </c>
       <c r="AN39" s="6">
         <f t="shared" si="14"/>
-        <v>98545</v>
+        <v>98548</v>
       </c>
       <c r="AO39" s="14">
-        <v>153971</v>
+        <v>153974</v>
       </c>
       <c r="AP39" s="7">
         <f t="shared" si="15"/>
-        <v>0.85309109847855236</v>
+        <v>0.85310772026639181</v>
       </c>
       <c r="AQ39" s="13">
         <v>302709</v>
@@ -7569,14 +7569,14 @@
       </c>
       <c r="AS39" s="6">
         <f t="shared" si="16"/>
-        <v>112539</v>
+        <v>112543</v>
       </c>
       <c r="AT39" s="15">
-        <v>273389</v>
+        <v>273393</v>
       </c>
       <c r="AU39" s="7">
         <f t="shared" si="17"/>
-        <v>0.90314130072115462</v>
+        <v>0.90315451473197028</v>
       </c>
       <c r="AV39" s="13">
         <v>175450</v>
@@ -7586,14 +7586,14 @@
       </c>
       <c r="AX39" s="6">
         <f t="shared" si="18"/>
-        <v>78383</v>
+        <v>78389</v>
       </c>
       <c r="AY39" s="14">
-        <v>155018</v>
+        <v>155024</v>
       </c>
       <c r="AZ39" s="7">
         <f t="shared" si="19"/>
-        <v>0.88354516956397833</v>
+        <v>0.88357936734112286</v>
       </c>
       <c r="BA39" s="13">
         <v>174499</v>
@@ -7603,14 +7603,14 @@
       </c>
       <c r="BC39" s="6">
         <f t="shared" si="20"/>
-        <v>36472</v>
+        <v>36479</v>
       </c>
       <c r="BD39" s="14">
-        <v>155252</v>
+        <v>155259</v>
       </c>
       <c r="BE39" s="7">
         <f t="shared" si="21"/>
-        <v>0.88970137364684043</v>
+        <v>0.88974148848990542</v>
       </c>
       <c r="BF39" s="13">
         <v>304085</v>
@@ -7620,14 +7620,14 @@
       </c>
       <c r="BH39" s="6">
         <f t="shared" si="22"/>
-        <v>83598</v>
+        <v>83608</v>
       </c>
       <c r="BI39" s="15">
-        <v>273284</v>
+        <v>273294</v>
       </c>
       <c r="BJ39" s="7">
         <f t="shared" si="23"/>
-        <v>0.89870924248154294</v>
+        <v>0.89874212802341447</v>
       </c>
     </row>
     <row r="40" spans="1:62" x14ac:dyDescent="0.3">
@@ -7645,14 +7645,14 @@
       </c>
       <c r="E40" s="6">
         <f t="shared" si="0"/>
-        <v>374874</v>
+        <v>374894</v>
       </c>
       <c r="F40" s="14">
-        <v>520751</v>
+        <v>520771</v>
       </c>
       <c r="G40" s="7">
         <f t="shared" si="1"/>
-        <v>0.76430192179551537</v>
+        <v>0.76433127562956638</v>
       </c>
       <c r="H40" s="13">
         <v>679109</v>
@@ -7662,14 +7662,14 @@
       </c>
       <c r="J40" s="6">
         <f t="shared" si="2"/>
-        <v>379426</v>
+        <v>379449</v>
       </c>
       <c r="K40" s="14">
-        <v>523720</v>
+        <v>523743</v>
       </c>
       <c r="L40" s="7">
         <f t="shared" si="3"/>
-        <v>0.77118695231546042</v>
+        <v>0.77122082022179062</v>
       </c>
       <c r="M40" s="13">
         <v>894344</v>
@@ -7679,14 +7679,14 @@
       </c>
       <c r="O40" s="6">
         <f t="shared" si="4"/>
-        <v>479426</v>
+        <v>479456</v>
       </c>
       <c r="P40" s="15">
-        <v>752522</v>
+        <v>752552</v>
       </c>
       <c r="Q40" s="7">
         <f t="shared" si="5"/>
-        <v>0.84142343438319034</v>
+        <v>0.84145697852280554</v>
       </c>
       <c r="R40" s="13">
         <v>670695</v>
@@ -7696,14 +7696,14 @@
       </c>
       <c r="T40" s="6">
         <f t="shared" si="6"/>
-        <v>398503</v>
+        <v>398523</v>
       </c>
       <c r="U40" s="14">
-        <v>530980</v>
+        <v>531000</v>
       </c>
       <c r="V40" s="7">
         <f t="shared" si="7"/>
-        <v>0.79168623591945664</v>
+        <v>0.79171605573323189</v>
       </c>
       <c r="W40" s="13">
         <v>664170</v>
@@ -7713,14 +7713,14 @@
       </c>
       <c r="Y40" s="6">
         <f t="shared" si="8"/>
-        <v>396985</v>
+        <v>397010</v>
       </c>
       <c r="Z40" s="14">
-        <v>534922</v>
+        <v>534947</v>
       </c>
       <c r="AA40" s="7">
         <f t="shared" si="9"/>
-        <v>0.80539922007919662</v>
+        <v>0.8054368610446121</v>
       </c>
       <c r="AB40" s="13">
         <v>900385</v>
@@ -7730,14 +7730,14 @@
       </c>
       <c r="AD40" s="6">
         <f t="shared" si="10"/>
-        <v>541877</v>
+        <v>541915</v>
       </c>
       <c r="AE40" s="15">
-        <v>769353</v>
+        <v>769391</v>
       </c>
       <c r="AF40" s="7">
         <f t="shared" si="11"/>
-        <v>0.85447114289998172</v>
+        <v>0.85451334706819859</v>
       </c>
       <c r="AG40" s="13">
         <v>654051</v>
@@ -7747,14 +7747,14 @@
       </c>
       <c r="AI40" s="6">
         <f t="shared" si="12"/>
-        <v>407274</v>
+        <v>407302</v>
       </c>
       <c r="AJ40" s="14">
-        <v>542107</v>
+        <v>542135</v>
       </c>
       <c r="AK40" s="7">
         <f t="shared" si="13"/>
-        <v>0.82884515121909452</v>
+        <v>0.82888796133634834</v>
       </c>
       <c r="AL40" s="13">
         <v>640748</v>
@@ -7764,14 +7764,14 @@
       </c>
       <c r="AN40" s="6">
         <f t="shared" si="14"/>
-        <v>372392</v>
+        <v>372418</v>
       </c>
       <c r="AO40" s="14">
-        <v>547336</v>
+        <v>547362</v>
       </c>
       <c r="AP40" s="7">
         <f t="shared" si="15"/>
-        <v>0.85421413722711581</v>
+        <v>0.85425471480207504</v>
       </c>
       <c r="AQ40" s="13">
         <v>877850</v>
@@ -7781,14 +7781,14 @@
       </c>
       <c r="AS40" s="6">
         <f t="shared" si="16"/>
-        <v>284021</v>
+        <v>284056</v>
       </c>
       <c r="AT40" s="15">
-        <v>786537</v>
+        <v>786572</v>
       </c>
       <c r="AU40" s="7">
         <f t="shared" si="17"/>
-        <v>0.89598109016346761</v>
+        <v>0.89602096030073475</v>
       </c>
       <c r="AV40" s="13">
         <v>620078</v>
@@ -7798,14 +7798,14 @@
       </c>
       <c r="AX40" s="6">
         <f t="shared" si="18"/>
-        <v>257026</v>
+        <v>257053</v>
       </c>
       <c r="AY40" s="14">
-        <v>553872</v>
+        <v>553899</v>
       </c>
       <c r="AZ40" s="7">
         <f t="shared" si="19"/>
-        <v>0.89322956144227017</v>
+        <v>0.89327310435138807</v>
       </c>
       <c r="BA40" s="13">
         <v>613352</v>
@@ -7815,14 +7815,14 @@
       </c>
       <c r="BC40" s="6">
         <f t="shared" si="20"/>
-        <v>101371</v>
+        <v>101400</v>
       </c>
       <c r="BD40" s="14">
-        <v>555605</v>
+        <v>555634</v>
       </c>
       <c r="BE40" s="7">
         <f t="shared" si="21"/>
-        <v>0.90585014803897268</v>
+        <v>0.90589742920867622</v>
       </c>
       <c r="BF40" s="13">
         <v>876639</v>
@@ -7832,14 +7832,14 @@
       </c>
       <c r="BH40" s="6">
         <f t="shared" si="22"/>
-        <v>217634</v>
+        <v>217692</v>
       </c>
       <c r="BI40" s="15">
-        <v>785665</v>
+        <v>785723</v>
       </c>
       <c r="BJ40" s="7">
         <f t="shared" si="23"/>
-        <v>0.89622410136897857</v>
+        <v>0.89629026315279148</v>
       </c>
     </row>
     <row r="41" spans="1:62" x14ac:dyDescent="0.3">
@@ -8451,14 +8451,14 @@
       </c>
       <c r="BC43" s="6">
         <f t="shared" si="20"/>
-        <v>50112</v>
+        <v>50113</v>
       </c>
       <c r="BD43" s="14">
-        <v>185998</v>
+        <v>185999</v>
       </c>
       <c r="BE43" s="7">
         <f t="shared" si="21"/>
-        <v>0.78103492439416655</v>
+        <v>0.78103912355181548</v>
       </c>
       <c r="BF43" s="13">
         <v>357819</v>
@@ -8468,14 +8468,14 @@
       </c>
       <c r="BH43" s="6">
         <f t="shared" si="22"/>
-        <v>87526</v>
+        <v>87527</v>
       </c>
       <c r="BI43" s="15">
-        <v>282587</v>
+        <v>282588</v>
       </c>
       <c r="BJ43" s="7">
         <f t="shared" si="23"/>
-        <v>0.78974844823779622</v>
+        <v>0.78975124294685306</v>
       </c>
     </row>
     <row r="44" spans="1:62" x14ac:dyDescent="0.3">
@@ -9111,15 +9111,15 @@
       </c>
       <c r="E47" s="8">
         <f>F47-D47</f>
-        <v>2360170</v>
+        <v>2360211</v>
       </c>
       <c r="F47" s="10">
         <f>SUM(F9:F46)</f>
-        <v>3455888</v>
+        <v>3455929</v>
       </c>
       <c r="G47" s="9">
         <f>F47/C47</f>
-        <v>0.60008942594620029</v>
+        <v>0.60009654529337353</v>
       </c>
       <c r="H47" s="10">
         <f>SUM(H9:H46)</f>
@@ -9131,15 +9131,15 @@
       </c>
       <c r="J47" s="8">
         <f>K47-I47</f>
-        <v>2353613</v>
+        <v>2353657</v>
       </c>
       <c r="K47" s="10">
         <f>SUM(K9:K46)</f>
-        <v>3468845</v>
+        <v>3468889</v>
       </c>
       <c r="L47" s="9">
         <f>K47/H47</f>
-        <v>0.62338799648629961</v>
+        <v>0.62339590374991194</v>
       </c>
       <c r="M47" s="10">
         <f>SUM(M9:M46)</f>
@@ -9151,15 +9151,15 @@
       </c>
       <c r="O47" s="8">
         <f>P47-N47</f>
-        <v>4976363</v>
+        <v>4976443</v>
       </c>
       <c r="P47" s="10">
         <f>SUM(P9:P46)</f>
-        <v>8855304</v>
+        <v>8855384</v>
       </c>
       <c r="Q47" s="9">
         <f>P47/M47</f>
-        <v>0.85489118540423092</v>
+        <v>0.8548989086054708</v>
       </c>
       <c r="R47" s="10">
         <f>SUM(R9:R46)</f>
@@ -9171,15 +9171,15 @@
       </c>
       <c r="T47" s="8">
         <f>U47-S47</f>
-        <v>2484372</v>
+        <v>2484416</v>
       </c>
       <c r="U47" s="10">
         <f>SUM(U9:U46)</f>
-        <v>3513942</v>
+        <v>3513986</v>
       </c>
       <c r="V47" s="9">
         <f>U47/R47</f>
-        <v>0.68455273656129112</v>
+        <v>0.68456130822252192</v>
       </c>
       <c r="W47" s="10">
         <f>SUM(W9:W46)</f>
@@ -9191,15 +9191,15 @@
       </c>
       <c r="Y47" s="8">
         <f>Z47-X47</f>
-        <v>2446559</v>
+        <v>2446610</v>
       </c>
       <c r="Z47" s="10">
         <f>SUM(Z9:Z46)</f>
-        <v>3535487</v>
+        <v>3535538</v>
       </c>
       <c r="AA47" s="9">
         <f>Z47/W47</f>
-        <v>0.70913033484393062</v>
+        <v>0.70914056416936078</v>
       </c>
       <c r="AB47" s="10">
         <f>SUM(AB9:AB46)</f>
@@ -9211,15 +9211,15 @@
       </c>
       <c r="AD47" s="8">
         <f>AE47-AC47</f>
-        <v>5974354</v>
+        <v>5974451</v>
       </c>
       <c r="AE47" s="10">
         <f>SUM(AE9:AE46)</f>
-        <v>9059357</v>
+        <v>9059454</v>
       </c>
       <c r="AF47" s="9">
         <f>AE47/AB47</f>
-        <v>0.86495301520534928</v>
+        <v>0.86496227639711765</v>
       </c>
       <c r="AG47" s="10">
         <f>SUM(AG9:AG46)</f>
@@ -9231,15 +9231,15 @@
       </c>
       <c r="AI47" s="8">
         <f>AJ47-AH47</f>
-        <v>2598214</v>
+        <v>2598274</v>
       </c>
       <c r="AJ47" s="10">
         <f>SUM(AJ9:AJ46)</f>
-        <v>3583961</v>
+        <v>3584021</v>
       </c>
       <c r="AK47" s="9">
         <f>AJ47/AG47</f>
-        <v>0.73963875353003861</v>
+        <v>0.73965113600998522</v>
       </c>
       <c r="AL47" s="10">
         <f>SUM(AL9:AL46)</f>
@@ -9251,15 +9251,15 @@
       </c>
       <c r="AN47" s="8">
         <f>AO47-AM47</f>
-        <v>2369256</v>
+        <v>2369312</v>
       </c>
       <c r="AO47" s="10">
         <f>SUM(AO9:AO46)</f>
-        <v>3627338</v>
+        <v>3627394</v>
       </c>
       <c r="AP47" s="9">
         <f>AO47/AL47</f>
-        <v>0.77193910612801253</v>
+        <v>0.77195102356993361</v>
       </c>
       <c r="AQ47" s="10">
         <f>SUM(AQ9:AQ46)</f>
@@ -9271,15 +9271,15 @@
       </c>
       <c r="AS47" s="8">
         <f>AT47-AR47</f>
-        <v>3171037</v>
+        <v>3171130</v>
       </c>
       <c r="AT47" s="10">
         <f>SUM(AT9:AT46)</f>
-        <v>9226919</v>
+        <v>9227012</v>
       </c>
       <c r="AU47" s="9">
         <f>AT47/AQ47</f>
-        <v>0.88970639142063646</v>
+        <v>0.8897153589529625</v>
       </c>
       <c r="AV47" s="10">
         <f>SUM(AV9:AV46)</f>
@@ -9291,15 +9291,15 @@
       </c>
       <c r="AX47" s="8">
         <f>AY47-AW47</f>
-        <v>1737610</v>
+        <v>1737671</v>
       </c>
       <c r="AY47" s="10">
         <f>SUM(AY9:AY46)</f>
-        <v>3649947</v>
+        <v>3650008</v>
       </c>
       <c r="AZ47" s="9">
         <f>AY47/AV47</f>
-        <v>0.81791199497682698</v>
+        <v>0.817925664389477</v>
       </c>
       <c r="BA47" s="10">
         <f>SUM(BA9:BA46)</f>
@@ -9311,15 +9311,15 @@
       </c>
       <c r="BC47" s="8">
         <f>BD47-BB47</f>
-        <v>869187</v>
+        <v>869256</v>
       </c>
       <c r="BD47" s="10">
         <f>SUM(BD9:BD46)</f>
-        <v>3647813</v>
+        <v>3647882</v>
       </c>
       <c r="BE47" s="9">
         <f>BD47/BA47</f>
-        <v>0.83396882515934923</v>
+        <v>0.83398460004938224</v>
       </c>
       <c r="BF47" s="10">
         <f>SUM(BF9:BF46)</f>
@@ -9331,48 +9331,48 @@
       </c>
       <c r="BH47" s="8">
         <f>BI47-BG47</f>
-        <v>2887731</v>
+        <v>2887872</v>
       </c>
       <c r="BI47" s="10">
         <f>SUM(BI9:BI46)</f>
-        <v>9180125</v>
+        <v>9180266</v>
       </c>
       <c r="BJ47" s="9">
         <f>BI47/BF47</f>
-        <v>0.88009754569254683</v>
+        <v>0.88011106334660305</v>
       </c>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="J57" s="18"/>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="J55" s="18"/>
     </row>
-    <row r="59" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A59" s="3" t="s">
+    <row r="57" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A57" s="3" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A61" s="24" t="s">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A59" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="B61" s="24"/>
-      <c r="C61" s="24"/>
-      <c r="D61" s="24"/>
-      <c r="E61" s="24"/>
-      <c r="F61" s="5"/>
+      <c r="B59" s="24"/>
+      <c r="C59" s="24"/>
+      <c r="D59" s="24"/>
+      <c r="E59" s="24"/>
+      <c r="F59" s="5"/>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="C62" s="4"/>
-      <c r="D62" s="4"/>
-      <c r="E62" s="4"/>
-      <c r="F62" s="4"/>
-      <c r="G62" s="4"/>
-      <c r="H62" s="4"/>
-      <c r="I62" s="4"/>
-      <c r="J62" s="4"/>
-      <c r="K62" s="4"/>
-      <c r="L62" s="4"/>
-      <c r="M62" s="4"/>
-      <c r="N62" s="4"/>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="C60" s="4"/>
+      <c r="D60" s="4"/>
+      <c r="E60" s="4"/>
+      <c r="F60" s="4"/>
+      <c r="G60" s="4"/>
+      <c r="H60" s="4"/>
+      <c r="I60" s="4"/>
+      <c r="J60" s="4"/>
+      <c r="K60" s="4"/>
+      <c r="L60" s="4"/>
+      <c r="M60" s="4"/>
+      <c r="N60" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="18">
@@ -9384,7 +9384,7 @@
     <mergeCell ref="AG7:AK7"/>
     <mergeCell ref="AL7:AP7"/>
     <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A61:E61"/>
+    <mergeCell ref="A59:E59"/>
     <mergeCell ref="M7:Q7"/>
     <mergeCell ref="R7:V7"/>
     <mergeCell ref="W7:AA7"/>
